--- a/saidas/ordens_dia/ordem_dia_2026_07_28_executor_v5_5.xlsx
+++ b/saidas/ordens_dia/ordem_dia_2026_07_28_executor_v5_5.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE7"/>
+  <dimension ref="A1:DE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1020,40 +1020,40 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4066</v>
+        <v>0.4079</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6757</v>
+        <v>0.6774</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3532</v>
+        <v>0.3564</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9105</v>
+        <v>0.9012</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1583</v>
+        <v>0.1617</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1215</v>
+        <v>0.1232</v>
       </c>
       <c r="R2" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1619</v>
+        <v>0.1624</v>
       </c>
       <c r="T2" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U2" t="n">
         <v>0.245</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0491</v>
+        <v>0.0489</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -1067,49 +1067,49 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.3273</v>
+        <v>0.3283</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.0229</v>
+        <v>1.0258</v>
       </c>
       <c r="AB2" t="n">
         <v>0.244</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3273</v>
+        <v>0.3283</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0692</v>
+        <v>0.0706</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0905</v>
+        <v>0.0919</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1438</v>
+        <v>0.1461</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0142</v>
+        <v>0.0137</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.3545</v>
+        <v>0.3162</v>
       </c>
       <c r="AI2" t="n">
-        <v>18.71</v>
+        <v>18.87</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19.33</v>
+        <v>19.47</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.0999</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.044322</v>
+        <v>0.059038</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.118375</v>
+        <v>1.116637</v>
       </c>
       <c r="AN2" t="n">
-        <v>11.84</v>
+        <v>11.66</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -1139,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.039722</v>
+        <v>0.038286</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.1158</v>
+        <v>1.542</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.5347</v>
+        <v>0.585</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.5347</v>
+        <v>0.585</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.244 | spread_35_20: esp=+0.069 | spread_45_25: esp=+0.090 | spread_45_15: esp=+0.144</t>
+          <t>naked_30: esp=+0.244 | spread_35_20: esp=+0.071 | spread_45_25: esp=+0.092 | spread_45_15: esp=+0.146</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.327 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.328 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1405,40 +1405,40 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1011</v>
+        <v>0.1031</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8298</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4333</v>
+        <v>0.4426</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2882</v>
+        <v>1.2819</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6083</v>
+        <v>0.7336</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0694</v>
+        <v>-0.059</v>
       </c>
       <c r="R3" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0058</v>
+        <v>0.0101</v>
       </c>
       <c r="T3" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6405</v>
+        <v>0.6505</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1205</v>
+        <v>0.1186</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1452,49 +1452,49 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.8126</v>
+        <v>0.8244</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5393</v>
+        <v>2.5762</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6395</v>
+        <v>0.6495</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8126</v>
+        <v>0.8244</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.159</v>
+        <v>0.1626</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2076</v>
+        <v>0.2106</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3189</v>
+        <v>0.3251</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0413</v>
+        <v>0.0398</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2355</v>
+        <v>0.2154</v>
       </c>
       <c r="AI3" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0648</v>
+        <v>0.067</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.203546</v>
+        <v>-0.196543</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.120573</v>
+        <v>1.162918</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.06</v>
+        <v>16.29</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
@@ -1524,10 +1524,10 @@
         <v>-1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.115249</v>
+        <v>0.111106</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.7661</v>
+        <v>1.769</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1675,10 +1675,10 @@
         <v>1</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.6065</v>
+        <v>0.6108</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.6065</v>
+        <v>0.6108</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.639 | spread_35_20: esp=+0.159 | spread_45_25: esp=+0.208 | spread_45_15: esp=+0.319</t>
+          <t>naked_30: esp=+0.649 | spread_35_20: esp=+0.163 | spread_45_25: esp=+0.211 | spread_45_15: esp=+0.325</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.813 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.824 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1789,13 +1789,13 @@
         <v>124</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2725</v>
+        <v>0.2719</v>
       </c>
       <c r="M4" t="n">
         <v>0.6613</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3333</v>
+        <v>0.3309</v>
       </c>
       <c r="O4" t="n">
         <v>0.6983</v>
@@ -1807,19 +1807,19 @@
         <v>0.0013</v>
       </c>
       <c r="R4" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="S4" t="n">
         <v>0.0726</v>
       </c>
       <c r="T4" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U4" t="n">
         <v>0.1501</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0507</v>
+        <v>0.0505</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1854,28 +1854,28 @@
         <v>0.1138</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0187</v>
+        <v>0.0188</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.324</v>
+        <v>0.3289</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5.04</v>
+        <v>5.13</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0409</v>
+        <v>0.0408</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.071608</v>
+        <v>-0.042337</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.101101</v>
+        <v>1.098742</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.11</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
@@ -1905,10 +1905,10 @@
         <v>-1</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.052086</v>
+        <v>0.052471</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.3748</v>
+        <v>0.8069</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2060,10 +2060,10 @@
         <v>1</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.5828</v>
+        <v>0.525</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.5828</v>
+        <v>0.525</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2132,26 +2132,26 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL (VETADA)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>VETADA — esperança histórica insuficiente</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2171,44 +2171,44 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1692</v>
+        <v>0.125</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5974</v>
+        <v>0.5263</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2353</v>
+        <v>0.1475</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7138</v>
+        <v>0.5541</v>
       </c>
       <c r="P5" t="n">
         <v>-0.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.168</v>
+        <v>-0.0184</v>
       </c>
       <c r="R5" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0547</v>
+        <v>-0.0692</v>
       </c>
       <c r="T5" t="n">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0565</v>
+        <v>-0.0577</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0481</v>
+        <v>0.0499</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2216,51 +2216,55 @@
           <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>esperanca</t>
+        </is>
+      </c>
       <c r="Z5" t="n">
-        <v>0.0789</v>
+        <v>-0.18</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2466</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0555</v>
+        <v>-0.0587</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0789</v>
+        <v>-0.0639</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0029</v>
+        <v>-0.0404</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0098</v>
+        <v>-0.0323</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.027</v>
+        <v>-0.0561</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.028</v>
+        <v>0.0231</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.2696</v>
+        <v>0.2245</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.94</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>7.42</v>
+        <v>9.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0072</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.076617</v>
+        <v>0.06382</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.124439</v>
+        <v>1.153469</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.44</v>
+        <v>15.35</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
@@ -2275,25 +2279,25 @@
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.139753</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.093605</v>
+        <v>1.139753</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.944926</v>
+        <v>0.845253</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.078274</v>
+        <v>0.06454500000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.9788</v>
+        <v>0.9888</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2339,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
         <v>0</v>
@@ -2348,16 +2352,16 @@
         <v>1</v>
       </c>
       <c r="BN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="BP5" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.6565656565656566</v>
+        <v>0.3535353535353535</v>
       </c>
       <c r="BR5" t="n">
         <v>1</v>
@@ -2379,43 +2383,43 @@
         </is>
       </c>
       <c r="BW5" t="n">
-        <v>0.6352</v>
+        <v>0.6584</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.6844</v>
+        <v>0.6328</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.5239</v>
+        <v>0.5611</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.4548554898040938</v>
+        <v>0.4382483987992929</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.6200542770327276</v>
+        <v>0.5747077669640731</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.6380981273485689</v>
+        <v>0.3957849185932791</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.6380981273485689</v>
+        <v>0.5747077669640731</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.5943396226415094</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.6122448979591837</v>
+        <v>0.4436619718309859</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.5930735930735931</v>
+        <v>0.6509433962264151</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.8782051282051282</v>
+        <v>0.4339622641509434</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.7884615384615384</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.2847222222222222</v>
+        <v>0.07843137254901961</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2432,7 +2436,7 @@
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>RV_RANK</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="CN5" t="n">
@@ -2442,73 +2446,41 @@
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.5376</v>
+        <v>0.5538</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.5376</v>
+        <v>0.5538</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CX5" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CY5" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.056 | spread_35_20: esp=+0.003 | spread_45_25: esp=+0.010 | spread_45_15: esp=+0.027</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>vetado_esperanca_historica</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.079 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="DB5" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
-        </is>
-      </c>
-      <c r="DC5" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DD5" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DE5" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
+          <t>vetada</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2517,16 +2489,16 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Alerta CALL (VETADA)</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2543,53 +2515,53 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1253</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5263</v>
+        <v>0.6512</v>
       </c>
       <c r="N6" t="n">
-        <v>0.15</v>
+        <v>0.0702</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5541</v>
+        <v>0.2666</v>
       </c>
       <c r="P6" t="n">
         <v>-0.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0184</v>
+        <v>-0.058</v>
       </c>
       <c r="R6" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0692</v>
+        <v>-0.0722</v>
       </c>
       <c r="T6" t="n">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0577</v>
+        <v>-0.1354</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0503</v>
+        <v>0.0178</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2598,7 +2570,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2613,43 +2585,43 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0587</v>
+        <v>-0.1364</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0639</v>
+        <v>-0.1831</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0404</v>
+        <v>-0.0723</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.0323</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0561</v>
+        <v>-0.1207</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0242</v>
+        <v>0.012</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2654</v>
+        <v>0.2936</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.609999999999999</v>
+        <v>18.15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>9.09</v>
+        <v>18.66</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.0072</v>
+        <v>-0.0128</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.064306</v>
+        <v>0.049109</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.155225</v>
+        <v>1.141632</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.52</v>
+        <v>14.16</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
@@ -2664,13 +2636,13 @@
         <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.139753</v>
+        <v>1.114435</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.139753</v>
+        <v>1.115445</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.845253</v>
+        <v>0.876011</v>
       </c>
       <c r="AV6" t="n">
         <v>1</v>
@@ -2679,10 +2651,10 @@
         <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.067536</v>
+        <v>0.033483</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.9522</v>
+        <v>1.4667</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -2701,24 +2673,20 @@
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BI6" t="n">
@@ -2740,78 +2708,78 @@
         <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BP6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.3535353535353535</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="BR6" t="n">
         <v>1</v>
       </c>
       <c r="BS6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>exec_bilateral</t>
+          <t>exec_alta</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>expansion_moderada</t>
+          <t>exec_expansion_har</t>
         </is>
       </c>
       <c r="BW6" t="n">
-        <v>0.6584</v>
+        <v>0.6368</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.6328</v>
+        <v>0.6546</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.5611</v>
+        <v>0.4917</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.4382483987992929</v>
+        <v>0.3478669257672033</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.5747077669640731</v>
+        <v>0.5742751832410374</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.3957849185932791</v>
+        <v>0.1717746127157639</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.5747077669640731</v>
+        <v>0.5742751832410374</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.5943396226415094</v>
+        <v>0.5181818181818182</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.4436619718309859</v>
+        <v>0.4956521739130435</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.6509433962264151</v>
+        <v>0.5811965811965812</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.4339622641509434</v>
+        <v>0.4503311258278146</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.07843137254901961</v>
+        <v>0</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>expansao_moderada_sem_exec_forte</t>
+          <t>har_fallback_aprovado_expansao</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
@@ -2821,23 +2789,23 @@
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="CN6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>0.6027397260273972</v>
       </c>
       <c r="CP6" t="n">
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.5419</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.5419</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="CS6" t="n">
         <v>1</v>
@@ -2866,359 +2834,6 @@
       <c r="DC6" t="inlineStr"/>
       <c r="DD6" t="inlineStr"/>
       <c r="DE6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>v5.5_executor_diario</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>KLBN11</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Compra CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>aprovado_executor_nivel_A</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>43</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.0945</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.6512</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.07140000000000001</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.2667</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.0612</v>
-      </c>
-      <c r="R7" t="n">
-        <v>435</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.0755</v>
-      </c>
-      <c r="T7" t="n">
-        <v>298</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.1354</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>nenhuma</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>esperanca</t>
-        </is>
-      </c>
-      <c r="Z7" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.1364</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.1831</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.0723</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.08649999999999999</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-0.1207</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.1526</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>17.68</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>18.09</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-0.0128</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.027719</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.183489</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.114435</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.115445</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.876011</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0.028043</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0.9885</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>expansao</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>39</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>66</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0.3434343434343434</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>exec_alta</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>exec_expansion_har</t>
-        </is>
-      </c>
-      <c r="BW7" t="n">
-        <v>0.6368</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0.6546</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0.4917</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0.3478669257672033</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.5742751832410374</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0.1717746127157639</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>0.5742751832410374</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>0.5181818181818182</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>0.4956521739130435</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0.5811965811965812</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0.4503311258278146</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK7" t="inlineStr">
-        <is>
-          <t>har_fallback_aprovado_expansao</t>
-        </is>
-      </c>
-      <c r="CL7" t="inlineStr">
-        <is>
-          <t>threshold_por_ativo</t>
-        </is>
-      </c>
-      <c r="CM7" t="inlineStr">
-        <is>
-          <t>HAR</t>
-        </is>
-      </c>
-      <c r="CN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0.6027397260273972</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>0.5202</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>0.5202</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT7" t="inlineStr">
-        <is>
-          <t>vetado_esperanca_historica</t>
-        </is>
-      </c>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="inlineStr"/>
-      <c r="CW7" t="inlineStr"/>
-      <c r="CX7" t="inlineStr"/>
-      <c r="CY7" t="inlineStr"/>
-      <c r="CZ7" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="DA7" t="inlineStr">
-        <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="DB7" t="inlineStr"/>
-      <c r="DC7" t="inlineStr"/>
-      <c r="DD7" t="inlineStr"/>
-      <c r="DE7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3324,7 +2939,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3333,61 +2948,61 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Compra CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>spread_45_15</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
-        <v>13.61</v>
+        <v>20.7</v>
       </c>
       <c r="I2" t="n">
-        <v>13.72</v>
+        <v>21.6</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.35</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.037</v>
+        <v>-0.207</v>
       </c>
       <c r="L2" t="n">
-        <v>0.425</v>
+        <v>0.49</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.255</v>
+        <v>-0.32</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.058</v>
+        <v>0.515</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0025</v>
+        <v>-0.0337</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>razao=0.06 &lt; 0.6 | M=-0.04 — ativo foi contra, tese falhou</t>
+          <t>razao=0.52 &lt; 0.6 | M=-0.21 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3396,61 +3011,61 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46211</v>
+        <v>46221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>10.35</v>
+        <v>13.61</v>
       </c>
       <c r="I3" t="n">
-        <v>11.03</v>
+        <v>13.74</v>
       </c>
       <c r="J3" t="n">
-        <v>6.57</v>
+        <v>0.96</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.45</v>
+        <v>-0.016</v>
       </c>
       <c r="L3" t="n">
-        <v>0.49</v>
+        <v>0.425</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.32</v>
+        <v>-0.255</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.067</v>
+        <v>0.368</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0042</v>
+        <v>0.015</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>razao=0.07 &lt; 0.6 | M=-0.45 — ativo foi contra, tese falhou</t>
+          <t>razao=0.37 &lt; 0.6 | M=-0.02 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3459,7 +3074,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46228</v>
+        <v>46211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3472,22 +3087,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>9.359999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="I4" t="n">
-        <v>9.57</v>
+        <v>11.23</v>
       </c>
       <c r="J4" t="n">
-        <v>2.24</v>
+        <v>8.5</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.662</v>
       </c>
       <c r="L4" t="n">
         <v>0.49</v>
@@ -3499,21 +3114,21 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.53</v>
+        <v>0.527</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0344</v>
+        <v>0.0323</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>razao=0.53 &lt; 0.6 | M=-0.01 — ativo foi contra, tese falhou</t>
+          <t>razao=0.53 &lt; 0.6 | M=-0.66 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLCE3</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3522,7 +3137,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46209</v>
+        <v>46228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3535,22 +3150,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>12.8</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>13.38</v>
+        <v>9.74</v>
       </c>
       <c r="J5" t="n">
-        <v>4.53</v>
+        <v>4.06</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.427</v>
+        <v>-0.189</v>
       </c>
       <c r="L5" t="n">
         <v>0.49</v>
@@ -3562,21 +3177,21 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.33</v>
+        <v>0.111</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0144</v>
+        <v>-0.0071</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>razao=0.33 &lt; 0.6 | M=-0.43 — ativo foi contra, tese falhou</t>
+          <t>razao=0.11 &lt; 0.6 | M=-0.19 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>SLCE3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3585,7 +3200,7 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3594,124 +3209,124 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>spread_45_15</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>73.15000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="I6" t="n">
-        <v>75.69</v>
+        <v>13.31</v>
       </c>
       <c r="J6" t="n">
-        <v>3.47</v>
+        <v>3.98</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.239</v>
+        <v>-0.368</v>
       </c>
       <c r="L6" t="n">
-        <v>0.425</v>
+        <v>0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.255</v>
+        <v>-0.32</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.347</v>
+        <v>0.217</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0165</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>razao=0.35 &lt; 0.6 | M=-0.24 — ativo foi contra, tese falhou</t>
+          <t>razao=0.22 &lt; 0.6 | M=-0.37 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SINAL INVERTIDO (fim horizonte)</t>
+          <t>SINAL FRACO (reverter)</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>naked_30</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>13.88</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>11.84</v>
+        <v>75.22</v>
       </c>
       <c r="J7" t="n">
-        <v>-14.7</v>
+        <v>2.83</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.387</v>
+        <v>-0.168</v>
       </c>
       <c r="L7" t="n">
-        <v>0.751</v>
+        <v>0.425</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.181</v>
+        <v>-0.255</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.431</v>
+        <v>0.371</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1016</v>
+        <v>0.017</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Modelo virou PUT mas restam 5d — previsão cobre 20d, maioria pós-vencimento | M=-1.39 | razao=1.43</t>
+          <t>razao=0.37 &lt; 0.6 | M=-0.17 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MANTER</t>
+          <t>SINAL INVERTIDO (fim horizonte)</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46230</v>
+        <v>46209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3720,52 +3335,52 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>naked_30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>18.71</v>
+        <v>13.88</v>
       </c>
       <c r="I8" t="n">
-        <v>18.71</v>
+        <v>11.92</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-14.12</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.167</v>
+        <v>-1.386</v>
       </c>
       <c r="L8" t="n">
-        <v>0.49</v>
+        <v>0.751</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.32</v>
+        <v>-0.181</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.116</v>
+        <v>1.129</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0443</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>M=-0.17 | razao=1.12 | 0/20d</t>
+          <t>Modelo virou PUT mas restam 4d — previsão cobre 20d, maioria pós-vencimento | M=-1.39 | razao=1.13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3778,7 +3393,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3787,48 +3402,48 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8100000000000001</v>
+        <v>18.71</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8100000000000001</v>
+        <v>18.87</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="K9" t="n">
-        <v>0.242</v>
+        <v>-0.034</v>
       </c>
       <c r="L9" t="n">
         <v>0.49</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.248</v>
+        <v>-0.32</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.766</v>
+        <v>1.542</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2035</v>
+        <v>0.059</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>M=0.24 | razao=1.77 | 0/20d</t>
+          <t>M=-0.03 | razao=1.54 | 1/20d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3837,7 +3452,7 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3856,35 +3471,35 @@
         <v>19</v>
       </c>
       <c r="H10" t="n">
-        <v>20.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>21.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>2.46</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.025</v>
+        <v>0.238</v>
       </c>
       <c r="L10" t="n">
         <v>0.49</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.32</v>
+        <v>-0.252</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.794</v>
+        <v>1.769</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0526</v>
+        <v>-0.1965</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>M=-0.03 | razao=0.79 | 1/20d</t>
+          <t>M=0.24 | razao=1.77 | 1/20d</t>
         </is>
       </c>
     </row>
@@ -3913,22 +3528,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
         <v>11.4</v>
       </c>
       <c r="I11" t="n">
-        <v>11.46</v>
+        <v>11.61</v>
       </c>
       <c r="J11" t="n">
-        <v>0.53</v>
+        <v>1.84</v>
       </c>
       <c r="K11" t="n">
-        <v>0.15</v>
+        <v>0.004</v>
       </c>
       <c r="L11" t="n">
         <v>0.49</v>
@@ -3940,14 +3555,14 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.846</v>
+        <v>1.252</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1048</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>M=0.15 | razao=1.85 | 1/20d</t>
+          <t>M=0.00 | razao=1.25 | 2/20d</t>
         </is>
       </c>
     </row>
@@ -3976,22 +3591,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
         <v>44.64</v>
       </c>
       <c r="I12" t="n">
-        <v>46.05</v>
+        <v>46.48</v>
       </c>
       <c r="J12" t="n">
-        <v>3.16</v>
+        <v>4.12</v>
       </c>
       <c r="K12" t="n">
-        <v>0.23</v>
+        <v>0.347</v>
       </c>
       <c r="L12" t="n">
         <v>0.751</v>
@@ -4003,14 +3618,14 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.888</v>
+        <v>0.911</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0507</v>
+        <v>0.05</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>M=0.23 | razao=0.89 | 7/20d</t>
+          <t>M=0.35 | razao=0.91 | 8/20d</t>
         </is>
       </c>
     </row>
@@ -4039,41 +3654,41 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
         <v>5.27</v>
       </c>
       <c r="I13" t="n">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="K13" t="n">
-        <v>0.211</v>
+        <v>0.007</v>
       </c>
       <c r="L13" t="n">
         <v>0.49</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.279</v>
+        <v>-0.32</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.375</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.0716</v>
+        <v>-0.0423</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>M=0.21 | razao=1.37 | 0/20d</t>
+          <t>M=0.01 | razao=0.81 | 1/20d</t>
         </is>
       </c>
     </row>
@@ -4102,41 +3717,41 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H14" t="n">
         <v>7.94</v>
       </c>
       <c r="I14" t="n">
-        <v>7.94</v>
+        <v>8.08</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="K14" t="n">
-        <v>0.21</v>
+        <v>0.067</v>
       </c>
       <c r="L14" t="n">
         <v>0.49</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.28</v>
+        <v>-0.32</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.979</v>
+        <v>0.666</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0766</v>
+        <v>-0.0512</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>M=0.21 | razao=0.98 | 0/20d</t>
+          <t>M=0.07 | razao=0.67 | 1/20d</t>
         </is>
       </c>
     </row>
@@ -4151,7 +3766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4273,10 +3888,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3545</v>
+        <v>0.3162</v>
       </c>
       <c r="D2" t="n">
-        <v>1.118375</v>
+        <v>1.116637</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4338,17 +3953,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.327 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.328 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.0142</v>
+        <v>0.0137</v>
       </c>
       <c r="S2" t="n">
-        <v>22.5</v>
+        <v>21.7</v>
       </c>
       <c r="T2" t="n">
-        <v>25.2</v>
+        <v>24.3</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -4368,10 +3983,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2355</v>
+        <v>0.2154</v>
       </c>
       <c r="D3" t="n">
-        <v>1.120573</v>
+        <v>1.162918</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4379,7 +3994,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.6405</v>
+        <v>0.6505</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4433,14 +4048,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.813 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.824 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.0413</v>
+        <v>0.0398</v>
       </c>
       <c r="S3" t="n">
-        <v>65.59999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="T3" t="n">
         <v>73.5</v>
@@ -4463,10 +4078,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.324</v>
+        <v>0.3289</v>
       </c>
       <c r="D4" t="n">
-        <v>1.101101</v>
+        <v>1.098742</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4532,13 +4147,13 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.0187</v>
+        <v>0.0188</v>
       </c>
       <c r="S4" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T4" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -4549,19 +4164,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL (VETADA)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2696</v>
+        <v>0.2245</v>
       </c>
       <c r="D5" t="n">
-        <v>1.124439</v>
+        <v>1.153469</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4569,71 +4184,39 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.0565</v>
+        <v>-0.0577</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>vetada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
+          <t>VETADA — esperança histórica insuficiente</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.079 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.028</v>
+        <v>0.0231</v>
       </c>
       <c r="S5" t="n">
-        <v>44.4</v>
+        <v>36.7</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -4644,19 +4227,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alerta CALL (VETADA)</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2654</v>
+        <v>0.2936</v>
       </c>
       <c r="D6" t="n">
-        <v>1.155225</v>
+        <v>1.141632</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4664,7 +4247,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-0.0577</v>
+        <v>-0.1354</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4690,78 +4273,15 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.0242</v>
+        <v>0.012</v>
       </c>
       <c r="S6" t="n">
-        <v>38.4</v>
+        <v>19</v>
       </c>
       <c r="T6" t="n">
-        <v>44.4</v>
+        <v>21.7</v>
       </c>
       <c r="U6" t="inlineStr">
-        <is>
-          <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KLBN11</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Compra CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.1526</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.183489</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.1354</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S7" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="T7" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="U7" t="inlineStr">
         <is>
           <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
         </is>
@@ -5325,7 +4845,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5358,7 +4878,7 @@
         <v>56</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1231</v>
+        <v>0.1228</v>
       </c>
       <c r="L2" t="n">
         <v>0.2321</v>
@@ -5376,13 +4896,13 @@
         <v>-0.0182</v>
       </c>
       <c r="Q2" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R2" t="n">
         <v>0.032</v>
       </c>
       <c r="S2" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T2" t="n">
         <v>-0.0922</v>
@@ -5427,28 +4947,28 @@
         <v>-0.153</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0176</v>
+        <v>0.0169</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4705</v>
+        <v>0.4342</v>
       </c>
       <c r="AH2" t="n">
-        <v>41.01</v>
+        <v>41.26</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.0114</v>
+        <v>-0.0113</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.040746</v>
+        <v>0.0468</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.954164</v>
+        <v>0.939721</v>
       </c>
       <c r="AM2" t="n">
-        <v>-4.58</v>
+        <v>-6.03</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -5478,10 +4998,10 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.049085</v>
+        <v>0.047078</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.9941</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -5633,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.4978</v>
+        <v>0.5215</v>
       </c>
       <c r="CQ2" t="n">
         <v>0</v>
@@ -5662,7 +5182,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5692,13 +5212,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0925</v>
+        <v>0.0945</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7143</v>
+        <v>0.6977</v>
       </c>
       <c r="M3" t="n">
         <v>0.4884</v>
@@ -5713,19 +5233,19 @@
         <v>-0.026</v>
       </c>
       <c r="Q3" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="R3" t="n">
         <v>0.0979</v>
       </c>
       <c r="S3" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T3" t="n">
-        <v>0.334</v>
+        <v>0.322</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0892</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -5739,49 +5259,49 @@
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>0.4499</v>
+        <v>0.432</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.406</v>
+        <v>1.3501</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.333</v>
+        <v>0.321</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4499</v>
+        <v>0.432</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1151</v>
+        <v>0.1095</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1408</v>
+        <v>0.133</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2303</v>
+        <v>0.219</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0211</v>
+        <v>0.0221</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0951</v>
+        <v>0.1206</v>
       </c>
       <c r="AH3" t="n">
-        <v>43.15</v>
+        <v>41.86</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0309</v>
+        <v>0.0304</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.106508</v>
+        <v>0.093568</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.166789</v>
+        <v>1.148604</v>
       </c>
       <c r="AM3" t="n">
-        <v>16.68</v>
+        <v>14.86</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -5811,10 +5331,10 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.058923</v>
+        <v>0.061793</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.8076</v>
+        <v>1.5142</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -5962,7 +5482,7 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.6247</v>
+        <v>0.5903</v>
       </c>
       <c r="CQ3" t="n">
         <v>0</v>
@@ -5991,7 +5511,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -6005,7 +5525,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -6039,16 +5559,16 @@
         <v>0.0392</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2137</v>
+        <v>0.2067</v>
       </c>
       <c r="Q4" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3148</v>
+        <v>0.3142</v>
       </c>
       <c r="S4" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="T4" t="n">
         <v>0.1725</v>
@@ -6089,13 +5609,13 @@
         <v>0.3812</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0133</v>
+        <v>0.0128</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.398</v>
+        <v>0.3575</v>
       </c>
       <c r="AH4" t="n">
-        <v>42.69</v>
+        <v>42.9</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -6104,13 +5624,13 @@
         <v>0.0011</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.004363</v>
+        <v>0.011089</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.006132</v>
+        <v>1.03149</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.61</v>
+        <v>3.15</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -6140,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.037154</v>
+        <v>0.035645</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1174</v>
+        <v>0.3111</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -6295,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.4506</v>
+        <v>0.4781</v>
       </c>
       <c r="CQ4" t="n">
         <v>0</v>
@@ -6324,7 +5844,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6357,7 +5877,7 @@
         <v>165</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3626</v>
+        <v>0.3618</v>
       </c>
       <c r="L5" t="n">
         <v>0.7091</v>
@@ -6372,16 +5892,16 @@
         <v>0.7824</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2889</v>
+        <v>0.2858</v>
       </c>
       <c r="Q5" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5921</v>
+        <v>0.577</v>
       </c>
       <c r="S5" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="T5" t="n">
         <v>0.642</v>
@@ -6422,28 +5942,28 @@
         <v>0.2479</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0171</v>
+        <v>0.0164</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5454</v>
       </c>
       <c r="AH5" t="n">
-        <v>75.69</v>
+        <v>75.22</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2328</v>
+        <v>0.2323</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.016544</v>
+        <v>0.017021</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.933643</v>
+        <v>0.943889</v>
       </c>
       <c r="AM5" t="n">
-        <v>-6.64</v>
+        <v>-5.61</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -6473,10 +5993,10 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.047622</v>
+        <v>0.045822</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.3474</v>
+        <v>0.3714</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -6628,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.4203</v>
+        <v>0.4292</v>
       </c>
       <c r="CQ5" t="n">
         <v>0</v>
@@ -6657,7 +6177,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6691,40 +6211,40 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4066</v>
+        <v>0.4079</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6757</v>
+        <v>0.6774</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3532</v>
+        <v>0.3564</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9105</v>
+        <v>0.9012</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1583</v>
+        <v>0.1617</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1215</v>
+        <v>0.1232</v>
       </c>
       <c r="Q6" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1619</v>
+        <v>0.1624</v>
       </c>
       <c r="S6" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="T6" t="n">
         <v>0.245</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0491</v>
+        <v>0.0489</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -6738,49 +6258,49 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>0.3273</v>
+        <v>0.3283</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.0229</v>
+        <v>1.0258</v>
       </c>
       <c r="AA6" t="n">
         <v>0.244</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3273</v>
+        <v>0.3283</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0692</v>
+        <v>0.0706</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0905</v>
+        <v>0.0919</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1438</v>
+        <v>0.1461</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0142</v>
+        <v>0.0137</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.3545</v>
+        <v>0.3162</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.71</v>
+        <v>18.87</v>
       </c>
       <c r="AI6" t="n">
-        <v>19.33</v>
+        <v>19.47</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.0999</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.044322</v>
+        <v>0.059038</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.118375</v>
+        <v>1.116637</v>
       </c>
       <c r="AM6" t="n">
-        <v>11.84</v>
+        <v>11.66</v>
       </c>
       <c r="AN6" t="n">
         <v>1</v>
@@ -6810,10 +6330,10 @@
         <v>1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.039722</v>
+        <v>0.038286</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.1158</v>
+        <v>1.542</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -6965,10 +6485,10 @@
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.5347</v>
+        <v>0.585</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.5347</v>
+        <v>0.585</v>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
@@ -6997,12 +6517,12 @@
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.244 | spread_35_20: esp=+0.069 | spread_45_25: esp=+0.090 | spread_45_15: esp=+0.144</t>
+          <t>naked_30: esp=+0.244 | spread_35_20: esp=+0.071 | spread_45_25: esp=+0.092 | spread_45_15: esp=+0.146</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.327 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Call delta~45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.328 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
@@ -7038,7 +6558,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7064,14 +6584,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>59</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1297</v>
+        <v>0.1294</v>
       </c>
       <c r="L7" t="n">
         <v>0.3729</v>
@@ -7089,13 +6609,13 @@
         <v>0.0303</v>
       </c>
       <c r="Q7" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R7" t="n">
         <v>0.0619</v>
       </c>
       <c r="S7" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="T7" t="n">
         <v>0.0128</v>
@@ -7140,13 +6660,13 @@
         <v>-0.0296</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0219</v>
+        <v>0.0211</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.3961</v>
+        <v>0.3656</v>
       </c>
       <c r="AH7" t="n">
-        <v>15.72</v>
+        <v>15.93</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -7155,13 +6675,13 @@
         <v>0.0017</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.029842</v>
+        <v>0.046149</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.017051</v>
+        <v>0.99451</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.71</v>
+        <v>-0.55</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -7191,10 +6711,10 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.061137</v>
+        <v>0.058995</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.4881</v>
+        <v>0.7822</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -7204,7 +6724,7 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -7346,7 +6866,7 @@
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.4321</v>
+        <v>0.4676</v>
       </c>
       <c r="CQ7" t="n">
         <v>0</v>
@@ -7375,7 +6895,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -7405,13 +6925,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3165</v>
+        <v>0.318</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4514</v>
+        <v>0.4483</v>
       </c>
       <c r="M8" t="n">
         <v>0.3046</v>
@@ -7426,19 +6946,19 @@
         <v>-0.0526</v>
       </c>
       <c r="Q8" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R8" t="n">
         <v>-0.0404</v>
       </c>
       <c r="S8" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1514</v>
+        <v>0.1491</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0487</v>
+        <v>0.0485</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7452,49 +6972,49 @@
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
-        <v>0.1681</v>
+        <v>0.1647</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5252</v>
+        <v>0.5148</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1504</v>
+        <v>0.1481</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1681</v>
+        <v>0.1647</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0215</v>
+        <v>0.0205</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0102</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0423</v>
+        <v>0.0402</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0332</v>
+        <v>0.0319</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.3404</v>
+        <v>0.2815</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.83</v>
+        <v>4.88</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0479</v>
+        <v>0.0474</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.007321</v>
+        <v>0.008691000000000001</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.113949</v>
+        <v>1.120849</v>
       </c>
       <c r="AM8" t="n">
-        <v>11.39</v>
+        <v>12.08</v>
       </c>
       <c r="AN8" t="n">
         <v>1</v>
@@ -7524,10 +7044,10 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.09273000000000001</v>
+        <v>0.088973</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0789</v>
+        <v>0.0977</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -7679,7 +7199,7 @@
         <v>1</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.437</v>
+        <v>0.4507</v>
       </c>
       <c r="CQ8" t="n">
         <v>0</v>
@@ -7708,7 +7228,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -7741,7 +7261,7 @@
         <v>73</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1604</v>
+        <v>0.1601</v>
       </c>
       <c r="L9" t="n">
         <v>0.4384</v>
@@ -7759,13 +7279,13 @@
         <v>0.0086</v>
       </c>
       <c r="Q9" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R9" t="n">
         <v>0.0305</v>
       </c>
       <c r="S9" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="T9" t="n">
         <v>0.1722</v>
@@ -7806,13 +7326,13 @@
         <v>-0.0119</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0204</v>
+        <v>0.0197</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.5179</v>
+        <v>0.4819</v>
       </c>
       <c r="AH9" t="n">
-        <v>46.05</v>
+        <v>46.48</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -7821,13 +7341,13 @@
         <v>0.0276</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.05068</v>
+        <v>0.050004</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.956386</v>
+        <v>0.959045</v>
       </c>
       <c r="AM9" t="n">
-        <v>-4.36</v>
+        <v>-4.1</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -7857,10 +7377,10 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.057052</v>
+        <v>0.054891</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.8883</v>
+        <v>0.911</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -8012,7 +7532,7 @@
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.5003</v>
+        <v>0.5098</v>
       </c>
       <c r="CQ9" t="n">
         <v>0</v>
@@ -8041,7 +7561,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -8074,7 +7594,7 @@
         <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0352</v>
+        <v>0.0351</v>
       </c>
       <c r="L10" t="n">
         <v>0.6875</v>
@@ -8089,16 +7609,16 @@
         <v>0.2055</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1621</v>
+        <v>0.1619</v>
       </c>
       <c r="Q10" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2786</v>
+        <v>0.2615</v>
       </c>
       <c r="S10" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="T10" t="n">
         <v>0.2173</v>
@@ -8139,13 +7659,13 @@
         <v>0.2834</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0153</v>
+        <v>0.0146</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5059</v>
+        <v>0.4604</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.72</v>
+        <v>13.74</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -8154,13 +7674,13 @@
         <v>0.0076</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.002468</v>
+        <v>0.01497</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.980554</v>
+        <v>0.987298</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1.94</v>
+        <v>-1.27</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -8190,10 +7710,10 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.042579</v>
+        <v>0.040686</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.058</v>
+        <v>0.3679</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -8345,7 +7865,7 @@
         <v>1</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.4006</v>
+        <v>0.4406</v>
       </c>
       <c r="CQ10" t="n">
         <v>0</v>
@@ -8374,7 +7894,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -8407,7 +7927,7 @@
         <v>125</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2747</v>
+        <v>0.2741</v>
       </c>
       <c r="L11" t="n">
         <v>0.672</v>
@@ -8425,7 +7945,7 @@
         <v>0.169</v>
       </c>
       <c r="Q11" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R11" t="n">
         <v>0.249</v>
@@ -8472,28 +7992,28 @@
         <v>0.165</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0159</v>
+        <v>0.0154</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.3596</v>
+        <v>0.3252</v>
       </c>
       <c r="AH11" t="n">
-        <v>24.48</v>
+        <v>24.8</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0653</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.128749</v>
+        <v>0.147852</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.880702</v>
+        <v>0.891917</v>
       </c>
       <c r="AM11" t="n">
-        <v>-11.93</v>
+        <v>-10.81</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -8523,13 +8043,13 @@
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.04446</v>
+        <v>0.042967</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.8959</v>
+        <v>3.441</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -8678,7 +8198,7 @@
         <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.5802</v>
+        <v>0.587</v>
       </c>
       <c r="CQ11" t="n">
         <v>0</v>
@@ -8707,7 +8227,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -8744,13 +8264,13 @@
         <v>57</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1253</v>
+        <v>0.125</v>
       </c>
       <c r="L12" t="n">
         <v>0.5263</v>
       </c>
       <c r="M12" t="n">
-        <v>0.15</v>
+        <v>0.1475</v>
       </c>
       <c r="N12" t="n">
         <v>0.5541</v>
@@ -8762,7 +8282,7 @@
         <v>-0.0184</v>
       </c>
       <c r="Q12" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R12" t="n">
         <v>-0.0692</v>
@@ -8774,7 +8294,7 @@
         <v>-0.0577</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0503</v>
+        <v>0.0499</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8813,13 +8333,13 @@
         <v>-0.0561</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0242</v>
+        <v>0.0231</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.2654</v>
+        <v>0.2245</v>
       </c>
       <c r="AH12" t="n">
-        <v>8.609999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AI12" t="n">
         <v>9.09</v>
@@ -8828,13 +8348,13 @@
         <v>-0.0072</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.064306</v>
+        <v>0.06382</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.155225</v>
+        <v>1.153469</v>
       </c>
       <c r="AM12" t="n">
-        <v>15.52</v>
+        <v>15.35</v>
       </c>
       <c r="AN12" t="n">
         <v>1</v>
@@ -8864,10 +8384,10 @@
         <v>1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.067536</v>
+        <v>0.06454500000000001</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.9522</v>
+        <v>0.9888</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -9019,10 +8539,10 @@
         <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.5419</v>
+        <v>0.5538</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.5419</v>
+        <v>0.5538</v>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
@@ -9060,7 +8580,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -9093,7 +8613,7 @@
         <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0418</v>
+        <v>0.0417</v>
       </c>
       <c r="L13" t="n">
         <v>0.5789</v>
@@ -9111,13 +8631,13 @@
         <v>-0.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R13" t="n">
         <v>-0.1221</v>
       </c>
       <c r="S13" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="T13" t="n">
         <v>-0.092</v>
@@ -9162,13 +8682,13 @@
         <v>-0.008</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0225</v>
+        <v>0.0217</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.3516</v>
+        <v>0.3084</v>
       </c>
       <c r="AH13" t="n">
-        <v>13.73</v>
+        <v>13.83</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -9177,13 +8697,13 @@
         <v>-0.0038</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.02987</v>
+        <v>-0.012007</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.000763</v>
+        <v>1.001307</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -9213,10 +8733,10 @@
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.062885</v>
+        <v>0.06044</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.475</v>
+        <v>0.1987</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -9364,7 +8884,7 @@
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.5051</v>
+        <v>0.4861</v>
       </c>
       <c r="CQ13" t="n">
         <v>0</v>
@@ -9393,7 +8913,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -9426,7 +8946,7 @@
         <v>106</v>
       </c>
       <c r="K14" t="n">
-        <v>0.233</v>
+        <v>0.2325</v>
       </c>
       <c r="L14" t="n">
         <v>0.5755</v>
@@ -9441,16 +8961,16 @@
         <v>0.0302</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0262</v>
+        <v>0.0323</v>
       </c>
       <c r="Q14" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0626</v>
+        <v>0.0675</v>
       </c>
       <c r="S14" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="T14" t="n">
         <v>0.0343</v>
@@ -9460,24 +8980,20 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>risco</t>
-        </is>
-      </c>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>-0.18</v>
+        <v>0.0584</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>0.1826</v>
       </c>
       <c r="AA14" t="n">
         <v>0.0333</v>
@@ -9495,13 +9011,13 @@
         <v>0.0311</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0148</v>
+        <v>0.0144</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.6198</v>
+        <v>0.5859</v>
       </c>
       <c r="AH14" t="n">
-        <v>40.54</v>
+        <v>40.92</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -9510,13 +9026,13 @@
         <v>0.008</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.021091</v>
+        <v>0.02066</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.922404</v>
+        <v>0.965649</v>
       </c>
       <c r="AM14" t="n">
-        <v>-7.76</v>
+        <v>-3.44</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -9546,10 +9062,10 @@
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.041422</v>
+        <v>0.040163</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.5092</v>
+        <v>0.5144</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -9697,7 +9213,7 @@
         <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.2924</v>
+        <v>0.2997</v>
       </c>
       <c r="CQ14" t="n">
         <v>0</v>
@@ -9726,7 +9242,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -9756,13 +9272,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2637</v>
+        <v>0.2654</v>
       </c>
       <c r="L15" t="n">
-        <v>0.775</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>0.7131</v>
@@ -9771,25 +9287,25 @@
         <v>2.0772</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1777</v>
+        <v>1.1709</v>
       </c>
       <c r="P15" t="n">
         <v>0.3561</v>
       </c>
       <c r="Q15" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R15" t="n">
         <v>0.5679999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4573</v>
+        <v>1.4438</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1849</v>
+        <v>0.1846</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9803,49 +9319,49 @@
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>1.6235</v>
+        <v>1.6075</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.0736</v>
+        <v>5.0234</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.4563</v>
+        <v>1.4428</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6235</v>
+        <v>1.6075</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.208</v>
+        <v>0.2052</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.22</v>
+        <v>0.2166</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.3868</v>
+        <v>0.3815</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.038</v>
+        <v>0.0368</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2204</v>
+        <v>0.2099</v>
       </c>
       <c r="AH15" t="n">
-        <v>10.19</v>
+        <v>10.37</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.3843</v>
+        <v>0.3831</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.100953</v>
+        <v>-0.084782</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.05102</v>
+        <v>1.067974</v>
       </c>
       <c r="AM15" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -9875,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.105958</v>
+        <v>0.10275</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.9528</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -10030,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5211</v>
       </c>
       <c r="CQ15" t="n">
         <v>0</v>
@@ -10059,7 +9575,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -10092,7 +9608,7 @@
         <v>68</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1495</v>
+        <v>0.1491</v>
       </c>
       <c r="L16" t="n">
         <v>0.2794</v>
@@ -10110,13 +9626,13 @@
         <v>0.09379999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R16" t="n">
         <v>0.1492</v>
       </c>
       <c r="S16" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0988</v>
@@ -10161,37 +9677,37 @@
         <v>-0.1003</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.03</v>
+        <v>0.0288</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.3769</v>
+        <v>0.3327</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.0148</v>
+        <v>-0.0147</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.035447</v>
+        <v>-0.016082</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.067825</v>
+        <v>1.082663</v>
       </c>
       <c r="AM16" t="n">
-        <v>6.78</v>
+        <v>8.27</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -10212,10 +9728,10 @@
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.08368399999999999</v>
+        <v>0.080308</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.4236</v>
+        <v>0.2003</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -10230,7 +9746,7 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BC16" t="n">
@@ -10367,7 +9883,7 @@
         <v>1</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.4686</v>
+        <v>0.4551</v>
       </c>
       <c r="CQ16" t="n">
         <v>0</v>
@@ -10396,7 +9912,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -10422,14 +9938,14 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J17" t="n">
         <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0636</v>
       </c>
       <c r="L17" t="n">
         <v>0.3793</v>
@@ -10444,16 +9960,16 @@
         <v>0.2096</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1523</v>
+        <v>-0.1527</v>
       </c>
       <c r="Q17" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0461</v>
+        <v>0.0388</v>
       </c>
       <c r="S17" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="T17" t="n">
         <v>0.1048</v>
@@ -10498,13 +10014,13 @@
         <v>-0.0331</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.013</v>
+        <v>0.0148</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0867</v>
+        <v>0.1355</v>
       </c>
       <c r="AH17" t="n">
-        <v>15.86</v>
+        <v>16.3</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -10513,13 +10029,13 @@
         <v>0.0067</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.00313</v>
+        <v>0.029962</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.233649</v>
+        <v>1.225198</v>
       </c>
       <c r="AM17" t="n">
-        <v>23.36</v>
+        <v>22.52</v>
       </c>
       <c r="AN17" t="n">
         <v>1</v>
@@ -10549,10 +10065,10 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.036222</v>
+        <v>0.041256</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0864</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -10562,7 +10078,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -10704,7 +10220,7 @@
         <v>0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.4406</v>
+        <v>0.4948</v>
       </c>
       <c r="CQ17" t="n">
         <v>0</v>
@@ -10733,7 +10249,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -10784,13 +10300,13 @@
         <v>-0.0225</v>
       </c>
       <c r="Q18" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R18" t="n">
         <v>-0.1272</v>
       </c>
       <c r="S18" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="T18" t="n">
         <v>-0.18</v>
@@ -10819,13 +10335,13 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.0345</v>
+        <v>0.0336</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.4828</v>
+        <v>0.4605</v>
       </c>
       <c r="AH18" t="n">
-        <v>5.71</v>
+        <v>5.63</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -10834,13 +10350,13 @@
         <v>-0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.207497</v>
+        <v>0.173394</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.935972</v>
+        <v>0.914203</v>
       </c>
       <c r="AM18" t="n">
-        <v>-6.4</v>
+        <v>-8.58</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -10852,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
         <v>1.084286</v>
@@ -10870,10 +10386,10 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.09618500000000001</v>
+        <v>0.093794</v>
       </c>
       <c r="AX18" t="n">
-        <v>2.1573</v>
+        <v>1.8487</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -11021,7 +10537,7 @@
         <v>1</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.6065</v>
+        <v>0.5958</v>
       </c>
       <c r="CQ18" t="n">
         <v>0</v>
@@ -11050,7 +10566,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -11080,13 +10596,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1385</v>
+        <v>0.1404</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8571</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="M19" t="n">
         <v>0.4615</v>
@@ -11095,25 +10611,25 @@
         <v>2.3202</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1807</v>
+        <v>0.1656</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.0057</v>
+        <v>-0.0107</v>
       </c>
       <c r="Q19" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2741</v>
+        <v>0.2725</v>
       </c>
       <c r="S19" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0174</v>
+        <v>0.9987</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2471</v>
+        <v>0.2458</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -11127,49 +10643,49 @@
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>1.143</v>
+        <v>1.1201</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5718</v>
+        <v>3.5004</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.0164</v>
+        <v>0.9977</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.143</v>
+        <v>1.1201</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1143</v>
+        <v>0.1105</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.1481</v>
+        <v>0.1427</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.2274</v>
+        <v>0.2198</v>
       </c>
       <c r="AF19" t="n">
         <v>0.0135</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5416</v>
+        <v>0.5477</v>
       </c>
       <c r="AH19" t="n">
-        <v>39.95</v>
+        <v>40.48</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1409</v>
+        <v>0.1402</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.009651</v>
+        <v>-0.004004</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.893615</v>
+        <v>0.887205</v>
       </c>
       <c r="AM19" t="n">
-        <v>-10.64</v>
+        <v>-11.28</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -11199,10 +10715,10 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.037551</v>
+        <v>0.037796</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.257</v>
+        <v>0.1059</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -11350,7 +10866,7 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.3802</v>
+        <v>0.3639</v>
       </c>
       <c r="CQ19" t="n">
         <v>0</v>
@@ -11379,7 +10895,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -11405,14 +10921,14 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J20" t="n">
         <v>69</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1516</v>
+        <v>0.1513</v>
       </c>
       <c r="L20" t="n">
         <v>0.6667</v>
@@ -11430,13 +10946,13 @@
         <v>-0.0055</v>
       </c>
       <c r="Q20" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R20" t="n">
         <v>-0.0351</v>
       </c>
       <c r="S20" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="T20" t="n">
         <v>0.1439</v>
@@ -11477,13 +10993,13 @@
         <v>0.1336</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0238</v>
+        <v>0.0235</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.2616</v>
+        <v>0.2556</v>
       </c>
       <c r="AH20" t="n">
-        <v>21.21</v>
+        <v>21.6</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -11492,13 +11008,13 @@
         <v>0.0218</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.052608</v>
+        <v>-0.033714</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.019772</v>
+        <v>0.972905</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.98</v>
+        <v>-2.71</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -11528,10 +11044,10 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.06629400000000001</v>
+        <v>0.065454</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.7936</v>
+        <v>0.5151</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -11541,12 +11057,12 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
       <c r="BC20" t="n">
@@ -11683,7 +11199,7 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.4783</v>
+        <v>0.4516</v>
       </c>
       <c r="CQ20" t="n">
         <v>0</v>
@@ -11712,7 +11228,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -11738,14 +11254,14 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>volatility_gate_bloqueado:har_fallback_moderado</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>51</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1121</v>
+        <v>0.1118</v>
       </c>
       <c r="L21" t="n">
         <v>0.6863</v>
@@ -11763,13 +11279,13 @@
         <v>-0.0915</v>
       </c>
       <c r="Q21" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R21" t="n">
         <v>-0.0484</v>
       </c>
       <c r="S21" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="T21" t="n">
         <v>0.102</v>
@@ -11814,13 +11330,13 @@
         <v>0.0421</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0192</v>
+        <v>0.0191</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.1171</v>
+        <v>0.1145</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.17</v>
+        <v>18.52</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -11829,13 +11345,13 @@
         <v>0.0114</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.017976</v>
+        <v>0.050616</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.071668</v>
+        <v>1.058592</v>
       </c>
       <c r="AM21" t="n">
-        <v>7.17</v>
+        <v>5.86</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -11865,10 +11381,10 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.053681</v>
+        <v>0.053354</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.3349</v>
+        <v>0.9487</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -11878,7 +11394,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -12020,7 +11536,7 @@
         <v>1</v>
       </c>
       <c r="CP21" t="n">
-        <v>0.4839</v>
+        <v>0.5458</v>
       </c>
       <c r="CQ21" t="n">
         <v>0</v>
@@ -12049,7 +11565,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -12079,13 +11595,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K22" t="n">
-        <v>0.156</v>
+        <v>0.1579</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6056</v>
+        <v>0.5972</v>
       </c>
       <c r="M22" t="n">
         <v>0.411</v>
@@ -12100,19 +11616,19 @@
         <v>0.2538</v>
       </c>
       <c r="Q22" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R22" t="n">
         <v>0.5024999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3415</v>
+        <v>0.3343</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0813</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -12126,49 +11642,49 @@
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>0.4156</v>
+        <v>0.4054</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.2988</v>
+        <v>1.2669</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.3405</v>
+        <v>0.3333</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.4156</v>
+        <v>0.4054</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.0806</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.0862</v>
+        <v>0.0823</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.1594</v>
+        <v>0.1537</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.0224</v>
+        <v>0.0219</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.3113</v>
+        <v>0.2955</v>
       </c>
       <c r="AH22" t="n">
-        <v>11.03</v>
+        <v>11.23</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.0533</v>
+        <v>0.0528</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.004152</v>
+        <v>0.032258</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.095943</v>
+        <v>1.021625</v>
       </c>
       <c r="AM22" t="n">
-        <v>9.59</v>
+        <v>2.16</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -12198,10 +11714,10 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.062441</v>
+        <v>0.061242</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.0665</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -12349,7 +11865,7 @@
         <v>0</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.3828</v>
+        <v>0.432</v>
       </c>
       <c r="CQ22" t="n">
         <v>0</v>
@@ -12378,7 +11894,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -12404,17 +11920,17 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2901</v>
+        <v>0.2917</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4394</v>
+        <v>0.4361</v>
       </c>
       <c r="M23" t="n">
         <v>0.1714</v>
@@ -12429,16 +11945,16 @@
         <v>0.0219</v>
       </c>
       <c r="Q23" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R23" t="n">
         <v>0.1334</v>
       </c>
       <c r="S23" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0573</v>
+        <v>-0.0583</v>
       </c>
       <c r="U23" t="n">
         <v>0.0234</v>
@@ -12465,49 +11981,49 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.0583</v>
+        <v>-0.0593</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.0804</v>
+        <v>-0.0822</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.025</v>
+        <v>-0.0257</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.0435</v>
+        <v>-0.0447</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.0514</v>
+        <v>-0.053</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0174</v>
+        <v>0.0171</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.3578</v>
+        <v>0.3466</v>
       </c>
       <c r="AH23" t="n">
-        <v>28.87</v>
+        <v>29.26</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.0166</v>
+        <v>-0.017</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.032103</v>
+        <v>-0.010942</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.030443</v>
+        <v>1.007212</v>
       </c>
       <c r="AM23" t="n">
-        <v>3.04</v>
+        <v>0.72</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -12531,10 +12047,10 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.048526</v>
+        <v>0.047787</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.6616</v>
+        <v>0.229</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -12544,7 +12060,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -12686,7 +12202,7 @@
         <v>1</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.5022</v>
+        <v>0.4612</v>
       </c>
       <c r="CQ23" t="n">
         <v>0</v>
@@ -12715,7 +12231,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -12748,7 +12264,7 @@
         <v>114</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2505</v>
+        <v>0.25</v>
       </c>
       <c r="L24" t="n">
         <v>0.7193000000000001</v>
@@ -12766,7 +12282,7 @@
         <v>0.0615</v>
       </c>
       <c r="Q24" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R24" t="n">
         <v>0.3719</v>
@@ -12813,28 +12329,28 @@
         <v>0.1303</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0157</v>
+        <v>0.0151</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.3308</v>
+        <v>0.285</v>
       </c>
       <c r="AH24" t="n">
-        <v>10.67</v>
+        <v>10.76</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.0478</v>
+        <v>0.0477</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.110183</v>
+        <v>0.121291</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.090594</v>
+        <v>1.110869</v>
       </c>
       <c r="AM24" t="n">
-        <v>9.06</v>
+        <v>11.09</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
@@ -12864,10 +12380,10 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.04387</v>
+        <v>0.042033</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.5116</v>
+        <v>2.8856</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -13019,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.5934</v>
+        <v>0.6025</v>
       </c>
       <c r="CQ24" t="n">
         <v>0</v>
@@ -13048,7 +12564,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -13081,7 +12597,7 @@
         <v>54</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1187</v>
+        <v>0.1184</v>
       </c>
       <c r="L25" t="n">
         <v>0.6296</v>
@@ -13099,13 +12615,13 @@
         <v>0.0281</v>
       </c>
       <c r="Q25" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R25" t="n">
         <v>0.1041</v>
       </c>
       <c r="S25" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T25" t="n">
         <v>0.0514</v>
@@ -13150,13 +12666,13 @@
         <v>0.0626</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0204</v>
+        <v>0.0198</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.7238</v>
+        <v>0.6846</v>
       </c>
       <c r="AH25" t="n">
-        <v>30.04</v>
+        <v>30.28</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -13165,13 +12681,13 @@
         <v>0.0061</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.020328</v>
+        <v>-0.019665</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.91775</v>
+        <v>0.934184</v>
       </c>
       <c r="AM25" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.58</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -13195,16 +12711,16 @@
         <v>0.913601</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV25" t="n">
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.057026</v>
+        <v>0.055339</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.3565</v>
+        <v>0.3553</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -13356,7 +12872,7 @@
         <v>1</v>
       </c>
       <c r="CP25" t="n">
-        <v>0.3875</v>
+        <v>0.3952</v>
       </c>
       <c r="CQ25" t="n">
         <v>0</v>
@@ -13385,7 +12901,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -13418,7 +12934,7 @@
         <v>148</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3253</v>
+        <v>0.3246</v>
       </c>
       <c r="L26" t="n">
         <v>0.6351</v>
@@ -13433,16 +12949,16 @@
         <v>0.3573</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1713</v>
+        <v>0.1636</v>
       </c>
       <c r="Q26" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5121</v>
+        <v>0.5039</v>
       </c>
       <c r="S26" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T26" t="n">
         <v>0.5133</v>
@@ -13452,24 +12968,20 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>spread_45_15</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>risco</t>
-        </is>
-      </c>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>0.139</v>
+        <v>0.5847</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.5446</v>
+        <v>1.8272</v>
       </c>
       <c r="AA26" t="n">
         <v>0.5123</v>
@@ -13487,28 +12999,28 @@
         <v>0.139</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0178</v>
+        <v>0.0173</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.6041</v>
+        <v>0.5754</v>
       </c>
       <c r="AH26" t="n">
-        <v>21.75</v>
+        <v>21.55</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.167</v>
+        <v>0.1666</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.009896</v>
+        <v>0.009042</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.921866</v>
+        <v>0.931169</v>
       </c>
       <c r="AM26" t="n">
-        <v>-7.81</v>
+        <v>-6.88</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
@@ -13538,10 +13050,10 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.049811</v>
+        <v>0.048219</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.1987</v>
+        <v>0.1875</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -13693,7 +13205,7 @@
         <v>0</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.3673</v>
+        <v>0.3719</v>
       </c>
       <c r="CQ26" t="n">
         <v>0</v>
@@ -13722,7 +13234,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -13755,7 +13267,7 @@
         <v>25</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0549</v>
+        <v>0.0548</v>
       </c>
       <c r="L27" t="n">
         <v>0.08</v>
@@ -13770,16 +13282,16 @@
         <v>0.0129</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1152</v>
+        <v>0.1016</v>
       </c>
       <c r="Q27" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4391</v>
+        <v>0.4355</v>
       </c>
       <c r="S27" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T27" t="n">
         <v>-0.1646</v>
@@ -13824,13 +13336,13 @@
         <v>-0.222</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0404</v>
+        <v>0.0387</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.2665</v>
+        <v>0.2429</v>
       </c>
       <c r="AH27" t="n">
-        <v>6.08</v>
+        <v>6.12</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -13839,13 +13351,13 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.038825</v>
+        <v>-0.031747</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.985866</v>
+        <v>0.98084</v>
       </c>
       <c r="AM27" t="n">
-        <v>-1.41</v>
+        <v>-1.92</v>
       </c>
       <c r="AN27" t="n">
         <v>0</v>
@@ -13875,10 +13387,10 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.11271</v>
+        <v>0.108117</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.3445</v>
+        <v>0.2936</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -14026,7 +13538,7 @@
         <v>0</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.4518</v>
+        <v>0.4514</v>
       </c>
       <c r="CQ27" t="n">
         <v>0</v>
@@ -14055,7 +13567,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -14088,7 +13600,7 @@
         <v>80</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1758</v>
+        <v>0.1754</v>
       </c>
       <c r="L28" t="n">
         <v>0.5625</v>
@@ -14106,13 +13618,13 @@
         <v>0.0025</v>
       </c>
       <c r="Q28" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R28" t="n">
         <v>0.0442</v>
       </c>
       <c r="S28" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="T28" t="n">
         <v>0.09379999999999999</v>
@@ -14157,13 +13669,13 @@
         <v>0.0243</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0254</v>
+        <v>0.0245</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.5742</v>
+        <v>0.5396</v>
       </c>
       <c r="AH28" t="n">
-        <v>11.84</v>
+        <v>11.92</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -14172,13 +13684,13 @@
         <v>0.0165</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.101563</v>
+        <v>-0.07730099999999999</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.061613</v>
+        <v>1.053869</v>
       </c>
       <c r="AM28" t="n">
-        <v>6.16</v>
+        <v>5.39</v>
       </c>
       <c r="AN28" t="n">
         <v>0</v>
@@ -14208,10 +13720,10 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.070989</v>
+        <v>0.06845999999999999</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.4307</v>
+        <v>1.1291</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -14359,7 +13871,7 @@
         <v>0</v>
       </c>
       <c r="CP28" t="n">
-        <v>0.4766</v>
+        <v>0.4534</v>
       </c>
       <c r="CQ28" t="n">
         <v>0</v>
@@ -14388,7 +13900,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -14421,7 +13933,7 @@
         <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0176</v>
+        <v>0.0175</v>
       </c>
       <c r="L29" t="n">
         <v>0.625</v>
@@ -14439,13 +13951,13 @@
         <v>-0.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R29" t="n">
         <v>-0.0736</v>
       </c>
       <c r="S29" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T29" t="n">
         <v>-0.1591</v>
@@ -14490,13 +14002,13 @@
         <v>-0.06850000000000001</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.0215</v>
+        <v>0.0208</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.2428</v>
+        <v>0.2224</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -14505,13 +14017,13 @@
         <v>-0.0028</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.032822</v>
+        <v>-0.023771</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.116594</v>
+        <v>1.112218</v>
       </c>
       <c r="AM29" t="n">
-        <v>11.66</v>
+        <v>11.22</v>
       </c>
       <c r="AN29" t="n">
         <v>0</v>
@@ -14541,10 +14053,10 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.060012</v>
+        <v>0.058127</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.409</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -14692,7 +14204,7 @@
         <v>0</v>
       </c>
       <c r="CP29" t="n">
-        <v>0.4919</v>
+        <v>0.4822</v>
       </c>
       <c r="CQ29" t="n">
         <v>0</v>
@@ -14721,7 +14233,7 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -14758,13 +14270,13 @@
         <v>124</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2725</v>
+        <v>0.2719</v>
       </c>
       <c r="L30" t="n">
         <v>0.6613</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3333</v>
+        <v>0.3309</v>
       </c>
       <c r="N30" t="n">
         <v>0.6983</v>
@@ -14776,19 +14288,19 @@
         <v>0.0013</v>
       </c>
       <c r="Q30" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R30" t="n">
         <v>0.0726</v>
       </c>
       <c r="S30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T30" t="n">
         <v>0.1501</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0507</v>
+        <v>0.0505</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -14823,28 +14335,28 @@
         <v>0.1138</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0187</v>
+        <v>0.0188</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.324</v>
+        <v>0.3289</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.04</v>
+        <v>5.13</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.0409</v>
+        <v>0.0408</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.071608</v>
+        <v>-0.042337</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.101101</v>
+        <v>1.098742</v>
       </c>
       <c r="AM30" t="n">
-        <v>10.11</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AN30" t="n">
         <v>1</v>
@@ -14874,10 +14386,10 @@
         <v>-1</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.052086</v>
+        <v>0.052471</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.3748</v>
+        <v>0.8069</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -15029,10 +14541,10 @@
         <v>1</v>
       </c>
       <c r="CP30" t="n">
-        <v>0.5828</v>
+        <v>0.525</v>
       </c>
       <c r="CQ30" t="n">
-        <v>0.5828</v>
+        <v>0.525</v>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
@@ -15102,7 +14614,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -15116,7 +14628,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -15132,13 +14644,13 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K31" t="n">
-        <v>0.3033</v>
+        <v>0.3048</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7174</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="M31" t="n">
         <v>0.3014</v>
@@ -15153,19 +14665,19 @@
         <v>0.0574</v>
       </c>
       <c r="Q31" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R31" t="n">
         <v>0.0502</v>
       </c>
       <c r="S31" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1506</v>
+        <v>0.1482</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0515</v>
+        <v>0.0513</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -15183,49 +14695,49 @@
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>0.0555</v>
+        <v>0.0533</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.2173</v>
+        <v>0.2088</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.1496</v>
+        <v>0.1472</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.182</v>
+        <v>0.1784</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.024</v>
+        <v>0.0229</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0242</v>
+        <v>0.0226</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.0555</v>
+        <v>0.0533</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0184</v>
+        <v>0.0181</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.5028</v>
+        <v>0.4845</v>
       </c>
       <c r="AH31" t="n">
-        <v>14.78</v>
+        <v>14.99</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.0457</v>
+        <v>0.0452</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.019928</v>
+        <v>3.3e-05</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.136935</v>
+        <v>1.13288</v>
       </c>
       <c r="AM31" t="n">
-        <v>13.69</v>
+        <v>13.29</v>
       </c>
       <c r="AN31" t="n">
         <v>1</v>
@@ -15255,10 +14767,10 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.051356</v>
+        <v>0.050463</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.388</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -15406,7 +14918,7 @@
         <v>0</v>
       </c>
       <c r="CP31" t="n">
-        <v>0.367</v>
+        <v>0.3319</v>
       </c>
       <c r="CQ31" t="n">
         <v>0</v>
@@ -15435,7 +14947,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -15472,37 +14984,37 @@
         <v>43</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0945</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="L32" t="n">
         <v>0.6512</v>
       </c>
       <c r="M32" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2667</v>
+        <v>0.2666</v>
       </c>
       <c r="O32" t="n">
         <v>-0.18</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.0612</v>
+        <v>-0.058</v>
       </c>
       <c r="Q32" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.0755</v>
+        <v>-0.0722</v>
       </c>
       <c r="S32" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="T32" t="n">
         <v>-0.1354</v>
       </c>
       <c r="U32" t="n">
-        <v>0.018</v>
+        <v>0.0178</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -15541,28 +15053,28 @@
         <v>-0.1207</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.1526</v>
+        <v>0.2936</v>
       </c>
       <c r="AH32" t="n">
-        <v>17.68</v>
+        <v>18.15</v>
       </c>
       <c r="AI32" t="n">
-        <v>18.09</v>
+        <v>18.66</v>
       </c>
       <c r="AJ32" t="n">
         <v>-0.0128</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.027719</v>
+        <v>0.049109</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.183489</v>
+        <v>1.141632</v>
       </c>
       <c r="AM32" t="n">
-        <v>18.35</v>
+        <v>14.16</v>
       </c>
       <c r="AN32" t="n">
         <v>1</v>
@@ -15592,10 +15104,10 @@
         <v>1</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.028043</v>
+        <v>0.033483</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.9885</v>
+        <v>1.4667</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -15743,10 +15255,10 @@
         <v>0</v>
       </c>
       <c r="CP32" t="n">
-        <v>0.5202</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="CQ32" t="n">
-        <v>0.5202</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="CR32" t="inlineStr">
         <is>
@@ -15784,7 +15296,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -15810,14 +15322,14 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J33" t="n">
         <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>0.022</v>
+        <v>0.0219</v>
       </c>
       <c r="L33" t="n">
         <v>0.4</v>
@@ -15829,19 +15341,19 @@
         <v>1.4798</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5298</v>
       </c>
       <c r="P33" t="n">
         <v>0.1278</v>
       </c>
       <c r="Q33" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R33" t="n">
         <v>0.2698</v>
       </c>
       <c r="S33" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="T33" t="n">
         <v>0.4839</v>
@@ -15864,7 +15376,7 @@
         <v>0.509</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.5906</v>
+        <v>1.5907</v>
       </c>
       <c r="AA33" t="n">
         <v>0.4829</v>
@@ -15885,10 +15397,10 @@
         <v>0.0166</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.3856</v>
+        <v>0.3845</v>
       </c>
       <c r="AH33" t="n">
-        <v>26.79</v>
+        <v>27.21</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -15897,13 +15409,13 @@
         <v>0.0106</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.030082</v>
+        <v>-0.013419</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.927673</v>
+        <v>0.872796</v>
       </c>
       <c r="AM33" t="n">
-        <v>-7.23</v>
+        <v>-12.72</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
@@ -15933,10 +15445,10 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.046349</v>
+        <v>0.046286</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.649</v>
+        <v>0.2899</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -15946,7 +15458,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -16088,7 +15600,7 @@
         <v>1</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.4517</v>
+        <v>0.416</v>
       </c>
       <c r="CQ33" t="n">
         <v>0</v>
@@ -16117,7 +15629,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -16147,40 +15659,40 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0462</v>
+        <v>0.0482</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2857</v>
+        <v>0.3182</v>
       </c>
       <c r="M34" t="n">
-        <v>0.25</v>
+        <v>0.2917</v>
       </c>
       <c r="N34" t="n">
-        <v>2.152</v>
+        <v>2.1845</v>
       </c>
       <c r="O34" t="n">
-        <v>2.2403</v>
+        <v>2.2783</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.1703</v>
+        <v>-0.1594</v>
       </c>
       <c r="Q34" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R34" t="n">
         <v>-0.18</v>
       </c>
       <c r="S34" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T34" t="n">
-        <v>0.4863</v>
+        <v>0.5723</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2251</v>
+        <v>0.2346</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -16194,49 +15706,49 @@
       </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>0.4853</v>
+        <v>0.5713</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.6811</v>
+        <v>3.1565</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.4853</v>
+        <v>0.5713</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.4606</v>
+        <v>0.5596</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.0027</v>
+        <v>0.0177</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.0387</v>
+        <v>-0.0208</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.0066</v>
+        <v>0.0216</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0205</v>
+        <v>0.0196</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.453</v>
+        <v>0.4093</v>
       </c>
       <c r="AH34" t="n">
-        <v>32.09</v>
+        <v>32.42</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.0224</v>
+        <v>0.0276</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.07989400000000001</v>
+        <v>0.085122</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.678023</v>
+        <v>0.726306</v>
       </c>
       <c r="AM34" t="n">
-        <v>-32.2</v>
+        <v>-27.37</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
@@ -16266,10 +15778,10 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.057101</v>
+        <v>0.054665</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.3992</v>
+        <v>1.5572</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -16417,7 +15929,7 @@
         <v>0</v>
       </c>
       <c r="CP34" t="n">
-        <v>0.512</v>
+        <v>0.5365</v>
       </c>
       <c r="CQ34" t="n">
         <v>0</v>
@@ -16446,7 +15958,7 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -16460,7 +15972,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -16479,7 +15991,7 @@
         <v>35</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0769</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L35" t="n">
         <v>0.3143</v>
@@ -16494,16 +16006,16 @@
         <v>-0.098</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0052</v>
+        <v>0.0039</v>
       </c>
       <c r="Q35" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0477</v>
+        <v>0.0472</v>
       </c>
       <c r="S35" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="T35" t="n">
         <v>-0.1032</v>
@@ -16548,13 +16060,13 @@
         <v>-0.1594</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.0226</v>
+        <v>0.0217</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.4299</v>
+        <v>0.3885</v>
       </c>
       <c r="AH35" t="n">
-        <v>21.06</v>
+        <v>21.24</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -16563,13 +16075,13 @@
         <v>-0.007900000000000001</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.010506</v>
+        <v>0.011244</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.937751</v>
+        <v>0.949411</v>
       </c>
       <c r="AM35" t="n">
-        <v>-6.22</v>
+        <v>-5.06</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -16599,10 +16111,10 @@
         <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.06314699999999999</v>
+        <v>0.060587</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.1664</v>
+        <v>0.1856</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -16750,7 +16262,7 @@
         <v>0</v>
       </c>
       <c r="CP35" t="n">
-        <v>0.3974</v>
+        <v>0.4076</v>
       </c>
       <c r="CQ35" t="n">
         <v>0</v>
@@ -16779,7 +16291,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -16793,7 +16305,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -16809,13 +16321,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0989</v>
+        <v>0.1009</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4444</v>
+        <v>0.4565</v>
       </c>
       <c r="M36" t="n">
         <v>0.36</v>
@@ -16827,22 +16339,22 @@
         <v>0.3232</v>
       </c>
       <c r="P36" t="n">
-        <v>0.1003</v>
+        <v>0.0898</v>
       </c>
       <c r="Q36" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1797</v>
+        <v>0.172</v>
       </c>
       <c r="S36" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T36" t="n">
-        <v>0.1242</v>
+        <v>0.1176</v>
       </c>
       <c r="U36" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -16856,49 +16368,49 @@
       </c>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="n">
-        <v>0.1592</v>
+        <v>0.1488</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.4976</v>
+        <v>0.465</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.1232</v>
+        <v>0.1166</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.1592</v>
+        <v>0.1488</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.0583</v>
+        <v>0.0542</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.041</v>
+        <v>0.0359</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.0983</v>
+        <v>0.0906</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.017</v>
+        <v>0.0172</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.4399</v>
+        <v>0.4495</v>
       </c>
       <c r="AH36" t="n">
-        <v>28.56</v>
+        <v>29.1</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.0123</v>
+        <v>0.0119</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0.026449</v>
+        <v>0.000307</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.939546</v>
+        <v>0.880878</v>
       </c>
       <c r="AM36" t="n">
-        <v>-6.05</v>
+        <v>-11.91</v>
       </c>
       <c r="AN36" t="n">
         <v>0</v>
@@ -16928,10 +16440,10 @@
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.047513</v>
+        <v>0.048067</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.5567</v>
+        <v>0.0064</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -17083,7 +16595,7 @@
         <v>0</v>
       </c>
       <c r="CP36" t="n">
-        <v>0.4184</v>
+        <v>0.3615</v>
       </c>
       <c r="CQ36" t="n">
         <v>0</v>
@@ -17112,7 +16624,7 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -17145,7 +16657,7 @@
         <v>22</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0484</v>
+        <v>0.0482</v>
       </c>
       <c r="L37" t="n">
         <v>0.8636</v>
@@ -17160,16 +16672,16 @@
         <v>0.4577</v>
       </c>
       <c r="P37" t="n">
-        <v>0.5857</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q37" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R37" t="n">
-        <v>0.8659</v>
+        <v>0.8572</v>
       </c>
       <c r="S37" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="T37" t="n">
         <v>0.3336</v>
@@ -17210,13 +16722,13 @@
         <v>0.1978</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.0205</v>
+        <v>0.0198</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.2983</v>
+        <v>0.278</v>
       </c>
       <c r="AH37" t="n">
-        <v>63.41</v>
+        <v>64.06</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -17225,13 +16737,13 @@
         <v>0.0161</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.003215</v>
+        <v>0.018584</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.648047</v>
+        <v>0.573437</v>
       </c>
       <c r="AM37" t="n">
-        <v>-35.2</v>
+        <v>-42.66</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -17261,10 +16773,10 @@
         <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.0573</v>
+        <v>0.05521</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.0561</v>
+        <v>0.3366</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -17412,7 +16924,7 @@
         <v>0</v>
       </c>
       <c r="CP37" t="n">
-        <v>0.4235</v>
+        <v>0.4556</v>
       </c>
       <c r="CQ37" t="n">
         <v>0</v>
@@ -17441,7 +16953,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -17450,7 +16962,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -17459,26 +16971,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J38" t="n">
         <v>77</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1692</v>
+        <v>0.1689</v>
       </c>
       <c r="L38" t="n">
         <v>0.5974</v>
@@ -17496,13 +17004,13 @@
         <v>-0.168</v>
       </c>
       <c r="Q38" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R38" t="n">
         <v>-0.0547</v>
       </c>
       <c r="S38" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="T38" t="n">
         <v>0.0565</v>
@@ -17543,28 +17051,28 @@
         <v>0.027</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.028</v>
+        <v>0.0276</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.2696</v>
+        <v>0.2527</v>
       </c>
       <c r="AH38" t="n">
-        <v>7.94</v>
+        <v>8.08</v>
       </c>
       <c r="AI38" t="n">
-        <v>7.42</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0095</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.076617</v>
+        <v>-0.051221</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.124439</v>
+        <v>1.114748</v>
       </c>
       <c r="AM38" t="n">
-        <v>12.44</v>
+        <v>11.47</v>
       </c>
       <c r="AN38" t="n">
         <v>1</v>
@@ -17591,13 +17099,13 @@
         <v>1</v>
       </c>
       <c r="AV38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.078274</v>
+        <v>0.076913</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.9788</v>
+        <v>0.666</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -17607,7 +17115,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -17749,71 +17257,27 @@
         <v>1</v>
       </c>
       <c r="CP38" t="n">
-        <v>0.5376</v>
+        <v>0.5097</v>
       </c>
       <c r="CQ38" t="n">
-        <v>0.5376</v>
-      </c>
-      <c r="CR38" t="inlineStr">
-        <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="CS38" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CT38" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CU38" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CV38" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CW38" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.056 | spread_35_20: esp=+0.003 | spread_45_25: esp=+0.010 | spread_45_15: esp=+0.027</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CR38" t="inlineStr"/>
+      <c r="CS38" t="inlineStr"/>
+      <c r="CT38" t="inlineStr"/>
+      <c r="CU38" t="inlineStr"/>
+      <c r="CV38" t="inlineStr"/>
+      <c r="CW38" t="inlineStr"/>
       <c r="CX38" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.079 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
-        </is>
-      </c>
-      <c r="CY38" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="CZ38" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
-        </is>
-      </c>
-      <c r="DA38" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DB38" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DC38" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
+          <t>Ticker neutro — sem sinal operacional</t>
+        </is>
+      </c>
+      <c r="CY38" t="inlineStr"/>
+      <c r="CZ38" t="inlineStr"/>
+      <c r="DA38" t="inlineStr"/>
+      <c r="DB38" t="inlineStr"/>
+      <c r="DC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17822,7 +17286,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -17852,13 +17316,13 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1604</v>
+        <v>0.1623</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4932</v>
+        <v>0.4865</v>
       </c>
       <c r="M39" t="n">
         <v>0.3165</v>
@@ -17873,19 +17337,19 @@
         <v>-0.0022</v>
       </c>
       <c r="Q39" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R39" t="n">
         <v>0.0395</v>
       </c>
       <c r="S39" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T39" t="n">
-        <v>0.1592</v>
+        <v>0.1547</v>
       </c>
       <c r="U39" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -17899,49 +17363,49 @@
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
-        <v>0.1711</v>
+        <v>0.1645</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.5347</v>
+        <v>0.5142</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.1582</v>
+        <v>0.1537</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.1711</v>
+        <v>0.1645</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.0253</v>
+        <v>0.0233</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.0068</v>
+        <v>0.0041</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.0492</v>
+        <v>0.0451</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.0156</v>
+        <v>0.015</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.5607</v>
+        <v>0.5218</v>
       </c>
       <c r="AH39" t="n">
-        <v>13.38</v>
+        <v>13.31</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.0255</v>
+        <v>0.0251</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.014403</v>
+        <v>0.009046</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.122978</v>
+        <v>1.146713</v>
       </c>
       <c r="AM39" t="n">
-        <v>12.3</v>
+        <v>14.67</v>
       </c>
       <c r="AN39" t="n">
         <v>0</v>
@@ -17971,10 +17435,10 @@
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.043616</v>
+        <v>0.04177</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.3302</v>
+        <v>0.2166</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -18126,7 +17590,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>0.4013</v>
+        <v>0.3977</v>
       </c>
       <c r="CQ39" t="n">
         <v>0</v>
@@ -18155,7 +17619,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -18188,7 +17652,7 @@
         <v>69</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1523</v>
+        <v>0.152</v>
       </c>
       <c r="L40" t="n">
         <v>0.7826</v>
@@ -18197,25 +17661,25 @@
         <v>0.2029</v>
       </c>
       <c r="N40" t="n">
-        <v>1.0366</v>
+        <v>1.0359</v>
       </c>
       <c r="O40" t="n">
         <v>-0.18</v>
       </c>
       <c r="P40" t="n">
-        <v>-0.1701</v>
+        <v>-0.1704</v>
       </c>
       <c r="Q40" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="R40" t="n">
         <v>-0.0815</v>
       </c>
       <c r="S40" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="T40" t="n">
-        <v>0.0707</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="U40" t="n">
         <v>0.0698</v>
@@ -18242,43 +17706,43 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.0697</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.0785</v>
+        <v>0.0781</v>
       </c>
       <c r="AC40" t="n">
         <v>-0.0219</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.0137</v>
+        <v>-0.014</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.0138</v>
+        <v>-0.014</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.0263</v>
+        <v>0.0256</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.9549</v>
+        <v>0.9226</v>
       </c>
       <c r="AH40" t="n">
-        <v>26.68</v>
+        <v>27.04</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.0108</v>
+        <v>0.0107</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.002424</v>
+        <v>0.005019</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.88493</v>
+        <v>0.865217</v>
       </c>
       <c r="AM40" t="n">
-        <v>-11.51</v>
+        <v>-13.48</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -18308,10 +17772,10 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.073354</v>
+        <v>0.071557</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.0331</v>
+        <v>0.0701</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -18459,7 +17923,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>0.2967</v>
+        <v>0.3068</v>
       </c>
       <c r="CQ40" t="n">
         <v>0</v>
@@ -18488,7 +17952,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -18502,7 +17966,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -18521,7 +17985,7 @@
         <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>0.022</v>
+        <v>0.0219</v>
       </c>
       <c r="L41" t="n">
         <v>0.2</v>
@@ -18536,16 +18000,16 @@
         <v>1.3137</v>
       </c>
       <c r="P41" t="n">
+        <v>-0.1375</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>436</v>
+      </c>
+      <c r="R41" t="n">
         <v>-0.1291</v>
       </c>
-      <c r="Q41" t="n">
-        <v>435</v>
-      </c>
-      <c r="R41" t="n">
-        <v>-0.1079</v>
-      </c>
       <c r="S41" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T41" t="n">
         <v>0.1187</v>
@@ -18590,13 +18054,13 @@
         <v>-0.08119999999999999</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.0134</v>
+        <v>0.0136</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.205</v>
+        <v>0.2157</v>
       </c>
       <c r="AH41" t="n">
-        <v>14.61</v>
+        <v>14.84</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -18605,13 +18069,13 @@
         <v>0.0026</v>
       </c>
       <c r="AK41" t="n">
-        <v>-0.016124</v>
+        <v>0.018574</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.052464</v>
+        <v>1.041764</v>
       </c>
       <c r="AM41" t="n">
-        <v>5.25</v>
+        <v>4.18</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -18641,10 +18105,10 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.037334</v>
+        <v>0.037819</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.4319</v>
+        <v>0.4911</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -18796,7 +18260,7 @@
         <v>1</v>
       </c>
       <c r="CP41" t="n">
-        <v>0.5222</v>
+        <v>0.5259</v>
       </c>
       <c r="CQ41" t="n">
         <v>0</v>
@@ -18825,7 +18289,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -18839,7 +18303,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -18855,13 +18319,13 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1714</v>
+        <v>0.1732</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3718</v>
+        <v>0.3797</v>
       </c>
       <c r="M42" t="n">
         <v>0.1829</v>
@@ -18870,25 +18334,25 @@
         <v>0.9302</v>
       </c>
       <c r="O42" t="n">
-        <v>0.0505</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.0385</v>
+        <v>-0.0283</v>
       </c>
       <c r="Q42" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.0191</v>
+        <v>-0.0211</v>
       </c>
       <c r="S42" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="T42" t="n">
-        <v>0.0372</v>
+        <v>0.0345</v>
       </c>
       <c r="U42" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0653</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -18912,43 +18376,43 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.0362</v>
+        <v>0.0335</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.0029</v>
+        <v>0.0033</v>
       </c>
       <c r="AC42" t="n">
         <v>-0.0342</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.0575</v>
+        <v>-0.0548</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.066</v>
+        <v>-0.0639</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.0167</v>
+        <v>0.0162</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.4807</v>
+        <v>0.4508</v>
       </c>
       <c r="AH42" t="n">
-        <v>54.29</v>
+        <v>54.92</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.0064</v>
+        <v>0.006</v>
       </c>
       <c r="AK42" t="n">
-        <v>-0.001311</v>
+        <v>0.01532</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.026351</v>
+        <v>1.017944</v>
       </c>
       <c r="AM42" t="n">
-        <v>2.64</v>
+        <v>1.79</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -18978,10 +18442,10 @@
         <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.046491</v>
+        <v>0.045222</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.0282</v>
+        <v>0.3388</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -19133,7 +18597,7 @@
         <v>0</v>
       </c>
       <c r="CP42" t="n">
-        <v>0.4023</v>
+        <v>0.4393</v>
       </c>
       <c r="CQ42" t="n">
         <v>0</v>
@@ -19162,7 +18626,7 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -19196,40 +18660,40 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1011</v>
+        <v>0.1031</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8298</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4333</v>
+        <v>0.4426</v>
       </c>
       <c r="N43" t="n">
-        <v>1.2882</v>
+        <v>1.2819</v>
       </c>
       <c r="O43" t="n">
-        <v>0.6083</v>
+        <v>0.7336</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.0694</v>
+        <v>-0.059</v>
       </c>
       <c r="Q43" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0058</v>
+        <v>0.0101</v>
       </c>
       <c r="S43" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="T43" t="n">
-        <v>0.6405</v>
+        <v>0.6505</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1205</v>
+        <v>0.1186</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -19243,49 +18707,49 @@
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>0.8126</v>
+        <v>0.8244</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.5393</v>
+        <v>2.5762</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.6395</v>
+        <v>0.6495</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.8126</v>
+        <v>0.8244</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.159</v>
+        <v>0.1626</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.2076</v>
+        <v>0.2106</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.3189</v>
+        <v>0.3251</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.0413</v>
+        <v>0.0398</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.2355</v>
+        <v>0.2154</v>
       </c>
       <c r="AH43" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.0648</v>
+        <v>0.067</v>
       </c>
       <c r="AK43" t="n">
-        <v>-0.203546</v>
+        <v>-0.196543</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.120573</v>
+        <v>1.162918</v>
       </c>
       <c r="AM43" t="n">
-        <v>12.06</v>
+        <v>16.29</v>
       </c>
       <c r="AN43" t="n">
         <v>1</v>
@@ -19315,10 +18779,10 @@
         <v>-1</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.115249</v>
+        <v>0.111106</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.7661</v>
+        <v>1.769</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -19466,10 +18930,10 @@
         <v>1</v>
       </c>
       <c r="CP43" t="n">
-        <v>0.6065</v>
+        <v>0.6108</v>
       </c>
       <c r="CQ43" t="n">
-        <v>0.6065</v>
+        <v>0.6108</v>
       </c>
       <c r="CR43" t="inlineStr">
         <is>
@@ -19498,12 +18962,12 @@
       </c>
       <c r="CW43" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.639 | spread_35_20: esp=+0.159 | spread_45_25: esp=+0.208 | spread_45_15: esp=+0.319</t>
+          <t>naked_30: esp=+0.649 | spread_35_20: esp=+0.163 | spread_45_25: esp=+0.211 | spread_45_15: esp=+0.325</t>
         </is>
       </c>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.813 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.824 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="CY43" t="inlineStr">
@@ -19539,7 +19003,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -19565,14 +19029,14 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0462</v>
+        <v>0.0461</v>
       </c>
       <c r="L44" t="n">
         <v>0.4762</v>
@@ -19587,16 +19051,16 @@
         <v>0.4406</v>
       </c>
       <c r="P44" t="n">
-        <v>-0.0785</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="Q44" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0713</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="S44" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T44" t="n">
         <v>0.1812</v>
@@ -19637,28 +19101,28 @@
         <v>0.1186</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0144</v>
+        <v>0.0143</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.1704</v>
+        <v>0.1749</v>
       </c>
       <c r="AH44" t="n">
-        <v>16.53</v>
+        <v>16.79</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.018077</v>
+        <v>0.043315</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.169565</v>
+        <v>1.175121</v>
       </c>
       <c r="AM44" t="n">
-        <v>16.96</v>
+        <v>17.51</v>
       </c>
       <c r="AN44" t="n">
         <v>0</v>
@@ -19688,10 +19152,10 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.040323</v>
+        <v>0.039979</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.4483</v>
+        <v>1.0834</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
@@ -19701,7 +19165,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -19843,7 +19307,7 @@
         <v>0</v>
       </c>
       <c r="CP44" t="n">
-        <v>0.4969</v>
+        <v>0.5595</v>
       </c>
       <c r="CQ44" t="n">
         <v>0</v>
@@ -19872,7 +19336,7 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -19905,7 +19369,7 @@
         <v>41</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0901</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="L45" t="n">
         <v>0.5610000000000001</v>
@@ -19923,13 +19387,13 @@
         <v>-0.1793</v>
       </c>
       <c r="Q45" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R45" t="n">
         <v>0.013</v>
       </c>
       <c r="S45" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T45" t="n">
         <v>0.0654</v>
@@ -19970,13 +19434,13 @@
         <v>0.1134</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.0233</v>
+        <v>0.023</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.2155</v>
+        <v>0.2026</v>
       </c>
       <c r="AH45" t="n">
-        <v>9.57</v>
+        <v>9.74</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -19985,13 +19449,13 @@
         <v>0.0059</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.034393</v>
+        <v>-0.007142</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.239353</v>
+        <v>1.056119</v>
       </c>
       <c r="AM45" t="n">
-        <v>23.94</v>
+        <v>5.61</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -20021,10 +19485,10 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.064903</v>
+        <v>0.06418699999999999</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.5299</v>
+        <v>0.1113</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -20172,7 +19636,7 @@
         <v>0</v>
       </c>
       <c r="CP45" t="n">
-        <v>0.4776</v>
+        <v>0.4383</v>
       </c>
       <c r="CQ45" t="n">
         <v>0</v>
@@ -20201,7 +19665,7 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -20234,7 +19698,7 @@
         <v>27</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0593</v>
+        <v>0.0592</v>
       </c>
       <c r="L46" t="n">
         <v>0.3333</v>
@@ -20252,13 +19716,13 @@
         <v>0.0284</v>
       </c>
       <c r="Q46" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R46" t="n">
         <v>0.1745</v>
       </c>
       <c r="S46" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="T46" t="n">
         <v>-0.1264</v>
@@ -20303,13 +19767,13 @@
         <v>-0.0945</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0203</v>
+        <v>0.0202</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.3571</v>
+        <v>0.3491</v>
       </c>
       <c r="AH46" t="n">
-        <v>11.46</v>
+        <v>11.61</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -20318,13 +19782,13 @@
         <v>-0.0075</v>
       </c>
       <c r="AK46" t="n">
-        <v>-0.104818</v>
+        <v>-0.070549</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.133951</v>
+        <v>1.094731</v>
       </c>
       <c r="AM46" t="n">
-        <v>13.4</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -20354,10 +19818,10 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.056779</v>
+        <v>0.056372</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.8461</v>
+        <v>1.2515</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
@@ -20509,7 +19973,7 @@
         <v>0</v>
       </c>
       <c r="CP46" t="n">
-        <v>0.5909</v>
+        <v>0.533</v>
       </c>
       <c r="CQ46" t="n">
         <v>0</v>
@@ -20538,7 +20002,7 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -20571,7 +20035,7 @@
         <v>51</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1121</v>
+        <v>0.1118</v>
       </c>
       <c r="L47" t="n">
         <v>0.6274999999999999</v>
@@ -20589,13 +20053,13 @@
         <v>0.0314</v>
       </c>
       <c r="Q47" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R47" t="n">
         <v>0.0425</v>
       </c>
       <c r="S47" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="T47" t="n">
         <v>1.2836</v>
@@ -20636,28 +20100,28 @@
         <v>0.2225</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.0258</v>
+        <v>0.0248</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.477</v>
+        <v>0.4431</v>
       </c>
       <c r="AH47" t="n">
-        <v>7.13</v>
+        <v>7.19</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.1439</v>
+        <v>0.1436</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.033248</v>
+        <v>-0.008533000000000001</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.970159</v>
+        <v>0.94677</v>
       </c>
       <c r="AM47" t="n">
-        <v>-2.98</v>
+        <v>-5.32</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
@@ -20687,10 +20151,10 @@
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.071867</v>
+        <v>0.06908</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.4626</v>
+        <v>0.1235</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -20842,7 +20306,7 @@
         <v>0</v>
       </c>
       <c r="CP47" t="n">
-        <v>0.3944</v>
+        <v>0.3673</v>
       </c>
       <c r="CQ47" t="n">
         <v>0</v>
@@ -20871,7 +20335,7 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -20904,7 +20368,7 @@
         <v>9</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0198</v>
+        <v>0.0197</v>
       </c>
       <c r="L48" t="n">
         <v>0.1111</v>
@@ -20919,16 +20383,16 @@
         <v>2.4065</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.1174</v>
+        <v>-0.1084</v>
       </c>
       <c r="Q48" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R48" t="n">
-        <v>-0.1442</v>
+        <v>-0.1426</v>
       </c>
       <c r="S48" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T48" t="n">
         <v>0.1074</v>
@@ -20973,13 +20437,13 @@
         <v>-0.1585</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.03</v>
+        <v>0.0287</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.2197</v>
+        <v>0.1817</v>
       </c>
       <c r="AH48" t="n">
-        <v>8.25</v>
+        <v>8.27</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -20988,13 +20452,13 @@
         <v>0.0021</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.059336</v>
+        <v>-0.057259</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.081431</v>
+        <v>1.100581</v>
       </c>
       <c r="AM48" t="n">
-        <v>8.140000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="AN48" t="n">
         <v>1</v>
@@ -21024,10 +20488,10 @@
         <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.083663</v>
+        <v>0.080112</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7147</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
@@ -21175,7 +20639,7 @@
         <v>0</v>
       </c>
       <c r="CP48" t="n">
-        <v>0.4842</v>
+        <v>0.4923</v>
       </c>
       <c r="CQ48" t="n">
         <v>0</v>
@@ -21204,7 +20668,7 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -21252,16 +20716,16 @@
         <v>-0.18</v>
       </c>
       <c r="P49" t="n">
-        <v>0.0227</v>
+        <v>0.0211</v>
       </c>
       <c r="Q49" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R49" t="n">
-        <v>0.1955</v>
+        <v>0.1807</v>
       </c>
       <c r="S49" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="T49" t="n">
         <v>-0.18</v>
@@ -21304,13 +20768,13 @@
         <v>-0.2552</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.0263</v>
+        <v>0.0254</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.5659</v>
+        <v>0.5299</v>
       </c>
       <c r="AH49" t="n">
-        <v>11.44</v>
+        <v>11.55</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -21319,13 +20783,13 @@
         <v>-0.0004</v>
       </c>
       <c r="AK49" t="n">
-        <v>-0.037688</v>
+        <v>-0.011632</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.052871</v>
+        <v>1.055021</v>
       </c>
       <c r="AM49" t="n">
-        <v>5.29</v>
+        <v>5.5</v>
       </c>
       <c r="AN49" t="n">
         <v>0</v>
@@ -21355,10 +20819,10 @@
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.073282</v>
+        <v>0.07076300000000001</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.5143</v>
+        <v>0.1644</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -21506,7 +20970,7 @@
         <v>0</v>
       </c>
       <c r="CP49" t="n">
-        <v>0.4274</v>
+        <v>0.3996</v>
       </c>
       <c r="CQ49" t="n">
         <v>0</v>
@@ -21535,7 +20999,7 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -21568,7 +21032,7 @@
         <v>77</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1692</v>
+        <v>0.1689</v>
       </c>
       <c r="L50" t="n">
         <v>0.7662</v>
@@ -21583,16 +21047,16 @@
         <v>0.07779999999999999</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0529</v>
+        <v>0.0519</v>
       </c>
       <c r="Q50" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="R50" t="n">
-        <v>0.1036</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="S50" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T50" t="n">
         <v>0.2314</v>
@@ -21633,28 +21097,28 @@
         <v>0.2292</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.0153</v>
+        <v>0.0146</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.1678</v>
+        <v>0.1445</v>
       </c>
       <c r="AH50" t="n">
-        <v>14.09</v>
+        <v>14.07</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.0392</v>
+        <v>0.0391</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.011308</v>
+        <v>0.01832</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.08553</v>
+        <v>1.103393</v>
       </c>
       <c r="AM50" t="n">
-        <v>8.550000000000001</v>
+        <v>10.34</v>
       </c>
       <c r="AN50" t="n">
         <v>1</v>
@@ -21684,10 +21148,10 @@
         <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.042671</v>
+        <v>0.040786</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.265</v>
+        <v>0.4492</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
@@ -21839,7 +21303,7 @@
         <v>0</v>
       </c>
       <c r="CP50" t="n">
-        <v>0.4391</v>
+        <v>0.4622</v>
       </c>
       <c r="CQ50" t="n">
         <v>0</v>
@@ -40423,7 +39887,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -40783,7 +40247,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -40891,7 +40355,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -40927,7 +40391,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>volatility_gate_bloqueado:har_fallback_moderado</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -40999,7 +40463,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -41359,7 +40823,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -41539,12 +41003,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -41755,7 +41219,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -42189,7 +41653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.4978</v>
+        <v>0.5215</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -42255,7 +41719,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.6247</v>
+        <v>0.5903</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -42321,7 +41785,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.4506</v>
+        <v>0.4781</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -42387,7 +41851,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.4203</v>
+        <v>0.4292</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -42499,7 +41963,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.5347</v>
+        <v>0.585</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -42730,7 +42194,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -42745,15 +42209,15 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.4321</v>
+        <v>0.4676</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -42815,7 +42279,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.437</v>
+        <v>0.4507</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -42973,7 +42437,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.5003</v>
+        <v>0.5098</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -43131,7 +42595,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.4006</v>
+        <v>0.4406</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -43197,7 +42661,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.5802</v>
+        <v>0.587</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -43263,7 +42727,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.5419</v>
+        <v>0.5538</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -43329,7 +42793,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.5051</v>
+        <v>0.4861</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -43395,7 +42859,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.2924</v>
+        <v>0.2997</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -43503,7 +42967,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5211</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -43615,7 +43079,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.4686</v>
+        <v>0.4551</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -43624,7 +43088,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
     </row>
@@ -43708,7 +43172,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -43723,15 +43187,15 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.4406</v>
+        <v>0.4948</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -43793,7 +43257,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.6065</v>
+        <v>0.5958</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -43951,7 +43415,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.3802</v>
+        <v>0.3639</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -44044,10 +43508,10 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -44059,20 +43523,20 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.4783</v>
+        <v>0.4516</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>compressao</t>
         </is>
       </c>
     </row>
@@ -44110,7 +43574,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -44125,15 +43589,15 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>volatility_gate_bloqueado:har_fallback_moderado</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.4839</v>
+        <v>0.5458</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -44195,7 +43659,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.3828</v>
+        <v>0.432</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -44242,7 +43706,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -44257,15 +43721,15 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.5022</v>
+        <v>0.4612</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -44327,7 +43791,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.5934</v>
+        <v>0.6025</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -44564,7 +44028,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -44577,7 +44041,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.3875</v>
+        <v>0.3952</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -44643,7 +44107,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.3673</v>
+        <v>0.3719</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -44709,7 +44173,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.4518</v>
+        <v>0.4514</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -44775,7 +44239,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.4766</v>
+        <v>0.4534</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -44979,7 +44443,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.4919</v>
+        <v>0.4822</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -45045,7 +44509,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.5828</v>
+        <v>0.525</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -45111,7 +44575,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.367</v>
+        <v>0.3319</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -45177,7 +44641,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.5202</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -45224,7 +44688,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -45239,15 +44703,15 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.4517</v>
+        <v>0.416</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -45539,7 +45003,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.512</v>
+        <v>0.5365</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -45927,7 +45391,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.3974</v>
+        <v>0.4076</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -46039,7 +45503,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.4184</v>
+        <v>0.3615</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -46105,7 +45569,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.4235</v>
+        <v>0.4556</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -46204,20 +45668,20 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.5376</v>
+        <v>0.5097</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -46279,7 +45743,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.4013</v>
+        <v>0.3977</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -46387,7 +45851,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.2967</v>
+        <v>0.3068</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -46499,7 +45963,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.5222</v>
+        <v>0.5259</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -46565,7 +46029,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.4023</v>
+        <v>0.4393</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -46895,7 +46359,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0.6065</v>
+        <v>0.6108</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -47076,7 +46540,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
@@ -47091,15 +46555,15 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.4969</v>
+        <v>0.5595</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -47161,7 +46625,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0.4776</v>
+        <v>0.4383</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -47227,7 +46691,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.5909</v>
+        <v>0.533</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -47339,7 +46803,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0.3944</v>
+        <v>0.3673</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -47405,7 +46869,7 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0.4842</v>
+        <v>0.4923</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -47517,7 +46981,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.4274</v>
+        <v>0.3996</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -47629,7 +47093,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0.4391</v>
+        <v>0.4622</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -47855,7 +47319,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -47865,7 +47329,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -47885,7 +47349,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -47925,7 +47389,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -47955,7 +47419,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30">
@@ -47975,7 +47439,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="32">

--- a/saidas/ordens_dia/ordem_dia_2026_07_28_executor_v5_5.xlsx
+++ b/saidas/ordens_dia/ordem_dia_2026_07_28_executor_v5_5.xlsx
@@ -1032,7 +1032,7 @@
         <v>0.3564</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9012</v>
+        <v>0.9003</v>
       </c>
       <c r="P2" t="n">
         <v>0.1617</v>
@@ -1050,7 +1050,7 @@
         <v>398</v>
       </c>
       <c r="U2" t="n">
-        <v>0.245</v>
+        <v>0.2446</v>
       </c>
       <c r="V2" t="n">
         <v>0.0489</v>
@@ -1067,16 +1067,16 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.3283</v>
+        <v>0.3279</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.0258</v>
+        <v>1.0247</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.244</v>
+        <v>0.2436</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3283</v>
+        <v>0.3279</v>
       </c>
       <c r="AD2" t="n">
         <v>0.0706</v>
@@ -1085,31 +1085,31 @@
         <v>0.0919</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1461</v>
+        <v>0.1457</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0137</v>
+        <v>0.0136</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.3162</v>
+        <v>0.3095</v>
       </c>
       <c r="AI2" t="n">
-        <v>18.87</v>
+        <v>18.81</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19.47</v>
+        <v>19.41</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0999</v>
+        <v>0.0998</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.059038</v>
+        <v>0.056146</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.116637</v>
+        <v>1.103892</v>
       </c>
       <c r="AN2" t="n">
-        <v>11.66</v>
+        <v>10.39</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -1139,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.038286</v>
+        <v>0.038034</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.542</v>
+        <v>1.4762</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.585</v>
+        <v>0.5798</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.585</v>
+        <v>0.5798</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1488,13 +1488,13 @@
         <v>0.067</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.196543</v>
+        <v>-0.196581</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.162918</v>
+        <v>1.152624</v>
       </c>
       <c r="AN3" t="n">
-        <v>16.29</v>
+        <v>15.26</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
@@ -1527,7 +1527,7 @@
         <v>0.111106</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.769</v>
+        <v>1.7693</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1854,28 +1854,28 @@
         <v>0.1138</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0188</v>
+        <v>0.0183</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.3289</v>
+        <v>0.3128</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5.13</v>
+        <v>5.1</v>
       </c>
       <c r="AK4" t="n">
         <v>0.0408</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.042337</v>
+        <v>-0.046389</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.098742</v>
+        <v>1.107465</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.869999999999999</v>
+        <v>10.75</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
@@ -1905,10 +1905,10 @@
         <v>-1</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.052471</v>
+        <v>0.051205</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.8069</v>
+        <v>0.9059</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2060,10 +2060,10 @@
         <v>1</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.525</v>
+        <v>0.5381</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.525</v>
+        <v>0.5381</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Alerta CALL (VETADA)</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2158,53 +2158,53 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="L5" t="n">
-        <v>0.125</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5263</v>
+        <v>0.6512</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1475</v>
+        <v>0.0702</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5541</v>
+        <v>0.2667</v>
       </c>
       <c r="P5" t="n">
         <v>-0.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0184</v>
+        <v>-0.058</v>
       </c>
       <c r="R5" t="n">
         <v>436</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0692</v>
+        <v>-0.0722</v>
       </c>
       <c r="T5" t="n">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0577</v>
+        <v>-0.1354</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0499</v>
+        <v>0.0178</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -2228,43 +2228,43 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0587</v>
+        <v>-0.1364</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.0639</v>
+        <v>-0.1831</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.0404</v>
+        <v>-0.0723</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.0323</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0561</v>
+        <v>-0.1207</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0231</v>
+        <v>0.011</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.2245</v>
+        <v>0.2226</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.630000000000001</v>
+        <v>18.04</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9.09</v>
+        <v>18.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.0072</v>
+        <v>-0.0128</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.06382</v>
+        <v>0.053369</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.153469</v>
+        <v>1.159549</v>
       </c>
       <c r="AN5" t="n">
-        <v>15.35</v>
+        <v>15.95</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
@@ -2279,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.139753</v>
+        <v>1.114435</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.139753</v>
+        <v>1.115445</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.845253</v>
+        <v>0.876011</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -2294,10 +2294,10 @@
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.06454500000000001</v>
+        <v>0.030743</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.9888</v>
+        <v>1.736</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2316,24 +2316,20 @@
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BI5" t="n">
@@ -2355,78 +2351,78 @@
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BP5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.3535353535353535</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="BR5" t="n">
         <v>1</v>
       </c>
       <c r="BS5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>exec_bilateral</t>
+          <t>exec_alta</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>expansion_moderada</t>
+          <t>exec_expansion_har</t>
         </is>
       </c>
       <c r="BW5" t="n">
-        <v>0.6584</v>
+        <v>0.6368</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.6328</v>
+        <v>0.6546</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.5611</v>
+        <v>0.4917</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.4382483987992929</v>
+        <v>0.3478669257672033</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.5747077669640731</v>
+        <v>0.5742751832410374</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.3957849185932791</v>
+        <v>0.1717746127157639</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.5747077669640731</v>
+        <v>0.5742751832410374</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.5943396226415094</v>
+        <v>0.5181818181818182</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.4436619718309859</v>
+        <v>0.4956521739130435</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.6509433962264151</v>
+        <v>0.5811965811965812</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.4339622641509434</v>
+        <v>0.4503311258278146</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.07843137254901961</v>
+        <v>0</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>expansao_moderada_sem_exec_forte</t>
+          <t>har_fallback_aprovado_expansao</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
@@ -2436,23 +2432,23 @@
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>0.6027397260273972</v>
       </c>
       <c r="CP5" t="n">
         <v>0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.5538</v>
+        <v>0.581</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.5538</v>
+        <v>0.581</v>
       </c>
       <c r="CS5" t="n">
         <v>1</v>
@@ -2493,12 +2489,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compra CALL (VETADA)</t>
+          <t>Alerta CALL (VETADA)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2515,53 +2511,53 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>aprovado_executor_nivel_A</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6512</v>
+        <v>0.5263</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0702</v>
+        <v>0.1475</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2666</v>
+        <v>0.5541</v>
       </c>
       <c r="P6" t="n">
         <v>-0.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.058</v>
+        <v>-0.0184</v>
       </c>
       <c r="R6" t="n">
         <v>436</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0722</v>
+        <v>-0.0692</v>
       </c>
       <c r="T6" t="n">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1354</v>
+        <v>-0.0577</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0178</v>
+        <v>0.0499</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -2570,7 +2566,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>spread_35_20,spread_45_15,spread_45_25</t>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -2585,43 +2581,43 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.1364</v>
+        <v>-0.0587</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1831</v>
+        <v>-0.0639</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0723</v>
+        <v>-0.0404</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0323</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.1207</v>
+        <v>-0.0561</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.012</v>
+        <v>0.0231</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.2936</v>
+        <v>0.2245</v>
       </c>
       <c r="AI6" t="n">
-        <v>18.15</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18.66</v>
+        <v>9.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.0128</v>
+        <v>-0.0072</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.049109</v>
+        <v>0.063786</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.141632</v>
+        <v>1.146744</v>
       </c>
       <c r="AN6" t="n">
-        <v>14.16</v>
+        <v>14.67</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
@@ -2636,13 +2632,13 @@
         <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.114435</v>
+        <v>1.139753</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.115445</v>
+        <v>1.139753</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.876011</v>
+        <v>0.845253</v>
       </c>
       <c r="AV6" t="n">
         <v>1</v>
@@ -2651,10 +2647,10 @@
         <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.033483</v>
+        <v>0.06454500000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.4667</v>
+        <v>0.9882</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -2673,20 +2669,24 @@
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BI6" t="n">
@@ -2708,78 +2708,78 @@
         <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BP6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.3434343434343434</v>
+        <v>0.3535353535353535</v>
       </c>
       <c r="BR6" t="n">
         <v>1</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>exec_alta</t>
+          <t>exec_bilateral</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>exec_expansion_har</t>
+          <t>expansion_moderada</t>
         </is>
       </c>
       <c r="BW6" t="n">
-        <v>0.6368</v>
+        <v>0.6584</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.6546</v>
+        <v>0.6328</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.4917</v>
+        <v>0.5611</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.3478669257672033</v>
+        <v>0.4382483987992929</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.5742751832410374</v>
+        <v>0.5747077669640731</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.1717746127157639</v>
+        <v>0.3957849185932791</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.5742751832410374</v>
+        <v>0.5747077669640731</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.5181818181818182</v>
+        <v>0.5943396226415094</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.4956521739130435</v>
+        <v>0.4436619718309859</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.5811965811965812</v>
+        <v>0.6509433962264151</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.4503311258278146</v>
+        <v>0.4339622641509434</v>
       </c>
       <c r="CH6" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>0.07843137254901961</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>har_fallback_aprovado_expansao</t>
+          <t>expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
@@ -2789,23 +2789,23 @@
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>HAR</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="CN6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.6027397260273972</v>
+        <v>0</v>
       </c>
       <c r="CP6" t="n">
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5537</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5537</v>
       </c>
       <c r="CS6" t="n">
         <v>1</v>
@@ -2970,13 +2970,13 @@
         <v>20.7</v>
       </c>
       <c r="I2" t="n">
-        <v>21.6</v>
+        <v>21.52</v>
       </c>
       <c r="J2" t="n">
-        <v>4.35</v>
+        <v>3.96</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.207</v>
+        <v>-0.176</v>
       </c>
       <c r="L2" t="n">
         <v>0.49</v>
@@ -2988,14 +2988,14 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.515</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0337</v>
+        <v>-0.0363</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>razao=0.52 &lt; 0.6 | M=-0.21 — ativo foi contra, tese falhou</t>
+          <t>razao=0.56 &lt; 0.6 | M=-0.18 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
@@ -3033,13 +3033,13 @@
         <v>13.61</v>
       </c>
       <c r="I3" t="n">
-        <v>13.74</v>
+        <v>13.73</v>
       </c>
       <c r="J3" t="n">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.016</v>
+        <v>-0.028</v>
       </c>
       <c r="L3" t="n">
         <v>0.425</v>
@@ -3051,14 +3051,14 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.368</v>
+        <v>0.352</v>
       </c>
       <c r="P3" t="n">
-        <v>0.015</v>
+        <v>0.0143</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>razao=0.37 &lt; 0.6 | M=-0.02 — ativo foi contra, tese falhou</t>
+          <t>razao=0.35 &lt; 0.6 | M=-0.03 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
@@ -3096,13 +3096,13 @@
         <v>10.35</v>
       </c>
       <c r="I4" t="n">
-        <v>11.23</v>
+        <v>11.11</v>
       </c>
       <c r="J4" t="n">
-        <v>8.5</v>
+        <v>7.34</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.662</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>0.49</v>
@@ -3114,14 +3114,14 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.527</v>
+        <v>0.416</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0323</v>
+        <v>0.0249</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>razao=0.53 &lt; 0.6 | M=-0.66 — ativo foi contra, tese falhou</t>
+          <t>razao=0.42 &lt; 0.6 | M=-0.56 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
@@ -3222,13 +3222,13 @@
         <v>12.8</v>
       </c>
       <c r="I6" t="n">
-        <v>13.31</v>
+        <v>13.23</v>
       </c>
       <c r="J6" t="n">
-        <v>3.98</v>
+        <v>3.36</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.368</v>
+        <v>-0.27</v>
       </c>
       <c r="L6" t="n">
         <v>0.49</v>
@@ -3240,14 +3240,14 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.217</v>
+        <v>0.092</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0039</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>razao=0.22 &lt; 0.6 | M=-0.37 — ativo foi contra, tese falhou</t>
+          <t>razao=0.09 &lt; 0.6 | M=-0.27 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3285,13 @@
         <v>73.15000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>75.22</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>2.83</v>
+        <v>3.27</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.168</v>
+        <v>-0.23</v>
       </c>
       <c r="L7" t="n">
         <v>0.425</v>
@@ -3303,93 +3303,93 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.371</v>
+        <v>0.434</v>
       </c>
       <c r="P7" t="n">
-        <v>0.017</v>
+        <v>0.0198</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>razao=0.37 &lt; 0.6 | M=-0.17 — ativo foi contra, tese falhou</t>
+          <t>razao=0.43 &lt; 0.6 | M=-0.23 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SINAL INVERTIDO (fim horizonte)</t>
+          <t>SINAL FRACO (reverter)</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46209</v>
+        <v>46230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>naked_30</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>13.88</v>
+        <v>7.94</v>
       </c>
       <c r="I8" t="n">
-        <v>11.92</v>
+        <v>8.18</v>
       </c>
       <c r="J8" t="n">
-        <v>-14.12</v>
+        <v>3.02</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.386</v>
+        <v>-0.025</v>
       </c>
       <c r="L8" t="n">
-        <v>0.751</v>
+        <v>0.49</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.181</v>
+        <v>-0.32</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.129</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0447</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Modelo virou PUT mas restam 4d — previsão cobre 20d, maioria pós-vencimento | M=-1.39 | razao=1.13</t>
+          <t>razao=0.56 &lt; 0.6 | M=-0.03 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MANTER</t>
+          <t>SINAL INVERTIDO (fim horizonte)</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46230</v>
+        <v>46209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3398,52 +3398,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>naked_30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>18.71</v>
+        <v>13.88</v>
       </c>
       <c r="I9" t="n">
-        <v>18.87</v>
+        <v>11.83</v>
       </c>
       <c r="J9" t="n">
-        <v>0.86</v>
+        <v>-14.77</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.034</v>
+        <v>-1.457</v>
       </c>
       <c r="L9" t="n">
-        <v>0.49</v>
+        <v>0.751</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.32</v>
+        <v>-0.181</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.542</v>
+        <v>1.213</v>
       </c>
       <c r="P9" t="n">
-        <v>0.059</v>
+        <v>-0.0824</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>M=-0.03 | razao=1.54 | 1/20d</t>
+          <t>Modelo virou PUT mas restam 4d — previsão cobre 20d, maioria pós-vencimento | M=-1.46 | razao=1.21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3471,42 +3471,42 @@
         <v>19</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8100000000000001</v>
+        <v>18.71</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8100000000000001</v>
+        <v>18.81</v>
       </c>
       <c r="J10" t="n">
-        <v>-0</v>
+        <v>0.53</v>
       </c>
       <c r="K10" t="n">
-        <v>0.238</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>0.49</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.252</v>
+        <v>-0.32</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.769</v>
+        <v>1.476</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1965</v>
+        <v>0.0561</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>M=0.24 | razao=1.77 | 1/20d</t>
+          <t>M=-0.09 | razao=1.48 | 1/20d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EZTC3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3528,48 +3528,48 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>11.4</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>11.61</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>1.84</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.004</v>
+        <v>0.238</v>
       </c>
       <c r="L11" t="n">
         <v>0.49</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.32</v>
+        <v>-0.252</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.252</v>
+        <v>1.769</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.1966</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>M=0.00 | razao=1.25 | 2/20d</t>
+          <t>M=0.24 | razao=1.77 | 1/20d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PETR3</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3578,61 +3578,61 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46219</v>
+        <v>46227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>naked_30</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>44.64</v>
+        <v>11.4</v>
       </c>
       <c r="I12" t="n">
-        <v>46.48</v>
+        <v>11.52</v>
       </c>
       <c r="J12" t="n">
-        <v>4.12</v>
+        <v>1.05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.347</v>
+        <v>0.089</v>
       </c>
       <c r="L12" t="n">
-        <v>0.751</v>
+        <v>0.49</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.181</v>
+        <v>-0.32</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.911</v>
+        <v>1.362</v>
       </c>
       <c r="P12" t="n">
-        <v>0.05</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>M=0.35 | razao=0.91 | 8/20d</t>
+          <t>M=0.09 | razao=1.36 | 2/20d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>PETR3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3641,61 +3641,61 @@
         </is>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>naked_30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>5.27</v>
+        <v>44.64</v>
       </c>
       <c r="I13" t="n">
-        <v>5.36</v>
+        <v>46.38</v>
       </c>
       <c r="J13" t="n">
-        <v>1.71</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>0.007</v>
+        <v>0.323</v>
       </c>
       <c r="L13" t="n">
-        <v>0.49</v>
+        <v>0.751</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.32</v>
+        <v>-0.181</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.0423</v>
+        <v>0.0513</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>M=0.01 | razao=0.81 | 1/20d</t>
+          <t>M=0.32 | razao=0.94 | 8/20d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3723,16 +3723,16 @@
         <v>19</v>
       </c>
       <c r="H14" t="n">
-        <v>7.94</v>
+        <v>5.27</v>
       </c>
       <c r="I14" t="n">
-        <v>8.08</v>
+        <v>5.33</v>
       </c>
       <c r="J14" t="n">
-        <v>1.76</v>
+        <v>1.14</v>
       </c>
       <c r="K14" t="n">
-        <v>0.067</v>
+        <v>0.073</v>
       </c>
       <c r="L14" t="n">
         <v>0.49</v>
@@ -3744,14 +3744,14 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.666</v>
+        <v>0.906</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0512</v>
+        <v>-0.0464</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>M=0.07 | razao=0.67 | 1/20d</t>
+          <t>M=0.07 | razao=0.91 | 1/20d</t>
         </is>
       </c>
     </row>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3162</v>
+        <v>0.3095</v>
       </c>
       <c r="D2" t="n">
-        <v>1.116637</v>
+        <v>1.103892</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.245</v>
+        <v>0.2446</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3957,13 +3957,13 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.0137</v>
+        <v>0.0136</v>
       </c>
       <c r="S2" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="T2" t="n">
-        <v>24.3</v>
+        <v>23.8</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>0.2154</v>
       </c>
       <c r="D3" t="n">
-        <v>1.162918</v>
+        <v>1.152624</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>63.2</v>
       </c>
       <c r="T3" t="n">
-        <v>73.5</v>
+        <v>72.8</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3289</v>
+        <v>0.3128</v>
       </c>
       <c r="D4" t="n">
-        <v>1.098742</v>
+        <v>1.107465</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4147,13 +4147,13 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.0188</v>
+        <v>0.0183</v>
       </c>
       <c r="S4" t="n">
-        <v>29.8</v>
+        <v>29.1</v>
       </c>
       <c r="T4" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -4164,19 +4164,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alerta CALL (VETADA)</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2245</v>
+        <v>0.2226</v>
       </c>
       <c r="D5" t="n">
-        <v>1.153469</v>
+        <v>1.159549</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-0.0577</v>
+        <v>-0.1354</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.0231</v>
+        <v>0.011</v>
       </c>
       <c r="S5" t="n">
-        <v>36.7</v>
+        <v>17.5</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>20.2</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -4227,19 +4227,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Compra CALL (VETADA)</t>
+          <t>Alerta CALL (VETADA)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2936</v>
+        <v>0.2245</v>
       </c>
       <c r="D6" t="n">
-        <v>1.141632</v>
+        <v>1.146744</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-0.1354</v>
+        <v>-0.0577</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4273,13 +4273,13 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.012</v>
+        <v>0.0231</v>
       </c>
       <c r="S6" t="n">
-        <v>19</v>
+        <v>36.7</v>
       </c>
       <c r="T6" t="n">
-        <v>21.7</v>
+        <v>42.1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -4947,13 +4947,13 @@
         <v>-0.153</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0169</v>
+        <v>0.0168</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4342</v>
+        <v>0.4317</v>
       </c>
       <c r="AH2" t="n">
-        <v>41.26</v>
+        <v>41.15</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -4962,13 +4962,13 @@
         <v>-0.0113</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0468</v>
+        <v>0.043759</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.939721</v>
+        <v>0.936111</v>
       </c>
       <c r="AM2" t="n">
-        <v>-6.03</v>
+        <v>-6.39</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4998,10 +4998,10 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.047078</v>
+        <v>0.046941</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.9941</v>
+        <v>0.9322</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.5215</v>
+        <v>0.5158</v>
       </c>
       <c r="CQ2" t="n">
         <v>0</v>
@@ -5280,13 +5280,13 @@
         <v>0.219</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0221</v>
+        <v>0.0209</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1206</v>
+        <v>0.0898</v>
       </c>
       <c r="AH3" t="n">
-        <v>41.86</v>
+        <v>42.41</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -5295,13 +5295,13 @@
         <v>0.0304</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.093568</v>
+        <v>0.107101</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.148604</v>
+        <v>1.214613</v>
       </c>
       <c r="AM3" t="n">
-        <v>14.86</v>
+        <v>21.46</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -5331,10 +5331,10 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.061793</v>
+        <v>0.05832</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.5142</v>
+        <v>1.8364</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.5903</v>
+        <v>0.6286</v>
       </c>
       <c r="CQ3" t="n">
         <v>0</v>
@@ -5609,13 +5609,13 @@
         <v>0.3812</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0128</v>
+        <v>0.0127</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3575</v>
+        <v>0.3555</v>
       </c>
       <c r="AH4" t="n">
-        <v>42.9</v>
+        <v>42.85</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -5624,13 +5624,13 @@
         <v>0.0011</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.011089</v>
+        <v>0.0097</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.03149</v>
+        <v>1.034993</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.035645</v>
+        <v>0.035573</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.3111</v>
+        <v>0.2727</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -5815,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.4781</v>
+        <v>0.4746</v>
       </c>
       <c r="CQ4" t="n">
         <v>0</v>
@@ -5942,13 +5942,13 @@
         <v>0.2479</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0164</v>
+        <v>0.0163</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5454</v>
+        <v>0.5405</v>
       </c>
       <c r="AH5" t="n">
-        <v>75.22</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -5957,13 +5957,13 @@
         <v>0.2323</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.017021</v>
+        <v>0.019769</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.943889</v>
+        <v>0.936077</v>
       </c>
       <c r="AM5" t="n">
-        <v>-5.61</v>
+        <v>-6.39</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -5993,10 +5993,10 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.045822</v>
+        <v>0.045548</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.3714</v>
+        <v>0.434</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -6148,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.4292</v>
+        <v>0.4365</v>
       </c>
       <c r="CQ5" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>0.3564</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9012</v>
+        <v>0.9003</v>
       </c>
       <c r="O6" t="n">
         <v>0.1617</v>
@@ -6241,7 +6241,7 @@
         <v>398</v>
       </c>
       <c r="T6" t="n">
-        <v>0.245</v>
+        <v>0.2446</v>
       </c>
       <c r="U6" t="n">
         <v>0.0489</v>
@@ -6258,16 +6258,16 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>0.3283</v>
+        <v>0.3279</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.0258</v>
+        <v>1.0247</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.244</v>
+        <v>0.2436</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3283</v>
+        <v>0.3279</v>
       </c>
       <c r="AC6" t="n">
         <v>0.0706</v>
@@ -6276,31 +6276,31 @@
         <v>0.0919</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1461</v>
+        <v>0.1457</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0137</v>
+        <v>0.0136</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.3162</v>
+        <v>0.3095</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.87</v>
+        <v>18.81</v>
       </c>
       <c r="AI6" t="n">
-        <v>19.47</v>
+        <v>19.41</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0999</v>
+        <v>0.0998</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.059038</v>
+        <v>0.056146</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.116637</v>
+        <v>1.103892</v>
       </c>
       <c r="AM6" t="n">
-        <v>11.66</v>
+        <v>10.39</v>
       </c>
       <c r="AN6" t="n">
         <v>1</v>
@@ -6330,10 +6330,10 @@
         <v>1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.038286</v>
+        <v>0.038034</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.542</v>
+        <v>1.4762</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -6485,10 +6485,10 @@
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.585</v>
+        <v>0.5798</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.585</v>
+        <v>0.5798</v>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
@@ -6660,13 +6660,13 @@
         <v>-0.0296</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0211</v>
+        <v>0.0218</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.3656</v>
+        <v>0.3916</v>
       </c>
       <c r="AH7" t="n">
-        <v>15.93</v>
+        <v>16.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -6675,13 +6675,13 @@
         <v>0.0017</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.046149</v>
+        <v>0.046041</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.99451</v>
+        <v>0.98431</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.55</v>
+        <v>-1.57</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -6711,10 +6711,10 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.058995</v>
+        <v>0.060823</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.7822</v>
+        <v>0.757</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -6866,7 +6866,7 @@
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.4676</v>
+        <v>0.4598</v>
       </c>
       <c r="CQ7" t="n">
         <v>0</v>
@@ -6993,13 +6993,13 @@
         <v>0.0402</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0319</v>
+        <v>0.0331</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.2815</v>
+        <v>0.336</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.88</v>
+        <v>4.99</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -7008,13 +7008,13 @@
         <v>0.0474</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.008691000000000001</v>
+        <v>0.028157</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.120849</v>
+        <v>1.111344</v>
       </c>
       <c r="AM8" t="n">
-        <v>12.08</v>
+        <v>11.13</v>
       </c>
       <c r="AN8" t="n">
         <v>1</v>
@@ -7044,10 +7044,10 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.088973</v>
+        <v>0.09245299999999999</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0977</v>
+        <v>0.3046</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -7199,7 +7199,7 @@
         <v>1</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.4507</v>
+        <v>0.4604</v>
       </c>
       <c r="CQ8" t="n">
         <v>0</v>
@@ -7326,13 +7326,13 @@
         <v>-0.0119</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0197</v>
+        <v>0.0196</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.4819</v>
+        <v>0.479</v>
       </c>
       <c r="AH9" t="n">
-        <v>46.48</v>
+        <v>46.38</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -7341,13 +7341,13 @@
         <v>0.0276</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.050004</v>
+        <v>0.051305</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.959045</v>
+        <v>0.953448</v>
       </c>
       <c r="AM9" t="n">
-        <v>-4.1</v>
+        <v>-4.66</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -7377,10 +7377,10 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.054891</v>
+        <v>0.054714</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.911</v>
+        <v>0.9377</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.5098</v>
+        <v>0.513</v>
       </c>
       <c r="CQ9" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0.4604</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.74</v>
+        <v>13.73</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -7674,13 +7674,13 @@
         <v>0.0076</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.01497</v>
+        <v>0.014305</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.987298</v>
+        <v>0.98791</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1.27</v>
+        <v>-1.21</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -7710,10 +7710,10 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.040686</v>
+        <v>0.040688</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3679</v>
+        <v>0.3516</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -7865,7 +7865,7 @@
         <v>1</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.4406</v>
+        <v>0.439</v>
       </c>
       <c r="CQ10" t="n">
         <v>0</v>
@@ -7992,13 +7992,13 @@
         <v>0.165</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0154</v>
+        <v>0.0165</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.3252</v>
+        <v>0.3948</v>
       </c>
       <c r="AH11" t="n">
-        <v>24.8</v>
+        <v>25.14</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -8007,13 +8007,13 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.147852</v>
+        <v>0.160118</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.891917</v>
+        <v>0.853546</v>
       </c>
       <c r="AM11" t="n">
-        <v>-10.81</v>
+        <v>-14.65</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -8043,10 +8043,10 @@
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.042967</v>
+        <v>0.045989</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.441</v>
+        <v>3.4816</v>
       </c>
       <c r="AY11" t="n">
         <v>1</v>
@@ -8198,7 +8198,7 @@
         <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.587</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="CQ11" t="n">
         <v>0</v>
@@ -8348,13 +8348,13 @@
         <v>-0.0072</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.06382</v>
+        <v>0.063786</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.153469</v>
+        <v>1.146744</v>
       </c>
       <c r="AM12" t="n">
-        <v>15.35</v>
+        <v>14.67</v>
       </c>
       <c r="AN12" t="n">
         <v>1</v>
@@ -8387,7 +8387,7 @@
         <v>0.06454500000000001</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.9888</v>
+        <v>0.9882</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -8539,10 +8539,10 @@
         <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.5538</v>
+        <v>0.5537</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.5538</v>
+        <v>0.5537</v>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
@@ -8682,13 +8682,13 @@
         <v>-0.008</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0217</v>
+        <v>0.0223</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.3084</v>
+        <v>0.3386</v>
       </c>
       <c r="AH13" t="n">
-        <v>13.83</v>
+        <v>13.99</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -8697,13 +8697,13 @@
         <v>-0.0038</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.012007</v>
+        <v>-0.005901</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.001307</v>
+        <v>0.985306</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.13</v>
+        <v>-1.47</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -8733,10 +8733,10 @@
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.06044</v>
+        <v>0.062153</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1987</v>
+        <v>0.0949</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -8884,7 +8884,7 @@
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.4861</v>
+        <v>0.4697</v>
       </c>
       <c r="CQ13" t="n">
         <v>0</v>
@@ -9011,13 +9011,13 @@
         <v>0.0311</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0144</v>
+        <v>0.0146</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.5859</v>
+        <v>0.5986</v>
       </c>
       <c r="AH14" t="n">
-        <v>40.92</v>
+        <v>41.04</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -9026,13 +9026,13 @@
         <v>0.008</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.02066</v>
+        <v>0.019764</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.965649</v>
+        <v>0.906312</v>
       </c>
       <c r="AM14" t="n">
-        <v>-3.44</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -9062,10 +9062,10 @@
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.040163</v>
+        <v>0.040635</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.5144</v>
+        <v>0.4864</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -9213,7 +9213,7 @@
         <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.2997</v>
+        <v>0.2943</v>
       </c>
       <c r="CQ14" t="n">
         <v>0</v>
@@ -9268,7 +9268,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:instabilidade_gap_alto</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -9287,7 +9287,7 @@
         <v>2.0772</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1709</v>
+        <v>1.1777</v>
       </c>
       <c r="P15" t="n">
         <v>0.3561</v>
@@ -9340,13 +9340,13 @@
         <v>0.3815</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0368</v>
+        <v>0.0389</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2099</v>
+        <v>0.2286</v>
       </c>
       <c r="AH15" t="n">
-        <v>10.37</v>
+        <v>10.64</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -9355,13 +9355,13 @@
         <v>0.3831</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.084782</v>
+        <v>-0.06748700000000001</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.067974</v>
+        <v>1.009227</v>
       </c>
       <c r="AM15" t="n">
-        <v>6.8</v>
+        <v>0.92</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.10275</v>
+        <v>0.108441</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.6223</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -9546,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.5211</v>
+        <v>0.4971</v>
       </c>
       <c r="CQ15" t="n">
         <v>0</v>
@@ -9677,13 +9677,13 @@
         <v>-0.1003</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0288</v>
+        <v>0.0289</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.3327</v>
+        <v>0.3378</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -9692,22 +9692,22 @@
         <v>-0.0147</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.016082</v>
+        <v>-0.01397</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.082663</v>
+        <v>1.070378</v>
       </c>
       <c r="AM16" t="n">
-        <v>8.27</v>
+        <v>7.04</v>
       </c>
       <c r="AN16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -9728,10 +9728,10 @@
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.080308</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.2003</v>
+        <v>0.1731</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>expansao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BC16" t="n">
@@ -9883,7 +9883,7 @@
         <v>1</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.4551</v>
+        <v>0.4514</v>
       </c>
       <c r="CQ16" t="n">
         <v>0</v>
@@ -9960,13 +9960,13 @@
         <v>0.2096</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1527</v>
+        <v>-0.1523</v>
       </c>
       <c r="Q17" t="n">
         <v>436</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0388</v>
+        <v>0.0461</v>
       </c>
       <c r="S17" t="n">
         <v>319</v>
@@ -10014,13 +10014,13 @@
         <v>-0.0331</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0148</v>
+        <v>0.0142</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.1355</v>
+        <v>0.1202</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.3</v>
+        <v>16.24</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -10029,13 +10029,13 @@
         <v>0.0067</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.029962</v>
+        <v>0.028871</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.225198</v>
+        <v>1.194306</v>
       </c>
       <c r="AM17" t="n">
-        <v>22.52</v>
+        <v>19.43</v>
       </c>
       <c r="AN17" t="n">
         <v>1</v>
@@ -10065,10 +10065,10 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.041256</v>
+        <v>0.039681</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7276</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -10220,7 +10220,7 @@
         <v>0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.4948</v>
+        <v>0.498</v>
       </c>
       <c r="CQ17" t="n">
         <v>0</v>
@@ -10350,13 +10350,13 @@
         <v>-0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.173394</v>
+        <v>0.173187</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.914203</v>
+        <v>0.921991</v>
       </c>
       <c r="AM18" t="n">
-        <v>-8.58</v>
+        <v>-7.8</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -10389,7 +10389,7 @@
         <v>0.093794</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.8487</v>
+        <v>1.8465</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -10537,7 +10537,7 @@
         <v>1</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.5958</v>
+        <v>0.5956</v>
       </c>
       <c r="CQ18" t="n">
         <v>0</v>
@@ -10611,7 +10611,7 @@
         <v>2.3202</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1656</v>
+        <v>0.1807</v>
       </c>
       <c r="P19" t="n">
         <v>-0.0107</v>
@@ -10664,13 +10664,13 @@
         <v>0.2198</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.0135</v>
+        <v>0.0129</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5477</v>
+        <v>0.4999</v>
       </c>
       <c r="AH19" t="n">
-        <v>40.48</v>
+        <v>39.9</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -10679,13 +10679,13 @@
         <v>0.1402</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.004004</v>
+        <v>-0.008932000000000001</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.887205</v>
+        <v>0.918605</v>
       </c>
       <c r="AM19" t="n">
-        <v>-11.28</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -10715,10 +10715,10 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.037796</v>
+        <v>0.035882</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.1059</v>
+        <v>0.2489</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -10866,7 +10866,7 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.3639</v>
+        <v>0.3877</v>
       </c>
       <c r="CQ19" t="n">
         <v>0</v>
@@ -10993,13 +10993,13 @@
         <v>0.1336</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0235</v>
+        <v>0.0232</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.2556</v>
+        <v>0.2506</v>
       </c>
       <c r="AH20" t="n">
-        <v>21.6</v>
+        <v>21.52</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -11008,13 +11008,13 @@
         <v>0.0218</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.033714</v>
+        <v>-0.036269</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.972905</v>
+        <v>0.975308</v>
       </c>
       <c r="AM20" t="n">
-        <v>-2.71</v>
+        <v>-2.47</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -11044,10 +11044,10 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.065454</v>
+        <v>0.064757</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.5151</v>
+        <v>0.5601</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -11199,7 +11199,7 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.4516</v>
+        <v>0.4571</v>
       </c>
       <c r="CQ20" t="n">
         <v>0</v>
@@ -11254,7 +11254,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:har_fallback_moderado</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -11330,13 +11330,13 @@
         <v>0.0421</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.0191</v>
+        <v>0.0184</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.1145</v>
+        <v>0.0985</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.52</v>
+        <v>18.22</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -11345,13 +11345,13 @@
         <v>0.0114</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.050616</v>
+        <v>0.040335</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.058592</v>
+        <v>1.078531</v>
       </c>
       <c r="AM21" t="n">
-        <v>5.86</v>
+        <v>7.85</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -11381,10 +11381,10 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.053354</v>
+        <v>0.051313</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.9487</v>
+        <v>0.7861</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -11536,7 +11536,7 @@
         <v>1</v>
       </c>
       <c r="CP21" t="n">
-        <v>0.5458</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="CQ21" t="n">
         <v>0</v>
@@ -11663,13 +11663,13 @@
         <v>0.1537</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.0219</v>
+        <v>0.0215</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.2955</v>
+        <v>0.2776</v>
       </c>
       <c r="AH22" t="n">
-        <v>11.23</v>
+        <v>11.11</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -11678,13 +11678,13 @@
         <v>0.0528</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.032258</v>
+        <v>0.024895</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.021625</v>
+        <v>1.081879</v>
       </c>
       <c r="AM22" t="n">
-        <v>2.16</v>
+        <v>8.19</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -11714,10 +11714,10 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.061242</v>
+        <v>0.059878</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.4158</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -11865,7 +11865,7 @@
         <v>0</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.432</v>
+        <v>0.4244</v>
       </c>
       <c r="CQ22" t="n">
         <v>0</v>
@@ -11996,13 +11996,13 @@
         <v>-0.053</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0171</v>
+        <v>0.0167</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.3466</v>
+        <v>0.3281</v>
       </c>
       <c r="AH23" t="n">
-        <v>29.26</v>
+        <v>28.69</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -12011,19 +12011,19 @@
         <v>-0.017</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.010942</v>
+        <v>-0.021845</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.007212</v>
+        <v>1.035398</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.72</v>
+        <v>3.54</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -12047,10 +12047,10 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.047787</v>
+        <v>0.046571</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.229</v>
+        <v>0.4691</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -12202,7 +12202,7 @@
         <v>1</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.4612</v>
+        <v>0.4889</v>
       </c>
       <c r="CQ23" t="n">
         <v>0</v>
@@ -12329,13 +12329,13 @@
         <v>0.1303</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0151</v>
+        <v>0.0155</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.285</v>
+        <v>0.3153</v>
       </c>
       <c r="AH24" t="n">
-        <v>10.76</v>
+        <v>10.86</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -12344,13 +12344,13 @@
         <v>0.0477</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.121291</v>
+        <v>0.128614</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.110869</v>
+        <v>1.107444</v>
       </c>
       <c r="AM24" t="n">
-        <v>11.09</v>
+        <v>10.74</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
@@ -12380,10 +12380,10 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.042033</v>
+        <v>0.043248</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.8856</v>
+        <v>2.9738</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.6025</v>
+        <v>0.5965</v>
       </c>
       <c r="CQ24" t="n">
         <v>0</v>
@@ -12666,13 +12666,13 @@
         <v>0.0626</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0198</v>
+        <v>0.0196</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.6846</v>
+        <v>0.6679</v>
       </c>
       <c r="AH25" t="n">
-        <v>30.28</v>
+        <v>30.06</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -12681,13 +12681,13 @@
         <v>0.0061</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.019665</v>
+        <v>-0.021373</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.934184</v>
+        <v>0.935563</v>
       </c>
       <c r="AM25" t="n">
-        <v>-6.58</v>
+        <v>-6.44</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -12717,10 +12717,10 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.055339</v>
+        <v>0.05462</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.3553</v>
+        <v>0.3913</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -12872,7 +12872,7 @@
         <v>1</v>
       </c>
       <c r="CP25" t="n">
-        <v>0.3952</v>
+        <v>0.4021</v>
       </c>
       <c r="CQ25" t="n">
         <v>0</v>
@@ -12999,13 +12999,13 @@
         <v>0.139</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0173</v>
+        <v>0.0171</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.5754</v>
+        <v>0.5662</v>
       </c>
       <c r="AH26" t="n">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -13014,13 +13014,13 @@
         <v>0.1666</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.009042</v>
+        <v>0.01477</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.931169</v>
+        <v>0.91444</v>
       </c>
       <c r="AM26" t="n">
-        <v>-6.88</v>
+        <v>-8.56</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
@@ -13050,10 +13050,10 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.048219</v>
+        <v>0.047709</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.1875</v>
+        <v>0.3096</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -13205,7 +13205,7 @@
         <v>0</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.3719</v>
+        <v>0.386</v>
       </c>
       <c r="CQ26" t="n">
         <v>0</v>
@@ -13336,13 +13336,13 @@
         <v>-0.222</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0387</v>
+        <v>0.0386</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.2429</v>
+        <v>0.2407</v>
       </c>
       <c r="AH27" t="n">
-        <v>6.12</v>
+        <v>6.04</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -13351,13 +13351,13 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.031747</v>
+        <v>-0.044544</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.98084</v>
+        <v>0.999688</v>
       </c>
       <c r="AM27" t="n">
-        <v>-1.92</v>
+        <v>-0.03</v>
       </c>
       <c r="AN27" t="n">
         <v>0</v>
@@ -13387,10 +13387,10 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.108117</v>
+        <v>0.107703</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.2936</v>
+        <v>0.4136</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -13538,7 +13538,7 @@
         <v>0</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.4514</v>
+        <v>0.4639</v>
       </c>
       <c r="CQ27" t="n">
         <v>0</v>
@@ -13669,13 +13669,13 @@
         <v>0.0243</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0245</v>
+        <v>0.0243</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.5396</v>
+        <v>0.532</v>
       </c>
       <c r="AH28" t="n">
-        <v>11.92</v>
+        <v>11.83</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -13684,13 +13684,13 @@
         <v>0.0165</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.07730099999999999</v>
+        <v>-0.082368</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.053869</v>
+        <v>1.060221</v>
       </c>
       <c r="AM28" t="n">
-        <v>5.39</v>
+        <v>6.02</v>
       </c>
       <c r="AN28" t="n">
         <v>0</v>
@@ -13720,10 +13720,10 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.06845999999999999</v>
+        <v>0.06790400000000001</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.1291</v>
+        <v>1.213</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -13871,7 +13871,7 @@
         <v>0</v>
       </c>
       <c r="CP28" t="n">
-        <v>0.4534</v>
+        <v>0.4633</v>
       </c>
       <c r="CQ28" t="n">
         <v>0</v>
@@ -14002,13 +14002,13 @@
         <v>-0.06850000000000001</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.0208</v>
+        <v>0.0206</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.2224</v>
+        <v>0.2145</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -14017,13 +14017,13 @@
         <v>-0.0028</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.023771</v>
+        <v>-0.028262</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.112218</v>
+        <v>1.121596</v>
       </c>
       <c r="AM29" t="n">
-        <v>11.22</v>
+        <v>12.16</v>
       </c>
       <c r="AN29" t="n">
         <v>0</v>
@@ -14053,10 +14053,10 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.058127</v>
+        <v>0.057399</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.409</v>
+        <v>0.4924</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -14204,7 +14204,7 @@
         <v>0</v>
       </c>
       <c r="CP29" t="n">
-        <v>0.4822</v>
+        <v>0.4921</v>
       </c>
       <c r="CQ29" t="n">
         <v>0</v>
@@ -14335,28 +14335,28 @@
         <v>0.1138</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0188</v>
+        <v>0.0183</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.3289</v>
+        <v>0.3128</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.13</v>
+        <v>5.1</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.0408</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.042337</v>
+        <v>-0.046389</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.098742</v>
+        <v>1.107465</v>
       </c>
       <c r="AM30" t="n">
-        <v>9.869999999999999</v>
+        <v>10.75</v>
       </c>
       <c r="AN30" t="n">
         <v>1</v>
@@ -14386,10 +14386,10 @@
         <v>-1</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.052471</v>
+        <v>0.051205</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.8069</v>
+        <v>0.9059</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -14541,10 +14541,10 @@
         <v>1</v>
       </c>
       <c r="CP30" t="n">
-        <v>0.525</v>
+        <v>0.5381</v>
       </c>
       <c r="CQ30" t="n">
-        <v>0.525</v>
+        <v>0.5381</v>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
@@ -14716,13 +14716,13 @@
         <v>0.0533</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0181</v>
+        <v>0.0182</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.4845</v>
+        <v>0.4899</v>
       </c>
       <c r="AH31" t="n">
-        <v>14.99</v>
+        <v>15.01</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -14731,13 +14731,13 @@
         <v>0.0452</v>
       </c>
       <c r="AK31" t="n">
-        <v>3.3e-05</v>
+        <v>0.000348</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.13288</v>
+        <v>1.132804</v>
       </c>
       <c r="AM31" t="n">
-        <v>13.29</v>
+        <v>13.28</v>
       </c>
       <c r="AN31" t="n">
         <v>1</v>
@@ -14767,10 +14767,10 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.050463</v>
+        <v>0.050728</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0069</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -14918,7 +14918,7 @@
         <v>0</v>
       </c>
       <c r="CP31" t="n">
-        <v>0.3319</v>
+        <v>0.3315</v>
       </c>
       <c r="CQ31" t="n">
         <v>0</v>
@@ -14993,7 +14993,7 @@
         <v>0.0702</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2666</v>
+        <v>0.2667</v>
       </c>
       <c r="O32" t="n">
         <v>-0.18</v>
@@ -15053,28 +15053,28 @@
         <v>-0.1207</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.2936</v>
+        <v>0.2226</v>
       </c>
       <c r="AH32" t="n">
-        <v>18.15</v>
+        <v>18.04</v>
       </c>
       <c r="AI32" t="n">
-        <v>18.66</v>
+        <v>18.5</v>
       </c>
       <c r="AJ32" t="n">
         <v>-0.0128</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.049109</v>
+        <v>0.053369</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.141632</v>
+        <v>1.159549</v>
       </c>
       <c r="AM32" t="n">
-        <v>14.16</v>
+        <v>15.95</v>
       </c>
       <c r="AN32" t="n">
         <v>1</v>
@@ -15104,10 +15104,10 @@
         <v>1</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.033483</v>
+        <v>0.030743</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.4667</v>
+        <v>1.736</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -15255,10 +15255,10 @@
         <v>0</v>
       </c>
       <c r="CP32" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="CQ32" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="CR32" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>1.4798</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5298</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="P33" t="n">
         <v>0.1278</v>
@@ -15376,7 +15376,7 @@
         <v>0.509</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.5907</v>
+        <v>1.5906</v>
       </c>
       <c r="AA33" t="n">
         <v>0.4829</v>
@@ -15394,13 +15394,13 @@
         <v>0.0979</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.0166</v>
+        <v>0.0164</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.3845</v>
+        <v>0.3735</v>
       </c>
       <c r="AH33" t="n">
-        <v>27.21</v>
+        <v>27.13</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -15409,13 +15409,13 @@
         <v>0.0106</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.013419</v>
+        <v>-0.015156</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.872796</v>
+        <v>0.905174</v>
       </c>
       <c r="AM33" t="n">
-        <v>-12.72</v>
+        <v>-9.48</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
@@ -15445,10 +15445,10 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.046286</v>
+        <v>0.045645</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.2899</v>
+        <v>0.332</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -15600,7 +15600,7 @@
         <v>1</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.416</v>
+        <v>0.4224</v>
       </c>
       <c r="CQ33" t="n">
         <v>0</v>
@@ -15671,7 +15671,7 @@
         <v>0.2917</v>
       </c>
       <c r="N34" t="n">
-        <v>2.1845</v>
+        <v>2.1808</v>
       </c>
       <c r="O34" t="n">
         <v>2.2783</v>
@@ -15689,10 +15689,10 @@
         <v>294</v>
       </c>
       <c r="T34" t="n">
-        <v>0.5723</v>
+        <v>0.5712</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2346</v>
+        <v>0.2342</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -15706,16 +15706,16 @@
       </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>0.5713</v>
+        <v>0.5702</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.1565</v>
+        <v>3.1501</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.5713</v>
+        <v>0.5702</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.5596</v>
+        <v>0.5584</v>
       </c>
       <c r="AC34" t="n">
         <v>0.0177</v>
@@ -15730,10 +15730,10 @@
         <v>0.0196</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.4093</v>
+        <v>0.4082</v>
       </c>
       <c r="AH34" t="n">
-        <v>32.42</v>
+        <v>32.37</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -15742,13 +15742,13 @@
         <v>0.0276</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.085122</v>
+        <v>0.083985</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.726306</v>
+        <v>0.721759</v>
       </c>
       <c r="AM34" t="n">
-        <v>-27.37</v>
+        <v>-27.82</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
@@ -15778,10 +15778,10 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.054665</v>
+        <v>0.054602</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.5572</v>
+        <v>1.5381</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -15929,7 +15929,7 @@
         <v>0</v>
       </c>
       <c r="CP34" t="n">
-        <v>0.5365</v>
+        <v>0.5349</v>
       </c>
       <c r="CQ34" t="n">
         <v>0</v>
@@ -16060,13 +16060,13 @@
         <v>-0.1594</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.0217</v>
+        <v>0.0221</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.3885</v>
+        <v>0.4047</v>
       </c>
       <c r="AH35" t="n">
-        <v>21.24</v>
+        <v>21.42</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -16075,13 +16075,13 @@
         <v>-0.007900000000000001</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.011244</v>
+        <v>0.013429</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.949411</v>
+        <v>0.930581</v>
       </c>
       <c r="AM35" t="n">
-        <v>-5.06</v>
+        <v>-6.94</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -16111,10 +16111,10 @@
         <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.060587</v>
+        <v>0.06159</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.1856</v>
+        <v>0.218</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -16389,13 +16389,13 @@
         <v>0.0906</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.0172</v>
+        <v>0.017</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.4495</v>
+        <v>0.4375</v>
       </c>
       <c r="AH36" t="n">
-        <v>29.1</v>
+        <v>29.02</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -16404,13 +16404,13 @@
         <v>0.0119</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.000307</v>
+        <v>-0.000387</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.880878</v>
+        <v>0.889769</v>
       </c>
       <c r="AM36" t="n">
-        <v>-11.91</v>
+        <v>-11.02</v>
       </c>
       <c r="AN36" t="n">
         <v>0</v>
@@ -16440,10 +16440,10 @@
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.048067</v>
+        <v>0.047374</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.0064</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
         <v>0</v>
       </c>
       <c r="CP36" t="n">
-        <v>0.3615</v>
+        <v>0.364</v>
       </c>
       <c r="CQ36" t="n">
         <v>0</v>
@@ -16722,13 +16722,13 @@
         <v>0.1978</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.0198</v>
+        <v>0.0203</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.278</v>
+        <v>0.2918</v>
       </c>
       <c r="AH37" t="n">
-        <v>64.06</v>
+        <v>64.64</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -16737,13 +16737,13 @@
         <v>0.0161</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.018584</v>
+        <v>0.024626</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.573437</v>
+        <v>0.6279439999999999</v>
       </c>
       <c r="AM37" t="n">
-        <v>-42.66</v>
+        <v>-37.21</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -16773,10 +16773,10 @@
         <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.05521</v>
+        <v>0.056628</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.3366</v>
+        <v>0.4349</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -16924,7 +16924,7 @@
         <v>0</v>
       </c>
       <c r="CP37" t="n">
-        <v>0.4556</v>
+        <v>0.4627</v>
       </c>
       <c r="CQ37" t="n">
         <v>0</v>
@@ -16979,7 +16979,7 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -17051,13 +17051,13 @@
         <v>0.027</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0276</v>
+        <v>0.0286</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.2527</v>
+        <v>0.2895</v>
       </c>
       <c r="AH38" t="n">
-        <v>8.08</v>
+        <v>8.18</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -17066,13 +17066,13 @@
         <v>0.0095</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.051221</v>
+        <v>-0.044707</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.114748</v>
+        <v>1.100384</v>
       </c>
       <c r="AM38" t="n">
-        <v>11.47</v>
+        <v>10.04</v>
       </c>
       <c r="AN38" t="n">
         <v>1</v>
@@ -17102,10 +17102,10 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.076913</v>
+        <v>0.079887</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.666</v>
+        <v>0.5596</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -17257,7 +17257,7 @@
         <v>1</v>
       </c>
       <c r="CP38" t="n">
-        <v>0.5097</v>
+        <v>0.4917</v>
       </c>
       <c r="CQ38" t="n">
         <v>0</v>
@@ -17384,13 +17384,13 @@
         <v>0.0451</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.015</v>
+        <v>0.0152</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.5218</v>
+        <v>0.5343</v>
       </c>
       <c r="AH39" t="n">
-        <v>13.31</v>
+        <v>13.23</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -17399,13 +17399,13 @@
         <v>0.0251</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.009046</v>
+        <v>0.00389</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.146713</v>
+        <v>1.137394</v>
       </c>
       <c r="AM39" t="n">
-        <v>14.67</v>
+        <v>13.74</v>
       </c>
       <c r="AN39" t="n">
         <v>0</v>
@@ -17435,10 +17435,10 @@
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.04177</v>
+        <v>0.042366</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.2166</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -17590,7 +17590,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>0.3977</v>
+        <v>0.3827</v>
       </c>
       <c r="CQ39" t="n">
         <v>0</v>
@@ -17721,13 +17721,13 @@
         <v>-0.014</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.0256</v>
+        <v>0.0253</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.9226</v>
+        <v>0.9059</v>
       </c>
       <c r="AH40" t="n">
-        <v>27.04</v>
+        <v>26.85</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -17736,13 +17736,13 @@
         <v>0.0107</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.005019</v>
+        <v>0.00384</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.865217</v>
+        <v>0.8711370000000001</v>
       </c>
       <c r="AM40" t="n">
-        <v>-13.48</v>
+        <v>-12.89</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -17772,10 +17772,10 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.071557</v>
+        <v>0.07062599999999999</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.0701</v>
+        <v>0.0544</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -17923,7 +17923,7 @@
         <v>0</v>
       </c>
       <c r="CP40" t="n">
-        <v>0.3068</v>
+        <v>0.3086</v>
       </c>
       <c r="CQ40" t="n">
         <v>0</v>
@@ -18054,13 +18054,13 @@
         <v>-0.08119999999999999</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.0136</v>
+        <v>0.0133</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.2157</v>
+        <v>0.1975</v>
       </c>
       <c r="AH41" t="n">
-        <v>14.84</v>
+        <v>14.79</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -18069,13 +18069,13 @@
         <v>0.0026</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.018574</v>
+        <v>0.01606</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.041764</v>
+        <v>1.060267</v>
       </c>
       <c r="AM41" t="n">
-        <v>4.18</v>
+        <v>6.03</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -18105,10 +18105,10 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.037819</v>
+        <v>0.036996</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.4911</v>
+        <v>0.4341</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -18260,7 +18260,7 @@
         <v>1</v>
       </c>
       <c r="CP41" t="n">
-        <v>0.5259</v>
+        <v>0.5239</v>
       </c>
       <c r="CQ41" t="n">
         <v>0</v>
@@ -18343,7 +18343,7 @@
         <v>436</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.0211</v>
+        <v>-0.017</v>
       </c>
       <c r="S42" t="n">
         <v>325</v>
@@ -18379,25 +18379,25 @@
         <v>0.0335</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.0033</v>
+        <v>0.0039</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.0342</v>
+        <v>-0.0336</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.0548</v>
+        <v>-0.0542</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.0639</v>
+        <v>-0.0633</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.0162</v>
+        <v>0.0163</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.4508</v>
+        <v>0.4602</v>
       </c>
       <c r="AH42" t="n">
-        <v>54.92</v>
+        <v>55.05</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -18406,13 +18406,13 @@
         <v>0.006</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.01532</v>
+        <v>0.015897</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.017944</v>
+        <v>1.013064</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -18442,10 +18442,10 @@
         <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.045222</v>
+        <v>0.045621</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.3388</v>
+        <v>0.3485</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -18597,7 +18597,7 @@
         <v>0</v>
       </c>
       <c r="CP42" t="n">
-        <v>0.4393</v>
+        <v>0.4384</v>
       </c>
       <c r="CQ42" t="n">
         <v>0</v>
@@ -18743,13 +18743,13 @@
         <v>0.067</v>
       </c>
       <c r="AK43" t="n">
-        <v>-0.196543</v>
+        <v>-0.196581</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.162918</v>
+        <v>1.152624</v>
       </c>
       <c r="AM43" t="n">
-        <v>16.29</v>
+        <v>15.26</v>
       </c>
       <c r="AN43" t="n">
         <v>1</v>
@@ -18782,7 +18782,7 @@
         <v>0.111106</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.769</v>
+        <v>1.7693</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -19101,13 +19101,13 @@
         <v>0.1186</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0143</v>
+        <v>0.0156</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.1749</v>
+        <v>0.2181</v>
       </c>
       <c r="AH44" t="n">
-        <v>16.79</v>
+        <v>16.99</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -19116,13 +19116,13 @@
         <v>0.0083</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.043315</v>
+        <v>0.047087</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.175121</v>
+        <v>1.121144</v>
       </c>
       <c r="AM44" t="n">
-        <v>17.51</v>
+        <v>12.11</v>
       </c>
       <c r="AN44" t="n">
         <v>0</v>
@@ -19152,10 +19152,10 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.039979</v>
+        <v>0.043598</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.0834</v>
+        <v>1.08</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
@@ -19307,7 +19307,7 @@
         <v>0</v>
       </c>
       <c r="CP44" t="n">
-        <v>0.5595</v>
+        <v>0.5505</v>
       </c>
       <c r="CQ44" t="n">
         <v>0</v>
@@ -19449,13 +19449,13 @@
         <v>0.0059</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.007142</v>
+        <v>-0.007147</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.056119</v>
+        <v>1.196915</v>
       </c>
       <c r="AM45" t="n">
-        <v>5.61</v>
+        <v>19.69</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -19767,13 +19767,13 @@
         <v>-0.0945</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0202</v>
+        <v>0.0197</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.3491</v>
+        <v>0.322</v>
       </c>
       <c r="AH46" t="n">
-        <v>11.61</v>
+        <v>11.52</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -19782,13 +19782,13 @@
         <v>-0.0075</v>
       </c>
       <c r="AK46" t="n">
-        <v>-0.070549</v>
+        <v>-0.074905</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.094731</v>
+        <v>1.121265</v>
       </c>
       <c r="AM46" t="n">
-        <v>9.470000000000001</v>
+        <v>12.13</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -19818,10 +19818,10 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.056372</v>
+        <v>0.054993</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.2515</v>
+        <v>1.3621</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
         <v>0</v>
       </c>
       <c r="CP46" t="n">
-        <v>0.533</v>
+        <v>0.5495</v>
       </c>
       <c r="CQ46" t="n">
         <v>0</v>
@@ -20100,13 +20100,13 @@
         <v>0.2225</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.0248</v>
+        <v>0.0247</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.4431</v>
+        <v>0.4417</v>
       </c>
       <c r="AH47" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -20115,13 +20115,13 @@
         <v>0.1436</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.008533000000000001</v>
+        <v>-0.01032</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.94677</v>
+        <v>0.959282</v>
       </c>
       <c r="AM47" t="n">
-        <v>-5.32</v>
+        <v>-4.07</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
@@ -20151,10 +20151,10 @@
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.06908</v>
+        <v>0.068967</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.1235</v>
+        <v>0.1496</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -20306,7 +20306,7 @@
         <v>0</v>
       </c>
       <c r="CP47" t="n">
-        <v>0.3673</v>
+        <v>0.3702</v>
       </c>
       <c r="CQ47" t="n">
         <v>0</v>
@@ -20440,10 +20440,10 @@
         <v>0.0287</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.1817</v>
+        <v>0.1803</v>
       </c>
       <c r="AH48" t="n">
-        <v>8.27</v>
+        <v>8.24</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -20452,13 +20452,13 @@
         <v>0.0021</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.057259</v>
+        <v>-0.06118</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.100581</v>
+        <v>1.103492</v>
       </c>
       <c r="AM48" t="n">
-        <v>10.06</v>
+        <v>10.35</v>
       </c>
       <c r="AN48" t="n">
         <v>1</v>
@@ -20488,10 +20488,10 @@
         <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.080112</v>
+        <v>0.079975</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.7147</v>
+        <v>0.765</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
@@ -20639,7 +20639,7 @@
         <v>0</v>
       </c>
       <c r="CP48" t="n">
-        <v>0.4923</v>
+        <v>0.4976</v>
       </c>
       <c r="CQ48" t="n">
         <v>0</v>
@@ -20768,13 +20768,13 @@
         <v>-0.2552</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.0254</v>
+        <v>0.0253</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.5299</v>
+        <v>0.5285</v>
       </c>
       <c r="AH49" t="n">
-        <v>11.55</v>
+        <v>11.54</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -20783,13 +20783,13 @@
         <v>-0.0004</v>
       </c>
       <c r="AK49" t="n">
-        <v>-0.011632</v>
+        <v>-0.012671</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.055021</v>
+        <v>1.055786</v>
       </c>
       <c r="AM49" t="n">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="AN49" t="n">
         <v>0</v>
@@ -20819,10 +20819,10 @@
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.07076300000000001</v>
+        <v>0.07066500000000001</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.1644</v>
+        <v>0.1793</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -20970,7 +20970,7 @@
         <v>0</v>
       </c>
       <c r="CP49" t="n">
-        <v>0.3996</v>
+        <v>0.4014</v>
       </c>
       <c r="CQ49" t="n">
         <v>0</v>
@@ -21103,7 +21103,7 @@
         <v>0.1445</v>
       </c>
       <c r="AH50" t="n">
-        <v>14.07</v>
+        <v>14.1</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -21112,13 +21112,13 @@
         <v>0.0391</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.01832</v>
+        <v>0.020334</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.103393</v>
+        <v>1.103573</v>
       </c>
       <c r="AM50" t="n">
-        <v>10.34</v>
+        <v>10.36</v>
       </c>
       <c r="AN50" t="n">
         <v>1</v>
@@ -21148,10 +21148,10 @@
         <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.040786</v>
+        <v>0.04078</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.4492</v>
+        <v>0.4986</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
@@ -21303,7 +21303,7 @@
         <v>0</v>
       </c>
       <c r="CP50" t="n">
-        <v>0.4622</v>
+        <v>0.4671</v>
       </c>
       <c r="CQ50" t="n">
         <v>0</v>
@@ -40175,7 +40175,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:instabilidade_gap_alto</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -40391,7 +40391,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:har_fallback_moderado</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -41003,7 +41003,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -41653,7 +41653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.5215</v>
+        <v>0.5158</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.5903</v>
+        <v>0.6286</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.4781</v>
+        <v>0.4746</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.4292</v>
+        <v>0.4365</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -41963,7 +41963,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.585</v>
+        <v>0.5798</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.4676</v>
+        <v>0.4598</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -42279,7 +42279,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.4507</v>
+        <v>0.4604</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.5098</v>
+        <v>0.513</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.4406</v>
+        <v>0.439</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.587</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.5538</v>
+        <v>0.5537</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.4861</v>
+        <v>0.4697</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.2997</v>
+        <v>0.2943</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -42963,15 +42963,15 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:instabilidade_gap_alto</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.5211</v>
+        <v>0.4971</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -43079,7 +43079,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.4551</v>
+        <v>0.4514</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>expansao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
     </row>
@@ -43191,7 +43191,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.4948</v>
+        <v>0.498</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.5958</v>
+        <v>0.5956</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -43415,7 +43415,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.3639</v>
+        <v>0.3877</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.4516</v>
+        <v>0.4571</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -43589,15 +43589,15 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>volatility_gate_bloqueado:har_fallback_moderado</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.5458</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -43659,7 +43659,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.432</v>
+        <v>0.4244</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -43725,7 +43725,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.4612</v>
+        <v>0.4889</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.6025</v>
+        <v>0.5965</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.3952</v>
+        <v>0.4021</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.3719</v>
+        <v>0.386</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -44173,7 +44173,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.4514</v>
+        <v>0.4639</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.4534</v>
+        <v>0.4633</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.4822</v>
+        <v>0.4921</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.525</v>
+        <v>0.5381</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.3319</v>
+        <v>0.3315</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.416</v>
+        <v>0.4224</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.5365</v>
+        <v>0.5349</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.3615</v>
+        <v>0.364</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -45569,7 +45569,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.4556</v>
+        <v>0.4627</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>1</v>
@@ -45673,15 +45673,15 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>razao_sinal_baixa</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.5097</v>
+        <v>0.4917</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>fraco</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -45743,7 +45743,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.3977</v>
+        <v>0.3827</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -45851,7 +45851,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.3068</v>
+        <v>0.3086</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.5259</v>
+        <v>0.5239</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.4393</v>
+        <v>0.4384</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.5595</v>
+        <v>0.5505</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.533</v>
+        <v>0.5495</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0.3673</v>
+        <v>0.3702</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0.4923</v>
+        <v>0.4976</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.3996</v>
+        <v>0.4014</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0.4622</v>
+        <v>0.4671</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>

--- a/saidas/ordens_dia/ordem_dia_2026_07_28_executor_v5_5.xlsx
+++ b/saidas/ordens_dia/ordem_dia_2026_07_28_executor_v5_5.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE6"/>
+  <dimension ref="A1:DE5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,10 +1032,10 @@
         <v>0.3564</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9003</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1617</v>
+        <v>0.1563</v>
       </c>
       <c r="Q2" t="n">
         <v>0.1232</v>
@@ -1050,7 +1050,7 @@
         <v>398</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2446</v>
+        <v>0.2444</v>
       </c>
       <c r="V2" t="n">
         <v>0.0489</v>
@@ -1067,49 +1067,49 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.3279</v>
+        <v>0.3277</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.0247</v>
+        <v>1.024</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2436</v>
+        <v>0.2434</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3279</v>
+        <v>0.3277</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0706</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="AE2" t="n">
         <v>0.0919</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1457</v>
+        <v>0.1455</v>
       </c>
       <c r="AG2" t="n">
         <v>0.0136</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.3095</v>
+        <v>0.3076</v>
       </c>
       <c r="AI2" t="n">
-        <v>18.81</v>
+        <v>18.77</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19.41</v>
+        <v>19.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0998</v>
+        <v>0.0997</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.056146</v>
+        <v>0.054728</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.103892</v>
+        <v>1.10471</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.39</v>
+        <v>10.47</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -1139,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.038034</v>
+        <v>0.037963</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.4762</v>
+        <v>1.4416</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.5798</v>
+        <v>0.5767</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.5798</v>
+        <v>0.5767</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.244 | spread_35_20: esp=+0.071 | spread_45_25: esp=+0.092 | spread_45_15: esp=+0.146</t>
+          <t>naked_30: esp=+0.243 | spread_35_20: esp=+0.070 | spread_45_25: esp=+0.092 | spread_45_15: esp=+0.145</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
@@ -1417,7 +1417,7 @@
         <v>0.4426</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2819</v>
+        <v>1.286</v>
       </c>
       <c r="P3" t="n">
         <v>0.7336</v>
@@ -1435,10 +1435,10 @@
         <v>378</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6505</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1186</v>
+        <v>0.1187</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1452,16 +1452,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.8244</v>
+        <v>0.8267</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5762</v>
+        <v>2.5833</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6495</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8244</v>
+        <v>0.8267</v>
       </c>
       <c r="AD3" t="n">
         <v>0.1626</v>
@@ -1473,28 +1473,28 @@
         <v>0.3251</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0398</v>
+        <v>0.0395</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2154</v>
+        <v>0.2112</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.067</v>
+        <v>0.0673</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.196581</v>
+        <v>-0.213894</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.152624</v>
+        <v>1.154009</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.26</v>
+        <v>15.4</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
@@ -1524,10 +1524,10 @@
         <v>-1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.111106</v>
+        <v>0.110244</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.7693</v>
+        <v>1.9402</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1675,10 +1675,10 @@
         <v>1</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.6108</v>
+        <v>0.6287</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.6108</v>
+        <v>0.6287</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.649 | spread_35_20: esp=+0.163 | spread_45_25: esp=+0.211 | spread_45_15: esp=+0.325</t>
+          <t>naked_30: esp=+0.652 | spread_35_20: esp=+0.163 | spread_45_25: esp=+0.211 | spread_45_15: esp=+0.325</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.824 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.827 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
@@ -1751,131 +1751,135 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>VETADA — esperança histórica insuficiente</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2719</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6613</v>
+        <v>0.6512</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3309</v>
+        <v>0.0702</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6983</v>
+        <v>0.2667</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0251</v>
+        <v>-0.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0013</v>
+        <v>-0.058</v>
       </c>
       <c r="R4" t="n">
         <v>436</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0726</v>
+        <v>-0.0722</v>
       </c>
       <c r="T4" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1501</v>
+        <v>-0.1354</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0505</v>
+        <v>0.0178</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>esperanca</t>
+        </is>
+      </c>
       <c r="Z4" t="n">
-        <v>0.2277</v>
+        <v>-0.18</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7117</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1491</v>
+        <v>-0.1364</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2277</v>
+        <v>-0.1831</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0538</v>
+        <v>-0.0723</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0818</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1138</v>
+        <v>-0.1207</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0183</v>
+        <v>0.011</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.3128</v>
+        <v>0.2226</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.33</v>
+        <v>18.04</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5.1</v>
+        <v>18.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0408</v>
+        <v>-0.0128</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.046389</v>
+        <v>0.053343</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.107465</v>
+        <v>1.159549</v>
       </c>
       <c r="AN4" t="n">
-        <v>10.75</v>
+        <v>15.95</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
@@ -1884,31 +1888,31 @@
         <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.075151</v>
+        <v>1.114435</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.110518</v>
+        <v>1.115445</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.97</v>
+        <v>0.876011</v>
       </c>
       <c r="AV4" t="n">
         <v>1</v>
       </c>
       <c r="AW4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.051205</v>
+        <v>0.030743</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.9059</v>
+        <v>1.7351</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -1923,28 +1927,24 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>neutro_zona_cinza</t>
+          <t>expansao</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BI4" t="n">
@@ -1954,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="BK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
@@ -1963,81 +1963,81 @@
         <v>1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="BP4" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.3434343434343434</v>
       </c>
       <c r="BR4" t="n">
         <v>1</v>
       </c>
       <c r="BS4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>exec_bilateral</t>
+          <t>exec_alta</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>expansion_moderada</t>
+          <t>exec_expansion_har</t>
         </is>
       </c>
       <c r="BW4" t="n">
-        <v>0.7411</v>
+        <v>0.6368</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.651</v>
+        <v>0.6546</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.5695</v>
+        <v>0.4917</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.464180008545714</v>
+        <v>0.3478669257672033</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.6544115048991059</v>
+        <v>0.5742751832410374</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.6592681272653879</v>
+        <v>0.1717746127157639</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.6592681272653879</v>
+        <v>0.5742751832410374</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5181818181818182</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.6122448979591837</v>
+        <v>0.4956521739130435</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.6368715083798883</v>
+        <v>0.5811965811965812</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.75</v>
+        <v>0.4503311258278146</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.8169014084507042</v>
+        <v>0</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.3515151515151515</v>
+        <v>0</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>expansao_moderada_sem_exec_forte</t>
+          <t>har_fallback_aprovado_expansao</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
@@ -2047,83 +2047,51 @@
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>RV_RANK</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="CN4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>0.6027397260273972</v>
       </c>
       <c r="CP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.5381</v>
+        <v>0.5809</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.5381</v>
+        <v>0.5809</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.149 | spread_35_20: esp=+0.054 | spread_45_25: esp=+0.082 | spread_45_15: esp=+0.114</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>vetado_esperanca_historica</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.228 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="DB4" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
-        </is>
-      </c>
-      <c r="DC4" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
+          <t>vetada</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2136,12 +2104,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Compra CALL (VETADA)</t>
+          <t>Alerta CALL (VETADA)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2158,53 +2126,53 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>aprovado_executor_nivel_A</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6512</v>
+        <v>0.5263</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0702</v>
+        <v>0.1475</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2667</v>
+        <v>0.5541</v>
       </c>
       <c r="P5" t="n">
         <v>-0.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.058</v>
+        <v>-0.0184</v>
       </c>
       <c r="R5" t="n">
         <v>436</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0722</v>
+        <v>-0.0692</v>
       </c>
       <c r="T5" t="n">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1354</v>
+        <v>-0.0577</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0178</v>
+        <v>0.0499</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -2213,7 +2181,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>spread_35_20,spread_45_15,spread_45_25</t>
+          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -2228,43 +2196,43 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1364</v>
+        <v>-0.0587</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1831</v>
+        <v>-0.0639</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.0723</v>
+        <v>-0.0404</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0323</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.1207</v>
+        <v>-0.0561</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.011</v>
+        <v>0.0233</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.2226</v>
+        <v>0.2293</v>
       </c>
       <c r="AI5" t="n">
-        <v>18.04</v>
+        <v>8.69</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.5</v>
+        <v>9.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.0128</v>
+        <v>-0.0072</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.053369</v>
+        <v>0.06879</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.159549</v>
+        <v>1.142491</v>
       </c>
       <c r="AN5" t="n">
-        <v>15.95</v>
+        <v>14.25</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
@@ -2279,13 +2247,13 @@
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.114435</v>
+        <v>1.139753</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.115445</v>
+        <v>1.139753</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.876011</v>
+        <v>0.845253</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -2294,10 +2262,10 @@
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.030743</v>
+        <v>0.06489499999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.736</v>
+        <v>1.06</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2316,20 +2284,24 @@
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BI5" t="n">
@@ -2351,78 +2323,78 @@
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BP5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.3434343434343434</v>
+        <v>0.3535353535353535</v>
       </c>
       <c r="BR5" t="n">
         <v>1</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>exec_alta</t>
+          <t>exec_bilateral</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>exec_expansion_har</t>
+          <t>expansion_moderada</t>
         </is>
       </c>
       <c r="BW5" t="n">
-        <v>0.6368</v>
+        <v>0.6584</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.6546</v>
+        <v>0.6328</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.4917</v>
+        <v>0.5611</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.3478669257672033</v>
+        <v>0.4382483987992929</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.5742751832410374</v>
+        <v>0.5747077669640731</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.1717746127157639</v>
+        <v>0.3957849185932791</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.5742751832410374</v>
+        <v>0.5747077669640731</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.5181818181818182</v>
+        <v>0.5943396226415094</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.4956521739130435</v>
+        <v>0.4436619718309859</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.5811965811965812</v>
+        <v>0.6509433962264151</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.4503311258278146</v>
+        <v>0.4339622641509434</v>
       </c>
       <c r="CH5" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>0.07843137254901961</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>har_fallback_aprovado_expansao</t>
+          <t>expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
@@ -2432,23 +2404,23 @@
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>HAR</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="CN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.6027397260273972</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
         <v>0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.581</v>
+        <v>0.5599</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.581</v>
+        <v>0.5599</v>
       </c>
       <c r="CS5" t="n">
         <v>1</v>
@@ -2477,363 +2449,6 @@
       <c r="DC5" t="inlineStr"/>
       <c r="DD5" t="inlineStr"/>
       <c r="DE5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>v5.5_executor_diario</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>USIM5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Alerta CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>alerta_executor_nivel_B</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>57</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.5263</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.1475</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.5541</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.0184</v>
-      </c>
-      <c r="R6" t="n">
-        <v>436</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.0692</v>
-      </c>
-      <c r="T6" t="n">
-        <v>335</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.0577</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.0499</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>nenhuma</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>esperanca</t>
-        </is>
-      </c>
-      <c r="Z6" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-0.0587</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.0639</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.0404</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-0.0323</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-0.0561</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.0231</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.2245</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-0.0072</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0.063786</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.146744</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.139753</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.139753</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.845253</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.06454500000000001</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.9882</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>expansao</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>65</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0.3535353535353535</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>exec_bilateral</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>expansion_moderada</t>
-        </is>
-      </c>
-      <c r="BW6" t="n">
-        <v>0.6584</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0.6328</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.5611</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.4382483987992929</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.5747077669640731</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.3957849185932791</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>0.5747077669640731</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>0.5943396226415094</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>0.4436619718309859</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>0.6509433962264151</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>0.4339622641509434</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>0.07843137254901961</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>expansao_moderada_sem_exec_forte</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>threshold_por_ativo</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="CN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>0.5537</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>0.5537</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>vetado_esperanca_historica</t>
-        </is>
-      </c>
-      <c r="CU6" t="inlineStr"/>
-      <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="inlineStr"/>
-      <c r="CX6" t="inlineStr"/>
-      <c r="CY6" t="inlineStr"/>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="DA6" t="inlineStr">
-        <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="DB6" t="inlineStr"/>
-      <c r="DC6" t="inlineStr"/>
-      <c r="DD6" t="inlineStr"/>
-      <c r="DE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2939,7 +2554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2948,7 +2563,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46227</v>
+        <v>46211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2961,22 +2576,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>20.7</v>
+        <v>10.35</v>
       </c>
       <c r="I2" t="n">
-        <v>21.52</v>
+        <v>11.05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.96</v>
+        <v>6.76</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.176</v>
+        <v>-0.5</v>
       </c>
       <c r="L2" t="n">
         <v>0.49</v>
@@ -2988,21 +2603,21 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.352</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0363</v>
+        <v>0.021</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>razao=0.56 &lt; 0.6 | M=-0.18 — ativo foi contra, tese falhou</t>
+          <t>razao=0.35 &lt; 0.6 | M=-0.50 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3011,61 +2626,61 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Compra CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>spread_45_15</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>13.61</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>13.73</v>
+        <v>9.65</v>
       </c>
       <c r="J3" t="n">
-        <v>0.88</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.028</v>
+        <v>-0.102</v>
       </c>
       <c r="L3" t="n">
-        <v>0.425</v>
+        <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.255</v>
+        <v>-0.32</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.352</v>
+        <v>0.221</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0143</v>
+        <v>-0.0139</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>razao=0.35 &lt; 0.6 | M=-0.03 — ativo foi contra, tese falhou</t>
+          <t>razao=0.22 &lt; 0.6 | M=-0.10 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>SLCE3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3074,7 +2689,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3087,22 +2702,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>10.35</v>
+        <v>12.8</v>
       </c>
       <c r="I4" t="n">
-        <v>11.11</v>
+        <v>13.16</v>
       </c>
       <c r="J4" t="n">
-        <v>7.34</v>
+        <v>2.81</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.183</v>
       </c>
       <c r="L4" t="n">
         <v>0.49</v>
@@ -3114,21 +2729,21 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.416</v>
+        <v>0.006</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0249</v>
+        <v>-0.0003</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>razao=0.42 &lt; 0.6 | M=-0.56 — ativo foi contra, tese falhou</t>
+          <t>razao=0.01 &lt; 0.6 | M=-0.18 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3137,7 +2752,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46228</v>
+        <v>46212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3146,52 +2761,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>9.359999999999999</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>9.74</v>
+        <v>75.69</v>
       </c>
       <c r="J5" t="n">
-        <v>4.06</v>
+        <v>3.47</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.189</v>
+        <v>-0.258</v>
       </c>
       <c r="L5" t="n">
-        <v>0.49</v>
+        <v>0.425</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.32</v>
+        <v>-0.255</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.111</v>
+        <v>0.47</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0071</v>
+        <v>0.0214</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>razao=0.11 &lt; 0.6 | M=-0.19 — ativo foi contra, tese falhou</t>
+          <t>razao=0.47 &lt; 0.6 | M=-0.26 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLCE3</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3200,7 +2815,7 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46209</v>
+        <v>46230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3213,22 +2828,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H6" t="n">
-        <v>12.8</v>
+        <v>7.94</v>
       </c>
       <c r="I6" t="n">
-        <v>13.23</v>
+        <v>8.16</v>
       </c>
       <c r="J6" t="n">
-        <v>3.36</v>
+        <v>2.77</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.27</v>
+        <v>-0.007</v>
       </c>
       <c r="L6" t="n">
         <v>0.49</v>
@@ -3240,156 +2855,156 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.092</v>
+        <v>0.578</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0039</v>
+        <v>-0.0458</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>razao=0.09 &lt; 0.6 | M=-0.27 — ativo foi contra, tese falhou</t>
+          <t>razao=0.58 &lt; 0.6 | M=-0.01 — ativo foi contra, tese falhou</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SINAL FRACO (reverter)</t>
+          <t>SINAL INVERTIDO (fim horizonte)</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>spread_45_15</t>
+          <t>naked_30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>73.15000000000001</v>
+        <v>13.88</v>
       </c>
       <c r="I7" t="n">
-        <v>75.54000000000001</v>
+        <v>11.64</v>
       </c>
       <c r="J7" t="n">
-        <v>3.27</v>
+        <v>-16.14</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.23</v>
+        <v>-1.564</v>
       </c>
       <c r="L7" t="n">
-        <v>0.425</v>
+        <v>0.751</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.255</v>
+        <v>-0.181</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.434</v>
+        <v>1.388</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0198</v>
+        <v>-0.0951</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>razao=0.43 &lt; 0.6 | M=-0.23 — ativo foi contra, tese falhou</t>
+          <t>Modelo virou PUT mas restam 4d — previsão cobre 20d, maioria pós-vencimento | M=-1.56 | razao=1.39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SINAL FRACO (reverter)</t>
+          <t>SINAL FRACO (segurar)</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46230</v>
+        <v>46221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>spread_45_15</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>7.94</v>
+        <v>13.61</v>
       </c>
       <c r="I8" t="n">
-        <v>8.18</v>
+        <v>13.76</v>
       </c>
       <c r="J8" t="n">
-        <v>3.02</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.025</v>
+        <v>0.006</v>
       </c>
       <c r="L8" t="n">
-        <v>0.49</v>
+        <v>0.425</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.32</v>
+        <v>-0.255</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0447</v>
+        <v>0.0155</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>razao=0.56 &lt; 0.6 | M=-0.03 — ativo foi contra, tese falhou</t>
+          <t>razao=0.38 &lt; 0.6 | M=0.01 — movimento OK, modelo ruidoso</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>BBDC4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SINAL INVERTIDO (fim horizonte)</t>
+          <t>MANTER</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46209</v>
+        <v>46230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3398,52 +3013,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>naked_30</t>
+          <t>naked_45</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H9" t="n">
-        <v>13.88</v>
+        <v>18.71</v>
       </c>
       <c r="I9" t="n">
-        <v>11.83</v>
+        <v>18.77</v>
       </c>
       <c r="J9" t="n">
-        <v>-14.77</v>
+        <v>0.32</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.457</v>
+        <v>-0.122</v>
       </c>
       <c r="L9" t="n">
-        <v>0.751</v>
+        <v>0.49</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.181</v>
+        <v>-0.32</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.213</v>
+        <v>1.442</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0824</v>
+        <v>0.0547</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Modelo virou PUT mas restam 4d — previsão cobre 20d, maioria pós-vencimento | M=-1.46 | razao=1.21</t>
+          <t>M=-0.12 | razao=1.44 | 1/20d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3456,7 +3071,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3471,42 +3086,42 @@
         <v>19</v>
       </c>
       <c r="H10" t="n">
-        <v>18.71</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>18.81</v>
+        <v>0.79</v>
       </c>
       <c r="J10" t="n">
-        <v>0.53</v>
+        <v>-2.47</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.377</v>
       </c>
       <c r="L10" t="n">
         <v>0.49</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.32</v>
+        <v>-0.113</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.476</v>
+        <v>1.94</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0561</v>
+        <v>-0.2139</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>M=-0.09 | razao=1.48 | 1/20d</t>
+          <t>M=0.38 | razao=1.94 | 1/20d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3515,7 +3130,7 @@
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3528,41 +3143,41 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8100000000000001</v>
+        <v>20.7</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8100000000000001</v>
+        <v>21.32</v>
       </c>
       <c r="J11" t="n">
-        <v>-0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.238</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>0.49</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.252</v>
+        <v>-0.32</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.769</v>
+        <v>0.659</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1966</v>
+        <v>-0.0419</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>M=0.24 | razao=1.77 | 1/20d</t>
+          <t>M=-0.09 | razao=0.66 | 2/20d</t>
         </is>
       </c>
     </row>
@@ -3600,32 +3215,32 @@
         <v>11.4</v>
       </c>
       <c r="I12" t="n">
-        <v>11.52</v>
+        <v>11.38</v>
       </c>
       <c r="J12" t="n">
-        <v>1.05</v>
+        <v>-0.18</v>
       </c>
       <c r="K12" t="n">
-        <v>0.089</v>
+        <v>0.229</v>
       </c>
       <c r="L12" t="n">
         <v>0.49</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.32</v>
+        <v>-0.261</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.362</v>
+        <v>1.578</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.0856</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>M=0.09 | razao=1.36 | 2/20d</t>
+          <t>M=0.23 | razao=1.58 | 2/20d</t>
         </is>
       </c>
     </row>
@@ -3663,13 +3278,13 @@
         <v>44.64</v>
       </c>
       <c r="I13" t="n">
-        <v>46.38</v>
+        <v>46.42</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>3.99</v>
       </c>
       <c r="K13" t="n">
-        <v>0.323</v>
+        <v>0.334</v>
       </c>
       <c r="L13" t="n">
         <v>0.751</v>
@@ -3681,14 +3296,14 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.949</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0513</v>
+        <v>0.052</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>M=0.32 | razao=0.94 | 8/20d</t>
+          <t>M=0.33 | razao=0.95 | 8/20d</t>
         </is>
       </c>
     </row>
@@ -3726,13 +3341,13 @@
         <v>5.27</v>
       </c>
       <c r="I14" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="J14" t="n">
-        <v>1.14</v>
+        <v>2.09</v>
       </c>
       <c r="K14" t="n">
-        <v>0.073</v>
+        <v>-0.033</v>
       </c>
       <c r="L14" t="n">
         <v>0.49</v>
@@ -3744,14 +3359,14 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.906</v>
+        <v>0.749</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0464</v>
+        <v>-0.0401</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>M=0.07 | razao=0.91 | 1/20d</t>
+          <t>M=-0.03 | razao=0.75 | 1/20d</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3888,10 +3503,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3095</v>
+        <v>0.3076</v>
       </c>
       <c r="D2" t="n">
-        <v>1.103892</v>
+        <v>1.10471</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3899,7 +3514,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.2446</v>
+        <v>0.2444</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3983,10 +3598,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2154</v>
+        <v>0.2112</v>
       </c>
       <c r="D3" t="n">
-        <v>1.152624</v>
+        <v>1.154009</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3994,7 +3609,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.6505</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4048,17 +3663,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.824 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.827 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.0398</v>
+        <v>0.0395</v>
       </c>
       <c r="S3" t="n">
-        <v>63.2</v>
+        <v>62.7</v>
       </c>
       <c r="T3" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -4069,19 +3684,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Compra CALL (VETADA)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3128</v>
+        <v>0.2226</v>
       </c>
       <c r="D4" t="n">
-        <v>1.107465</v>
+        <v>1.159549</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4089,71 +3704,39 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.1501</v>
+        <v>-0.1354</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>vetada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
+          <t>VETADA — esperança histórica insuficiente</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.228 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.0183</v>
+        <v>0.011</v>
       </c>
       <c r="S4" t="n">
-        <v>29.1</v>
+        <v>17.5</v>
       </c>
       <c r="T4" t="n">
-        <v>32.2</v>
+        <v>20.2</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -4164,19 +3747,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Compra CALL (VETADA)</t>
+          <t>Alerta CALL (VETADA)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2226</v>
+        <v>0.2293</v>
       </c>
       <c r="D5" t="n">
-        <v>1.159549</v>
+        <v>1.142491</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4184,7 +3767,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-0.1354</v>
+        <v>-0.0577</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4210,78 +3793,15 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.011</v>
+        <v>0.0233</v>
       </c>
       <c r="S5" t="n">
-        <v>17.5</v>
+        <v>37</v>
       </c>
       <c r="T5" t="n">
-        <v>20.2</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="inlineStr">
-        <is>
-          <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>USIM5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Alerta CALL (VETADA)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.2245</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.146744</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.0577</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>vetada</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>VETADA — esperança histórica insuficiente</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Sinal vetado pelo gate de esperança histórica — não operar.</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>0.0231</v>
-      </c>
-      <c r="S6" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="U6" t="inlineStr">
         <is>
           <t>Se IV_mercado &lt; vol_anualizada_pct → opção barata (compra favorável)</t>
         </is>
@@ -4950,10 +4470,10 @@
         <v>0.0168</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4317</v>
+        <v>0.4329</v>
       </c>
       <c r="AH2" t="n">
-        <v>41.15</v>
+        <v>41.21</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -4962,13 +4482,13 @@
         <v>-0.0113</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.043759</v>
+        <v>0.045996</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.936111</v>
+        <v>0.936253</v>
       </c>
       <c r="AM2" t="n">
-        <v>-6.39</v>
+        <v>-6.37</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4998,10 +4518,10 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.046941</v>
+        <v>0.047003</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.9322</v>
+        <v>0.9786</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -5153,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.5158</v>
+        <v>0.5202</v>
       </c>
       <c r="CQ2" t="n">
         <v>0</v>
@@ -5280,13 +4800,13 @@
         <v>0.219</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0209</v>
+        <v>0.0208</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0898</v>
+        <v>0.0873</v>
       </c>
       <c r="AH3" t="n">
-        <v>42.41</v>
+        <v>42.47</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -5295,13 +4815,13 @@
         <v>0.0304</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.107101</v>
+        <v>0.108583</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.214613</v>
+        <v>1.218094</v>
       </c>
       <c r="AM3" t="n">
-        <v>21.46</v>
+        <v>21.81</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -5331,10 +4851,10 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.05832</v>
+        <v>0.058038</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.8364</v>
+        <v>1.8709</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -5482,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.6286</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="CQ3" t="n">
         <v>0</v>
@@ -5609,13 +5129,13 @@
         <v>0.3812</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0127</v>
+        <v>0.0128</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3555</v>
+        <v>0.3559</v>
       </c>
       <c r="AH4" t="n">
-        <v>42.85</v>
+        <v>42.86</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -5624,10 +5144,10 @@
         <v>0.0011</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0097</v>
+        <v>0.009955</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.034993</v>
+        <v>1.034966</v>
       </c>
       <c r="AM4" t="n">
         <v>3.5</v>
@@ -5660,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.035573</v>
+        <v>0.035586</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.2727</v>
+        <v>0.2798</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -5815,7 +5335,7 @@
         <v>1</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.4746</v>
+        <v>0.4753</v>
       </c>
       <c r="CQ4" t="n">
         <v>0</v>
@@ -5945,10 +5465,10 @@
         <v>0.0163</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5405</v>
+        <v>0.5397</v>
       </c>
       <c r="AH5" t="n">
-        <v>75.54000000000001</v>
+        <v>75.69</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -5957,13 +5477,13 @@
         <v>0.2323</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.019769</v>
+        <v>0.021369</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.936077</v>
+        <v>0.934263</v>
       </c>
       <c r="AM5" t="n">
-        <v>-6.39</v>
+        <v>-6.57</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -5993,10 +5513,10 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.045548</v>
+        <v>0.045506</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.434</v>
+        <v>0.4696</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -6148,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.4365</v>
+        <v>0.4402</v>
       </c>
       <c r="CQ5" t="n">
         <v>0</v>
@@ -6223,10 +5743,10 @@
         <v>0.3564</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9003</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1617</v>
+        <v>0.1563</v>
       </c>
       <c r="P6" t="n">
         <v>0.1232</v>
@@ -6241,7 +5761,7 @@
         <v>398</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2446</v>
+        <v>0.2444</v>
       </c>
       <c r="U6" t="n">
         <v>0.0489</v>
@@ -6258,49 +5778,49 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>0.3279</v>
+        <v>0.3277</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.0247</v>
+        <v>1.024</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2436</v>
+        <v>0.2434</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3279</v>
+        <v>0.3277</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0706</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>0.0919</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1457</v>
+        <v>0.1455</v>
       </c>
       <c r="AF6" t="n">
         <v>0.0136</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.3095</v>
+        <v>0.3076</v>
       </c>
       <c r="AH6" t="n">
-        <v>18.81</v>
+        <v>18.77</v>
       </c>
       <c r="AI6" t="n">
-        <v>19.41</v>
+        <v>19.36</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0998</v>
+        <v>0.0997</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.056146</v>
+        <v>0.054728</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.103892</v>
+        <v>1.10471</v>
       </c>
       <c r="AM6" t="n">
-        <v>10.39</v>
+        <v>10.47</v>
       </c>
       <c r="AN6" t="n">
         <v>1</v>
@@ -6330,10 +5850,10 @@
         <v>1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.038034</v>
+        <v>0.037963</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.4762</v>
+        <v>1.4416</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -6485,10 +6005,10 @@
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.5798</v>
+        <v>0.5767</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.5798</v>
+        <v>0.5767</v>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
@@ -6517,7 +6037,7 @@
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.244 | spread_35_20: esp=+0.071 | spread_45_25: esp=+0.092 | spread_45_15: esp=+0.146</t>
+          <t>naked_30: esp=+0.243 | spread_35_20: esp=+0.070 | spread_45_25: esp=+0.092 | spread_45_15: esp=+0.145</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
@@ -6660,13 +6180,13 @@
         <v>-0.0296</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0218</v>
+        <v>0.0214</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.3916</v>
+        <v>0.3742</v>
       </c>
       <c r="AH7" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -6675,13 +6195,13 @@
         <v>0.0017</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.046041</v>
+        <v>0.046078</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.98431</v>
+        <v>0.995816</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1.57</v>
+        <v>-0.42</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -6711,10 +6231,10 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.060823</v>
+        <v>0.059601</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.757</v>
+        <v>0.7731</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -6866,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.4598</v>
+        <v>0.4649</v>
       </c>
       <c r="CQ7" t="n">
         <v>0</v>
@@ -6940,7 +6460,7 @@
         <v>0.8591</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3004</v>
+        <v>0.2902</v>
       </c>
       <c r="P8" t="n">
         <v>-0.0526</v>
@@ -6993,13 +6513,13 @@
         <v>0.0402</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0331</v>
+        <v>0.0318</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.336</v>
+        <v>0.2758</v>
       </c>
       <c r="AH8" t="n">
-        <v>4.99</v>
+        <v>4.83</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -7008,13 +6528,13 @@
         <v>0.0474</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.028157</v>
+        <v>0.000629</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.111344</v>
+        <v>1.119202</v>
       </c>
       <c r="AM8" t="n">
-        <v>11.13</v>
+        <v>11.92</v>
       </c>
       <c r="AN8" t="n">
         <v>1</v>
@@ -7044,10 +6564,10 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.09245299999999999</v>
+        <v>0.08860700000000001</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.3046</v>
+        <v>0.0071</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
@@ -7199,7 +6719,7 @@
         <v>1</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.4604</v>
+        <v>0.4427</v>
       </c>
       <c r="CQ8" t="n">
         <v>0</v>
@@ -7329,10 +6849,10 @@
         <v>0.0196</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.479</v>
+        <v>0.4801</v>
       </c>
       <c r="AH9" t="n">
-        <v>46.38</v>
+        <v>46.42</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -7341,13 +6861,13 @@
         <v>0.0276</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.051305</v>
+        <v>0.051975</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.953448</v>
+        <v>0.950933</v>
       </c>
       <c r="AM9" t="n">
-        <v>-4.66</v>
+        <v>-4.91</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -7377,10 +6897,10 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.054714</v>
+        <v>0.054778</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.9377</v>
+        <v>0.9488</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
@@ -7532,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.513</v>
+        <v>0.5139</v>
       </c>
       <c r="CQ9" t="n">
         <v>0</v>
@@ -7662,10 +7182,10 @@
         <v>0.0146</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.4604</v>
+        <v>0.4609</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.73</v>
+        <v>13.76</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -7674,13 +7194,13 @@
         <v>0.0076</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.014305</v>
+        <v>0.015451</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.98791</v>
+        <v>0.986305</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1.21</v>
+        <v>-1.37</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -7710,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.040688</v>
+        <v>0.040708</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3516</v>
+        <v>0.3796</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -7865,7 +7385,7 @@
         <v>1</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.439</v>
+        <v>0.4417</v>
       </c>
       <c r="CQ10" t="n">
         <v>0</v>
@@ -8007,13 +7527,13 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.160118</v>
+        <v>0.16075</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.853546</v>
+        <v>0.859348</v>
       </c>
       <c r="AM11" t="n">
-        <v>-14.65</v>
+        <v>-14.07</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -8046,7 +7566,7 @@
         <v>0.045989</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.4816</v>
+        <v>3.4954</v>
       </c>
       <c r="AY11" t="n">
         <v>1</v>
@@ -8333,28 +7853,28 @@
         <v>-0.0561</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0231</v>
+        <v>0.0233</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.2245</v>
+        <v>0.2293</v>
       </c>
       <c r="AH12" t="n">
-        <v>8.630000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="AI12" t="n">
-        <v>9.09</v>
+        <v>9.16</v>
       </c>
       <c r="AJ12" t="n">
         <v>-0.0072</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.063786</v>
+        <v>0.06879</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.146744</v>
+        <v>1.142491</v>
       </c>
       <c r="AM12" t="n">
-        <v>14.67</v>
+        <v>14.25</v>
       </c>
       <c r="AN12" t="n">
         <v>1</v>
@@ -8384,10 +7904,10 @@
         <v>1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.06454500000000001</v>
+        <v>0.06489499999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.9882</v>
+        <v>1.06</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -8539,10 +8059,10 @@
         <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.5537</v>
+        <v>0.5599</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.5537</v>
+        <v>0.5599</v>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
@@ -8682,13 +8202,13 @@
         <v>-0.008</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0223</v>
+        <v>0.0219</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.3386</v>
+        <v>0.3186</v>
       </c>
       <c r="AH13" t="n">
-        <v>13.99</v>
+        <v>13.9</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -8697,13 +8217,13 @@
         <v>-0.0038</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.005901</v>
+        <v>-0.009472</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.985306</v>
+        <v>0.993719</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1.47</v>
+        <v>-0.63</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -8733,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.062153</v>
+        <v>0.061018</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0949</v>
+        <v>0.1552</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -8884,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.4697</v>
+        <v>0.4797</v>
       </c>
       <c r="CQ13" t="n">
         <v>0</v>
@@ -8980,20 +8500,24 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>naked_45</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>naked_30,naked_45,spread_35_20,spread_45_15,spread_45_25</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
+          <t>spread_35_20,spread_45_15,spread_45_25</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>risco</t>
+        </is>
+      </c>
       <c r="Y14" t="n">
-        <v>0.0584</v>
+        <v>-0.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1826</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0.0333</v>
@@ -9011,13 +8535,13 @@
         <v>0.0311</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0146</v>
+        <v>0.0149</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.5986</v>
+        <v>0.6227</v>
       </c>
       <c r="AH14" t="n">
-        <v>41.04</v>
+        <v>41.21</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -9026,13 +8550,13 @@
         <v>0.008</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.019764</v>
+        <v>0.01836</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.906312</v>
+        <v>0.888196</v>
       </c>
       <c r="AM14" t="n">
-        <v>-9.369999999999999</v>
+        <v>-11.18</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -9062,10 +8586,10 @@
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.040635</v>
+        <v>0.041529</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.4864</v>
+        <v>0.4421</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -9213,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.2943</v>
+        <v>0.2851</v>
       </c>
       <c r="CQ14" t="n">
         <v>0</v>
@@ -9340,13 +8864,13 @@
         <v>0.3815</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0389</v>
+        <v>0.0385</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2286</v>
+        <v>0.225</v>
       </c>
       <c r="AH15" t="n">
-        <v>10.64</v>
+        <v>10.6</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -9355,13 +8879,13 @@
         <v>0.3831</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.06748700000000001</v>
+        <v>-0.06969499999999999</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.009227</v>
+        <v>1.01504</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.92</v>
+        <v>1.5</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -9391,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.108441</v>
+        <v>0.10735</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.6223</v>
+        <v>0.6492</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -9546,7 +9070,7 @@
         <v>1</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.4971</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="CQ15" t="n">
         <v>0</v>
@@ -9677,13 +9201,13 @@
         <v>-0.1003</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0289</v>
+        <v>0.0287</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.3378</v>
+        <v>0.3282</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -9692,13 +9216,13 @@
         <v>-0.0147</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.01397</v>
+        <v>-0.020941</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.070378</v>
+        <v>1.074508</v>
       </c>
       <c r="AM16" t="n">
-        <v>7.04</v>
+        <v>7.45</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -9728,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.07996499999999999</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1731</v>
+        <v>0.2619</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -9883,7 +9407,7 @@
         <v>1</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.4514</v>
+        <v>0.4622</v>
       </c>
       <c r="CQ16" t="n">
         <v>0</v>
@@ -10014,13 +9538,13 @@
         <v>-0.0331</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0142</v>
+        <v>0.0132</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.1202</v>
+        <v>0.0916</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.24</v>
+        <v>16.1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -10029,13 +9553,13 @@
         <v>0.0067</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.028871</v>
+        <v>0.023942</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.194306</v>
+        <v>1.225348</v>
       </c>
       <c r="AM17" t="n">
-        <v>19.43</v>
+        <v>22.53</v>
       </c>
       <c r="AN17" t="n">
         <v>1</v>
@@ -10065,10 +9589,10 @@
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.039681</v>
+        <v>0.036733</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.7276</v>
+        <v>0.6518</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -10220,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.498</v>
+        <v>0.4961</v>
       </c>
       <c r="CQ17" t="n">
         <v>0</v>
@@ -10335,13 +9859,13 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.0336</v>
+        <v>0.0335</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.4605</v>
+        <v>0.458</v>
       </c>
       <c r="AH18" t="n">
-        <v>5.63</v>
+        <v>5.64</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -10350,13 +9874,13 @@
         <v>-0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.173187</v>
+        <v>0.176382</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.921991</v>
+        <v>0.935353</v>
       </c>
       <c r="AM18" t="n">
-        <v>-7.8</v>
+        <v>-6.46</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -10368,7 +9892,7 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
         <v>1.084286</v>
@@ -10386,10 +9910,10 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.093794</v>
+        <v>0.093523</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.8465</v>
+        <v>1.886</v>
       </c>
       <c r="AY18" t="n">
         <v>0</v>
@@ -10537,7 +10061,7 @@
         <v>1</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.5956</v>
+        <v>0.6001</v>
       </c>
       <c r="CQ18" t="n">
         <v>0</v>
@@ -10667,10 +10191,10 @@
         <v>0.0129</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.4999</v>
+        <v>0.5011</v>
       </c>
       <c r="AH19" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -10679,13 +10203,13 @@
         <v>0.1402</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.008932000000000001</v>
+        <v>-0.011194</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.918605</v>
+        <v>0.927648</v>
       </c>
       <c r="AM19" t="n">
-        <v>-8.140000000000001</v>
+        <v>-7.24</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -10715,10 +10239,10 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.035882</v>
+        <v>0.035928</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.2489</v>
+        <v>0.3116</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -10866,7 +10390,7 @@
         <v>0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.3877</v>
+        <v>0.3938</v>
       </c>
       <c r="CQ19" t="n">
         <v>0</v>
@@ -10921,7 +10445,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -10993,13 +10517,13 @@
         <v>0.1336</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0232</v>
+        <v>0.0228</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.2506</v>
+        <v>0.2425</v>
       </c>
       <c r="AH20" t="n">
-        <v>21.52</v>
+        <v>21.32</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -11008,13 +10532,13 @@
         <v>0.0218</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.036269</v>
+        <v>-0.041938</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.975308</v>
+        <v>0.981366</v>
       </c>
       <c r="AM20" t="n">
-        <v>-2.47</v>
+        <v>-1.86</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -11044,10 +10568,10 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.064757</v>
+        <v>0.06361600000000001</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.5601</v>
+        <v>0.6592</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -11057,12 +10581,12 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
       <c r="BC20" t="n">
@@ -11199,7 +10723,7 @@
         <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.4571</v>
+        <v>0.4687</v>
       </c>
       <c r="CQ20" t="n">
         <v>0</v>
@@ -11333,10 +10857,10 @@
         <v>0.0184</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.0985</v>
+        <v>0.0984</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.22</v>
+        <v>18.2</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -11345,13 +10869,13 @@
         <v>0.0114</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.040335</v>
+        <v>0.039287</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.078531</v>
+        <v>1.079021</v>
       </c>
       <c r="AM21" t="n">
-        <v>7.85</v>
+        <v>7.9</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -11381,10 +10905,10 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.051313</v>
+        <v>0.051296</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.7861</v>
+        <v>0.7659</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -11536,7 +11060,7 @@
         <v>1</v>
       </c>
       <c r="CP21" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5308</v>
       </c>
       <c r="CQ21" t="n">
         <v>0</v>
@@ -11663,13 +11187,13 @@
         <v>0.1537</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.0215</v>
+        <v>0.0214</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.2776</v>
+        <v>0.2749</v>
       </c>
       <c r="AH22" t="n">
-        <v>11.11</v>
+        <v>11.05</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -11678,13 +11202,13 @@
         <v>0.0528</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.024895</v>
+        <v>0.020977</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.081879</v>
+        <v>1.104961</v>
       </c>
       <c r="AM22" t="n">
-        <v>8.19</v>
+        <v>10.5</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -11714,10 +11238,10 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.059878</v>
+        <v>0.059668</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.4158</v>
+        <v>0.3516</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -11865,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.4244</v>
+        <v>0.4186</v>
       </c>
       <c r="CQ22" t="n">
         <v>0</v>
@@ -11920,7 +11444,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -11996,13 +11520,13 @@
         <v>-0.053</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0167</v>
+        <v>0.0176</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.3281</v>
+        <v>0.366</v>
       </c>
       <c r="AH23" t="n">
-        <v>28.69</v>
+        <v>28.27</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -12011,19 +11535,19 @@
         <v>-0.017</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.021845</v>
+        <v>-0.032839</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.035398</v>
+        <v>1.025918</v>
       </c>
       <c r="AM23" t="n">
-        <v>3.54</v>
+        <v>2.59</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
         <v>0</v>
@@ -12047,10 +11571,10 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.046571</v>
+        <v>0.049065</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.4691</v>
+        <v>0.6693</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -12060,7 +11584,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -12202,7 +11726,7 @@
         <v>1</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.4889</v>
+        <v>0.5014</v>
       </c>
       <c r="CQ23" t="n">
         <v>0</v>
@@ -12329,13 +11853,13 @@
         <v>0.1303</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.0155</v>
+        <v>0.0157</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.3153</v>
+        <v>0.3306</v>
       </c>
       <c r="AH24" t="n">
-        <v>10.86</v>
+        <v>10.89</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -12344,13 +11868,13 @@
         <v>0.0477</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.128614</v>
+        <v>0.131477</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.107444</v>
+        <v>1.095958</v>
       </c>
       <c r="AM24" t="n">
-        <v>10.74</v>
+        <v>9.6</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
@@ -12380,10 +11904,10 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.043248</v>
+        <v>0.04386</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.9738</v>
+        <v>2.9977</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -12535,7 +12059,7 @@
         <v>0</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.5965</v>
+        <v>0.5934</v>
       </c>
       <c r="CQ24" t="n">
         <v>0</v>
@@ -12666,13 +12190,13 @@
         <v>0.0626</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0196</v>
+        <v>0.0195</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.6679</v>
+        <v>0.6661</v>
       </c>
       <c r="AH25" t="n">
-        <v>30.06</v>
+        <v>30.01</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -12681,13 +12205,13 @@
         <v>0.0061</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.021373</v>
+        <v>-0.022007</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.935563</v>
+        <v>0.936376</v>
       </c>
       <c r="AM25" t="n">
-        <v>-6.44</v>
+        <v>-6.36</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -12717,10 +12241,10 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.05462</v>
+        <v>0.054544</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.3913</v>
+        <v>0.4035</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -12872,7 +12396,7 @@
         <v>1</v>
       </c>
       <c r="CP25" t="n">
-        <v>0.4021</v>
+        <v>0.4037</v>
       </c>
       <c r="CQ25" t="n">
         <v>0</v>
@@ -13002,10 +12526,10 @@
         <v>0.0171</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.5662</v>
+        <v>0.5642</v>
       </c>
       <c r="AH26" t="n">
-        <v>21.67</v>
+        <v>21.76</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -13014,13 +12538,13 @@
         <v>0.1666</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.01477</v>
+        <v>0.019371</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.91444</v>
+        <v>0.909883</v>
       </c>
       <c r="AM26" t="n">
-        <v>-8.56</v>
+        <v>-9.01</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
@@ -13050,10 +12574,10 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.047709</v>
+        <v>0.047596</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.3096</v>
+        <v>0.407</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -13205,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.386</v>
+        <v>0.3961</v>
       </c>
       <c r="CQ26" t="n">
         <v>0</v>
@@ -13336,13 +12860,13 @@
         <v>-0.222</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0386</v>
+        <v>0.0388</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.2407</v>
+        <v>0.244</v>
       </c>
       <c r="AH27" t="n">
-        <v>6.04</v>
+        <v>5.96</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -13351,13 +12875,13 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.044544</v>
+        <v>-0.056493</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.999688</v>
+        <v>1.010373</v>
       </c>
       <c r="AM27" t="n">
-        <v>-0.03</v>
+        <v>1.04</v>
       </c>
       <c r="AN27" t="n">
         <v>0</v>
@@ -13387,10 +12911,10 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.107703</v>
+        <v>0.108328</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.4136</v>
+        <v>0.5215</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -13538,7 +13062,7 @@
         <v>0</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.4639</v>
+        <v>0.474</v>
       </c>
       <c r="CQ27" t="n">
         <v>0</v>
@@ -13669,13 +13193,13 @@
         <v>0.0243</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0243</v>
+        <v>0.0246</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.532</v>
+        <v>0.5407</v>
       </c>
       <c r="AH28" t="n">
-        <v>11.83</v>
+        <v>11.64</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -13684,13 +13208,13 @@
         <v>0.0165</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.082368</v>
+        <v>-0.095135</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.060221</v>
+        <v>1.069328</v>
       </c>
       <c r="AM28" t="n">
-        <v>6.02</v>
+        <v>6.93</v>
       </c>
       <c r="AN28" t="n">
         <v>0</v>
@@ -13720,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.06790400000000001</v>
+        <v>0.068534</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.213</v>
+        <v>1.3882</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -13871,7 +13395,7 @@
         <v>0</v>
       </c>
       <c r="CP28" t="n">
-        <v>0.4633</v>
+        <v>0.479</v>
       </c>
       <c r="CQ28" t="n">
         <v>0</v>
@@ -13926,7 +13450,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -14002,13 +13526,13 @@
         <v>-0.06850000000000001</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.0206</v>
+        <v>0.0208</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.2145</v>
+        <v>0.2217</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -14017,13 +13541,13 @@
         <v>-0.0028</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.028262</v>
+        <v>-0.03875</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.121596</v>
+        <v>1.108823</v>
       </c>
       <c r="AM29" t="n">
-        <v>12.16</v>
+        <v>10.88</v>
       </c>
       <c r="AN29" t="n">
         <v>0</v>
@@ -14053,10 +13577,10 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.057399</v>
+        <v>0.05806</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.4924</v>
+        <v>0.6674</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -14066,7 +13590,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -14204,7 +13728,7 @@
         <v>0</v>
       </c>
       <c r="CP29" t="n">
-        <v>0.4921</v>
+        <v>0.5082</v>
       </c>
       <c r="CQ29" t="n">
         <v>0</v>
@@ -14242,7 +13766,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14251,19 +13775,15 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -14276,7 +13796,7 @@
         <v>0.6613</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3309</v>
+        <v>0.3333</v>
       </c>
       <c r="N30" t="n">
         <v>0.6983</v>
@@ -14300,7 +13820,7 @@
         <v>0.1501</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0505</v>
+        <v>0.0507</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -14335,28 +13855,28 @@
         <v>0.1138</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.0183</v>
+        <v>0.0192</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.3128</v>
+        <v>0.3422</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.0408</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.046389</v>
+        <v>-0.040058</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.107465</v>
+        <v>1.091863</v>
       </c>
       <c r="AM30" t="n">
-        <v>10.75</v>
+        <v>9.19</v>
       </c>
       <c r="AN30" t="n">
         <v>1</v>
@@ -14383,13 +13903,13 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.051205</v>
+        <v>0.053517</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.9059</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -14399,7 +13919,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -14541,71 +14061,27 @@
         <v>1</v>
       </c>
       <c r="CP30" t="n">
-        <v>0.5381</v>
+        <v>0.5165</v>
       </c>
       <c r="CQ30" t="n">
-        <v>0.5381</v>
-      </c>
-      <c r="CR30" t="inlineStr">
-        <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="CS30" t="inlineStr">
-        <is>
-          <t>Put delta~-50 naked (ATM, máximo gamma)</t>
-        </is>
-      </c>
-      <c r="CT30" t="inlineStr">
-        <is>
-          <t>Put delta~-40 naked (ligeiramente mais OTM)</t>
-        </is>
-      </c>
-      <c r="CU30" t="inlineStr">
-        <is>
-          <t>OTM extremo sem vol prevista muito forte</t>
-        </is>
-      </c>
-      <c r="CV30" t="inlineStr">
-        <is>
-          <t>~0.45</t>
-        </is>
-      </c>
-      <c r="CW30" t="inlineStr">
-        <is>
-          <t>naked_30: esp=+0.149 | spread_35_20: esp=+0.054 | spread_45_25: esp=+0.082 | spread_45_15: esp=+0.114</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="CR30" t="inlineStr"/>
+      <c r="CS30" t="inlineStr"/>
+      <c r="CT30" t="inlineStr"/>
+      <c r="CU30" t="inlineStr"/>
+      <c r="CV30" t="inlineStr"/>
+      <c r="CW30" t="inlineStr"/>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.228 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
-        </is>
-      </c>
-      <c r="CY30" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="CZ30" t="inlineStr">
-        <is>
-          <t>Verificar IV no mercado: entrar só se IV_mercado ≤ vol_prevista_anualizada. Se IV &gt; vol_prevista: aguardar ou reduzir tamanho. [Taxa livre de risco: 0.053%/dia | carry 20 pregões: 1.06%]</t>
-        </is>
-      </c>
-      <c r="DA30" t="inlineStr">
-        <is>
-          <t>80% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DB30" t="inlineStr">
-        <is>
-          <t>40% do prêmio pago</t>
-        </is>
-      </c>
-      <c r="DC30" t="inlineStr">
-        <is>
-          <t>Regra 80/40: realizar 80%, stop 40%.</t>
-        </is>
-      </c>
+          <t>Ticker neutro — sem sinal operacional</t>
+        </is>
+      </c>
+      <c r="CY30" t="inlineStr"/>
+      <c r="CZ30" t="inlineStr"/>
+      <c r="DA30" t="inlineStr"/>
+      <c r="DB30" t="inlineStr"/>
+      <c r="DC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14628,7 +14104,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -14716,13 +14192,13 @@
         <v>0.0533</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0182</v>
+        <v>0.0178</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.4899</v>
+        <v>0.471</v>
       </c>
       <c r="AH31" t="n">
-        <v>15.01</v>
+        <v>14.93</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -14731,13 +14207,13 @@
         <v>0.0452</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.000348</v>
+        <v>-0.00214</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.132804</v>
+        <v>1.132573</v>
       </c>
       <c r="AM31" t="n">
-        <v>13.28</v>
+        <v>13.26</v>
       </c>
       <c r="AN31" t="n">
         <v>1</v>
@@ -14767,10 +14243,10 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.050728</v>
+        <v>0.049803</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.0069</v>
+        <v>0.043</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -14918,7 +14394,7 @@
         <v>0</v>
       </c>
       <c r="CP31" t="n">
-        <v>0.3315</v>
+        <v>0.3389</v>
       </c>
       <c r="CQ31" t="n">
         <v>0</v>
@@ -15068,7 +14544,7 @@
         <v>-0.0128</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.053369</v>
+        <v>0.053343</v>
       </c>
       <c r="AL32" t="n">
         <v>1.159549</v>
@@ -15107,7 +14583,7 @@
         <v>0.030743</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.736</v>
+        <v>1.7351</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -15255,10 +14731,10 @@
         <v>0</v>
       </c>
       <c r="CP32" t="n">
-        <v>0.581</v>
+        <v>0.5809</v>
       </c>
       <c r="CQ32" t="n">
-        <v>0.581</v>
+        <v>0.5809</v>
       </c>
       <c r="CR32" t="inlineStr">
         <is>
@@ -15397,10 +14873,10 @@
         <v>0.0164</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.3735</v>
+        <v>0.3747</v>
       </c>
       <c r="AH33" t="n">
-        <v>27.13</v>
+        <v>27.14</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -15409,13 +14885,13 @@
         <v>0.0106</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.015156</v>
+        <v>-0.015398</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.905174</v>
+        <v>0.921488</v>
       </c>
       <c r="AM33" t="n">
-        <v>-9.48</v>
+        <v>-7.85</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
@@ -15445,10 +14921,10 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.045645</v>
+        <v>0.045719</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.332</v>
+        <v>0.3368</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -15600,7 +15076,7 @@
         <v>1</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.4224</v>
+        <v>0.4227</v>
       </c>
       <c r="CQ33" t="n">
         <v>0</v>
@@ -15671,7 +15147,7 @@
         <v>0.2917</v>
       </c>
       <c r="N34" t="n">
-        <v>2.1808</v>
+        <v>2.1867</v>
       </c>
       <c r="O34" t="n">
         <v>2.2783</v>
@@ -15689,10 +15165,10 @@
         <v>294</v>
       </c>
       <c r="T34" t="n">
-        <v>0.5712</v>
+        <v>0.573</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2342</v>
+        <v>0.2349</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -15706,16 +15182,16 @@
       </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>0.5702</v>
+        <v>0.572</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.1501</v>
+        <v>3.1604</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.5702</v>
+        <v>0.572</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.5584</v>
+        <v>0.5603</v>
       </c>
       <c r="AC34" t="n">
         <v>0.0177</v>
@@ -15730,10 +15206,10 @@
         <v>0.0196</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.4082</v>
+        <v>0.4102</v>
       </c>
       <c r="AH34" t="n">
-        <v>32.37</v>
+        <v>32.45</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -15742,10 +15218,10 @@
         <v>0.0276</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.083985</v>
+        <v>0.08622199999999999</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.721759</v>
+        <v>0.721796</v>
       </c>
       <c r="AM34" t="n">
         <v>-27.82</v>
@@ -15778,10 +15254,10 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.054602</v>
+        <v>0.054716</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.5381</v>
+        <v>1.5758</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -15929,7 +15405,7 @@
         <v>0</v>
       </c>
       <c r="CP34" t="n">
-        <v>0.5349</v>
+        <v>0.5382</v>
       </c>
       <c r="CQ34" t="n">
         <v>0</v>
@@ -16063,10 +15539,10 @@
         <v>0.0221</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.4047</v>
+        <v>0.4073</v>
       </c>
       <c r="AH35" t="n">
-        <v>21.42</v>
+        <v>21.44</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -16075,13 +15551,13 @@
         <v>-0.007900000000000001</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.013429</v>
+        <v>0.013666</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.930581</v>
+        <v>0.928799</v>
       </c>
       <c r="AM35" t="n">
-        <v>-6.94</v>
+        <v>-7.12</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -16111,10 +15587,10 @@
         <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.06159</v>
+        <v>0.061748</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.218</v>
+        <v>0.2213</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -16262,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="CP35" t="n">
-        <v>0.4076</v>
+        <v>0.4074</v>
       </c>
       <c r="CQ35" t="n">
         <v>0</v>
@@ -16327,7 +15803,7 @@
         <v>0.1009</v>
       </c>
       <c r="L36" t="n">
-        <v>0.4565</v>
+        <v>0.4348</v>
       </c>
       <c r="M36" t="n">
         <v>0.36</v>
@@ -16339,13 +15815,13 @@
         <v>0.3232</v>
       </c>
       <c r="P36" t="n">
-        <v>0.0898</v>
+        <v>0.1003</v>
       </c>
       <c r="Q36" t="n">
         <v>436</v>
       </c>
       <c r="R36" t="n">
-        <v>0.172</v>
+        <v>0.1797</v>
       </c>
       <c r="S36" t="n">
         <v>302</v>
@@ -16389,13 +15865,13 @@
         <v>0.0906</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.017</v>
+        <v>0.0165</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.4375</v>
+        <v>0.4128</v>
       </c>
       <c r="AH36" t="n">
-        <v>29.02</v>
+        <v>28.79</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -16404,13 +15880,13 @@
         <v>0.0119</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0.000387</v>
+        <v>-0.00311</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.889769</v>
+        <v>0.907466</v>
       </c>
       <c r="AM36" t="n">
-        <v>-11.02</v>
+        <v>-9.25</v>
       </c>
       <c r="AN36" t="n">
         <v>0</v>
@@ -16440,10 +15916,10 @@
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.047374</v>
+        <v>0.045945</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0677</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -16595,7 +16071,7 @@
         <v>0</v>
       </c>
       <c r="CP36" t="n">
-        <v>0.364</v>
+        <v>0.3749</v>
       </c>
       <c r="CQ36" t="n">
         <v>0</v>
@@ -16722,13 +16198,13 @@
         <v>0.1978</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.0203</v>
+        <v>0.02</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.2918</v>
+        <v>0.2847</v>
       </c>
       <c r="AH37" t="n">
-        <v>64.64</v>
+        <v>64.39</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -16737,13 +16213,13 @@
         <v>0.0161</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.024626</v>
+        <v>0.02272</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.6279439999999999</v>
+        <v>0.6495649999999999</v>
       </c>
       <c r="AM37" t="n">
-        <v>-37.21</v>
+        <v>-35.04</v>
       </c>
       <c r="AN37" t="n">
         <v>0</v>
@@ -16773,10 +16249,10 @@
         <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.056628</v>
+        <v>0.055902</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.4349</v>
+        <v>0.4064</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -16924,7 +16400,7 @@
         <v>0</v>
       </c>
       <c r="CP37" t="n">
-        <v>0.4627</v>
+        <v>0.4613</v>
       </c>
       <c r="CQ37" t="n">
         <v>0</v>
@@ -17051,13 +16527,13 @@
         <v>0.027</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0286</v>
+        <v>0.0284</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.2895</v>
+        <v>0.281</v>
       </c>
       <c r="AH38" t="n">
-        <v>8.18</v>
+        <v>8.16</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -17066,13 +16542,13 @@
         <v>0.0095</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.044707</v>
+        <v>-0.045788</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.100384</v>
+        <v>1.107654</v>
       </c>
       <c r="AM38" t="n">
-        <v>10.04</v>
+        <v>10.77</v>
       </c>
       <c r="AN38" t="n">
         <v>1</v>
@@ -17102,10 +16578,10 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.079887</v>
+        <v>0.079197</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.5596</v>
+        <v>0.5782</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -17257,7 +16733,7 @@
         <v>1</v>
       </c>
       <c r="CP38" t="n">
-        <v>0.4917</v>
+        <v>0.4952</v>
       </c>
       <c r="CQ38" t="n">
         <v>0</v>
@@ -17300,7 +16776,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -17384,13 +16860,13 @@
         <v>0.0451</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.0152</v>
+        <v>0.0155</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.5343</v>
+        <v>0.5545</v>
       </c>
       <c r="AH39" t="n">
-        <v>13.23</v>
+        <v>13.16</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -17399,13 +16875,13 @@
         <v>0.0251</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.00389</v>
+        <v>-0.000254</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.137394</v>
+        <v>1.127403</v>
       </c>
       <c r="AM39" t="n">
-        <v>13.74</v>
+        <v>12.74</v>
       </c>
       <c r="AN39" t="n">
         <v>0</v>
@@ -17435,10 +16911,10 @@
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.042366</v>
+        <v>0.043321</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0059</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -17590,7 +17066,7 @@
         <v>0</v>
       </c>
       <c r="CP39" t="n">
-        <v>0.3827</v>
+        <v>0.3701</v>
       </c>
       <c r="CQ39" t="n">
         <v>0</v>
@@ -17724,10 +17200,10 @@
         <v>0.0253</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.9059</v>
+        <v>0.9053</v>
       </c>
       <c r="AH40" t="n">
-        <v>26.85</v>
+        <v>26.84</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -17736,13 +17212,13 @@
         <v>0.0107</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.00384</v>
+        <v>0.003778</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.8711370000000001</v>
+        <v>0.871166</v>
       </c>
       <c r="AM40" t="n">
-        <v>-12.89</v>
+        <v>-12.88</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -17772,10 +17248,10 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.07062599999999999</v>
+        <v>0.07059</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.0544</v>
+        <v>0.0535</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -18054,13 +17530,13 @@
         <v>-0.08119999999999999</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.0133</v>
+        <v>0.0129</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.1975</v>
+        <v>0.1739</v>
       </c>
       <c r="AH41" t="n">
-        <v>14.79</v>
+        <v>14.69</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -18069,13 +17545,13 @@
         <v>0.0026</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.01606</v>
+        <v>0.012667</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.060267</v>
+        <v>1.084565</v>
       </c>
       <c r="AM41" t="n">
-        <v>6.03</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -18105,10 +17581,10 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.036996</v>
+        <v>0.035931</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.4341</v>
+        <v>0.3525</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -18260,7 +17736,7 @@
         <v>1</v>
       </c>
       <c r="CP41" t="n">
-        <v>0.5239</v>
+        <v>0.5204</v>
       </c>
       <c r="CQ41" t="n">
         <v>0</v>
@@ -18337,13 +17813,13 @@
         <v>0.007900000000000001</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.0283</v>
+        <v>-0.03</v>
       </c>
       <c r="Q42" t="n">
         <v>436</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.017</v>
+        <v>-0.0211</v>
       </c>
       <c r="S42" t="n">
         <v>325</v>
@@ -18379,25 +17855,25 @@
         <v>0.0335</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.0039</v>
+        <v>0.0032</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.0336</v>
+        <v>-0.0343</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.0542</v>
+        <v>-0.0549</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.0633</v>
+        <v>-0.064</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.0163</v>
+        <v>0.0162</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.4602</v>
+        <v>0.4502</v>
       </c>
       <c r="AH42" t="n">
-        <v>55.05</v>
+        <v>54.91</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -18406,13 +17882,13 @@
         <v>0.006</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.015897</v>
+        <v>0.015275</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.013064</v>
+        <v>1.018285</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
@@ -18442,10 +17918,10 @@
         <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.045621</v>
+        <v>0.045194</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.3485</v>
+        <v>0.338</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -18597,7 +18073,7 @@
         <v>0</v>
       </c>
       <c r="CP42" t="n">
-        <v>0.4384</v>
+        <v>0.4394</v>
       </c>
       <c r="CQ42" t="n">
         <v>0</v>
@@ -18672,7 +18148,7 @@
         <v>0.4426</v>
       </c>
       <c r="N43" t="n">
-        <v>1.2819</v>
+        <v>1.286</v>
       </c>
       <c r="O43" t="n">
         <v>0.7336</v>
@@ -18690,10 +18166,10 @@
         <v>378</v>
       </c>
       <c r="T43" t="n">
-        <v>0.6505</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1186</v>
+        <v>0.1187</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -18707,16 +18183,16 @@
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>0.8244</v>
+        <v>0.8267</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.5762</v>
+        <v>2.5833</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.6495</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.8244</v>
+        <v>0.8267</v>
       </c>
       <c r="AC43" t="n">
         <v>0.1626</v>
@@ -18728,28 +18204,28 @@
         <v>0.3251</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.0398</v>
+        <v>0.0395</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.2154</v>
+        <v>0.2112</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.067</v>
+        <v>0.0673</v>
       </c>
       <c r="AK43" t="n">
-        <v>-0.196581</v>
+        <v>-0.213894</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.152624</v>
+        <v>1.154009</v>
       </c>
       <c r="AM43" t="n">
-        <v>15.26</v>
+        <v>15.4</v>
       </c>
       <c r="AN43" t="n">
         <v>1</v>
@@ -18779,10 +18255,10 @@
         <v>-1</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.111106</v>
+        <v>0.110244</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.7693</v>
+        <v>1.9402</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -18930,10 +18406,10 @@
         <v>1</v>
       </c>
       <c r="CP43" t="n">
-        <v>0.6108</v>
+        <v>0.6287</v>
       </c>
       <c r="CQ43" t="n">
-        <v>0.6108</v>
+        <v>0.6287</v>
       </c>
       <c r="CR43" t="inlineStr">
         <is>
@@ -18962,12 +18438,12 @@
       </c>
       <c r="CW43" t="inlineStr">
         <is>
-          <t>naked_30: esp=+0.649 | spread_35_20: esp=+0.163 | spread_45_25: esp=+0.211 | spread_45_15: esp=+0.325</t>
+          <t>naked_30: esp=+0.652 | spread_35_20: esp=+0.163 | spread_45_25: esp=+0.211 | spread_45_15: esp=+0.325</t>
         </is>
       </c>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.824 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
+          <t>[Empírico] Put delta~-45 naked (quase ATM, ~0.9σ, 20d) — esp_estrutura=0.827 DP. Selecionada por esperança dentro da família, ROI entre famílias, respeitando o contexto de risco.</t>
         </is>
       </c>
       <c r="CY43" t="inlineStr">
@@ -19101,13 +18577,13 @@
         <v>0.1186</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.0156</v>
+        <v>0.0162</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.2181</v>
+        <v>0.2383</v>
       </c>
       <c r="AH44" t="n">
-        <v>16.99</v>
+        <v>17.06</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -19116,13 +18592,13 @@
         <v>0.0083</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.047087</v>
+        <v>0.047552</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.121144</v>
+        <v>1.090423</v>
       </c>
       <c r="AM44" t="n">
-        <v>12.11</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AN44" t="n">
         <v>0</v>
@@ -19152,10 +18628,10 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.043598</v>
+        <v>0.045294</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.08</v>
+        <v>1.0498</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
@@ -19307,7 +18783,7 @@
         <v>0</v>
       </c>
       <c r="CP44" t="n">
-        <v>0.5505</v>
+        <v>0.5434</v>
       </c>
       <c r="CQ44" t="n">
         <v>0</v>
@@ -19434,13 +18910,13 @@
         <v>0.1134</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.023</v>
+        <v>0.0225</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.2026</v>
+        <v>0.1749</v>
       </c>
       <c r="AH45" t="n">
-        <v>9.74</v>
+        <v>9.65</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -19449,13 +18925,13 @@
         <v>0.0059</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.007147</v>
+        <v>-0.013872</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.196915</v>
+        <v>1.273217</v>
       </c>
       <c r="AM45" t="n">
-        <v>19.69</v>
+        <v>27.32</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -19485,10 +18961,10 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.06418699999999999</v>
+        <v>0.062663</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.1113</v>
+        <v>0.2214</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
@@ -19636,7 +19112,7 @@
         <v>0</v>
       </c>
       <c r="CP45" t="n">
-        <v>0.4383</v>
+        <v>0.4549</v>
       </c>
       <c r="CQ45" t="n">
         <v>0</v>
@@ -19767,13 +19243,13 @@
         <v>-0.0945</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0197</v>
+        <v>0.0194</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.322</v>
+        <v>0.3077</v>
       </c>
       <c r="AH46" t="n">
-        <v>11.52</v>
+        <v>11.38</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -19782,13 +19258,13 @@
         <v>-0.0075</v>
       </c>
       <c r="AK46" t="n">
-        <v>-0.074905</v>
+        <v>-0.085623</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.121265</v>
+        <v>1.136051</v>
       </c>
       <c r="AM46" t="n">
-        <v>12.13</v>
+        <v>13.61</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -19818,10 +19294,10 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.054993</v>
+        <v>0.054261</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.3621</v>
+        <v>1.578</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
@@ -19973,7 +19449,7 @@
         <v>0</v>
       </c>
       <c r="CP46" t="n">
-        <v>0.5495</v>
+        <v>0.5739</v>
       </c>
       <c r="CQ46" t="n">
         <v>0</v>
@@ -20103,10 +19579,10 @@
         <v>0.0247</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.4417</v>
+        <v>0.4406</v>
       </c>
       <c r="AH47" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -20115,13 +19591,13 @@
         <v>0.1436</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.01032</v>
+        <v>-0.011832</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.959282</v>
+        <v>0.967388</v>
       </c>
       <c r="AM47" t="n">
-        <v>-4.07</v>
+        <v>-3.26</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
@@ -20151,10 +19627,10 @@
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.068967</v>
+        <v>0.068871</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.1496</v>
+        <v>0.1718</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -20306,7 +19782,7 @@
         <v>0</v>
       </c>
       <c r="CP47" t="n">
-        <v>0.3702</v>
+        <v>0.3726</v>
       </c>
       <c r="CQ47" t="n">
         <v>0</v>
@@ -20361,7 +19837,7 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -20437,13 +19913,13 @@
         <v>-0.1585</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.0287</v>
+        <v>0.0288</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.1803</v>
+        <v>0.1858</v>
       </c>
       <c r="AH48" t="n">
-        <v>8.24</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -20452,13 +19928,13 @@
         <v>0.0021</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.06118</v>
+        <v>-0.075325</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.103492</v>
+        <v>1.105022</v>
       </c>
       <c r="AM48" t="n">
-        <v>10.35</v>
+        <v>10.5</v>
       </c>
       <c r="AN48" t="n">
         <v>1</v>
@@ -20488,10 +19964,10 @@
         <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.079975</v>
+        <v>0.080497</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.765</v>
+        <v>0.9358</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
@@ -20501,7 +19977,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -20639,7 +20115,7 @@
         <v>0</v>
       </c>
       <c r="CP48" t="n">
-        <v>0.4976</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="CQ48" t="n">
         <v>0</v>
@@ -20768,13 +20244,13 @@
         <v>-0.2552</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.0253</v>
+        <v>0.0251</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.5285</v>
+        <v>0.5203</v>
       </c>
       <c r="AH49" t="n">
-        <v>11.54</v>
+        <v>11.45</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -20783,19 +20259,19 @@
         <v>-0.0004</v>
       </c>
       <c r="AK49" t="n">
-        <v>-0.012671</v>
+        <v>-0.015437</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.055786</v>
+        <v>1.061931</v>
       </c>
       <c r="AM49" t="n">
-        <v>5.58</v>
+        <v>6.19</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP49" t="n">
         <v>0</v>
@@ -20819,10 +20295,10 @@
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.07066500000000001</v>
+        <v>0.070095</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.1793</v>
+        <v>0.2202</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -20970,7 +20446,7 @@
         <v>0</v>
       </c>
       <c r="CP49" t="n">
-        <v>0.4014</v>
+        <v>0.4071</v>
       </c>
       <c r="CQ49" t="n">
         <v>0</v>
@@ -21097,13 +20573,13 @@
         <v>0.2292</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.0146</v>
+        <v>0.0147</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.1445</v>
+        <v>0.1463</v>
       </c>
       <c r="AH50" t="n">
-        <v>14.1</v>
+        <v>14.15</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -21112,13 +20588,13 @@
         <v>0.0391</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.020334</v>
+        <v>0.023197</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.103573</v>
+        <v>1.108987</v>
       </c>
       <c r="AM50" t="n">
-        <v>10.36</v>
+        <v>10.9</v>
       </c>
       <c r="AN50" t="n">
         <v>1</v>
@@ -21148,10 +20624,10 @@
         <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.04078</v>
+        <v>0.040931</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.4986</v>
+        <v>0.5667</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
@@ -21303,7 +20779,7 @@
         <v>0</v>
       </c>
       <c r="CP50" t="n">
-        <v>0.4671</v>
+        <v>0.4736</v>
       </c>
       <c r="CQ50" t="n">
         <v>0</v>
@@ -40355,7 +39831,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -40463,7 +39939,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -40679,7 +40155,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -40715,12 +40191,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -41363,7 +40839,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -41653,7 +41129,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.5158</v>
+        <v>0.5202</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -41719,7 +41195,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.6286</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -41785,7 +41261,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.4746</v>
+        <v>0.4753</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -41851,7 +41327,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.4365</v>
+        <v>0.4402</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -41963,7 +41439,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.5798</v>
+        <v>0.5767</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -42213,7 +41689,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.4598</v>
+        <v>0.4649</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -42279,7 +41755,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.4604</v>
+        <v>0.4427</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -42437,7 +41913,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.513</v>
+        <v>0.5139</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -42595,7 +42071,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.439</v>
+        <v>0.4417</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -42727,7 +42203,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.5537</v>
+        <v>0.5599</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -42793,7 +42269,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.4697</v>
+        <v>0.4797</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -42859,7 +42335,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.2943</v>
+        <v>0.2851</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -42967,7 +42443,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.4971</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -43079,7 +42555,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.4514</v>
+        <v>0.4622</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -43191,7 +42667,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.498</v>
+        <v>0.4961</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -43257,7 +42733,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.5956</v>
+        <v>0.6001</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -43415,7 +42891,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.3877</v>
+        <v>0.3938</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -43508,10 +42984,10 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -43523,20 +42999,20 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.4571</v>
+        <v>0.4687</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>compressao</t>
+          <t>neutro_zona_cinza</t>
         </is>
       </c>
     </row>
@@ -43593,7 +43069,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5308</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -43659,7 +43135,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.4244</v>
+        <v>0.4186</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -43706,7 +43182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -43721,15 +43197,15 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.4889</v>
+        <v>0.5014</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -43791,7 +43267,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.5965</v>
+        <v>0.5934</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -44041,7 +43517,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.4021</v>
+        <v>0.4037</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -44107,7 +43583,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.386</v>
+        <v>0.3961</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -44173,7 +43649,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.4639</v>
+        <v>0.474</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -44239,7 +43715,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.4633</v>
+        <v>0.479</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -44424,7 +43900,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -44439,15 +43915,15 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>razao_sinal_baixa</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.4921</v>
+        <v>0.5082</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>fraco</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -44500,20 +43976,20 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Neutro</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>razao_sinal_marginal_sem_condicoes</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.5381</v>
+        <v>0.5165</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>forte</t>
+          <t>marginal</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -44575,7 +44051,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.3315</v>
+        <v>0.3389</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -44641,7 +44117,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0.581</v>
+        <v>0.5809</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -44707,7 +44183,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.4224</v>
+        <v>0.4227</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -45003,7 +44479,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.5349</v>
+        <v>0.5382</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -45391,7 +44867,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.4076</v>
+        <v>0.4074</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -45503,7 +44979,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.364</v>
+        <v>0.3749</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -45569,7 +45045,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.4627</v>
+        <v>0.4613</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -45677,7 +45153,7 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.4917</v>
+        <v>0.4952</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -45743,7 +45219,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.3827</v>
+        <v>0.3701</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -45963,7 +45439,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.5239</v>
+        <v>0.5204</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -46029,7 +45505,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.4384</v>
+        <v>0.4394</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -46359,7 +45835,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0.6108</v>
+        <v>0.6287</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -46559,7 +46035,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.5505</v>
+        <v>0.5434</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -46625,7 +46101,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0.4383</v>
+        <v>0.4549</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -46691,7 +46167,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.5495</v>
+        <v>0.5739</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -46803,7 +46279,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0.3702</v>
+        <v>0.3726</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -46865,15 +46341,15 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>razao_sinal_marginal_sem_condicoes</t>
+          <t>volatility_gate_bloqueado:expansao_moderada_sem_exec_forte</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0.4976</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>marginal</t>
+          <t>forte</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -46981,7 +46457,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.4014</v>
+        <v>0.4071</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -47093,7 +46569,7 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0.4671</v>
+        <v>0.4736</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -47319,7 +46795,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -47329,7 +46805,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -47349,7 +46825,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -47389,7 +46865,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -47419,7 +46895,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30">
@@ -47439,7 +46915,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="32">
